--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1061,6 +1061,501 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129945635</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gillermyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>630288</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6967162</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 ex födosökande</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129945638</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gillermyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>630193</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6967148</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129945640</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91812</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>48</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gillermyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>630115</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6967055</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129945641</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gillermyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>630122</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6967130</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129945639</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91897</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>658</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gillermyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>630098</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6967064</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>129945635</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129945638</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129945640</v>
       </c>
       <c r="B8" t="n">
-        <v>91812</v>
+        <v>91815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129945641</v>
+        <v>129945639</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>91900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630122</v>
+        <v>630098</v>
       </c>
       <c r="R9" t="n">
-        <v>6967130</v>
+        <v>6967064</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129945639</v>
+        <v>129945641</v>
       </c>
       <c r="B10" t="n">
-        <v>91897</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630098</v>
+        <v>630122</v>
       </c>
       <c r="R10" t="n">
-        <v>6967064</v>
+        <v>6967130</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>129945635</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129945638</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129945640</v>
       </c>
       <c r="B8" t="n">
-        <v>91815</v>
+        <v>91818</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129945639</v>
       </c>
       <c r="B9" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129945641</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1270,7 +1270,7 @@
         <v>129945640</v>
       </c>
       <c r="B8" t="n">
-        <v>91818</v>
+        <v>91819</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129945639</v>
       </c>
       <c r="B9" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129945641</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129945639</v>
+        <v>129945641</v>
       </c>
       <c r="B9" t="n">
-        <v>91904</v>
+        <v>79088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630098</v>
+        <v>630122</v>
       </c>
       <c r="R9" t="n">
-        <v>6967064</v>
+        <v>6967130</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129945641</v>
+        <v>129945639</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>91904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630122</v>
+        <v>630098</v>
       </c>
       <c r="R10" t="n">
-        <v>6967130</v>
+        <v>6967064</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1168,7 +1168,7 @@
         <v>129945638</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129945640</v>
       </c>
       <c r="B8" t="n">
-        <v>91819</v>
+        <v>91836</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129945641</v>
+        <v>129945639</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>91921</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630122</v>
+        <v>630098</v>
       </c>
       <c r="R9" t="n">
-        <v>6967130</v>
+        <v>6967064</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129945639</v>
+        <v>129945641</v>
       </c>
       <c r="B10" t="n">
-        <v>91904</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630098</v>
+        <v>630122</v>
       </c>
       <c r="R10" t="n">
-        <v>6967064</v>
+        <v>6967130</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1270,7 +1270,7 @@
         <v>129945640</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129945639</v>
       </c>
       <c r="B9" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>129945635</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129945638</v>
       </c>
       <c r="B7" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129945640</v>
       </c>
       <c r="B8" t="n">
-        <v>91854</v>
+        <v>91941</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129945639</v>
+        <v>129945641</v>
       </c>
       <c r="B9" t="n">
-        <v>91939</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630098</v>
+        <v>630122</v>
       </c>
       <c r="R9" t="n">
-        <v>6967064</v>
+        <v>6967130</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129945641</v>
+        <v>129945639</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>92026</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630122</v>
+        <v>630098</v>
       </c>
       <c r="R10" t="n">
-        <v>6967130</v>
+        <v>6967064</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129945641</v>
+        <v>129945639</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>92026</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630122</v>
+        <v>630098</v>
       </c>
       <c r="R9" t="n">
-        <v>6967130</v>
+        <v>6967064</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129945639</v>
+        <v>129945641</v>
       </c>
       <c r="B10" t="n">
-        <v>92026</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630098</v>
+        <v>630122</v>
       </c>
       <c r="R10" t="n">
-        <v>6967064</v>
+        <v>6967130</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>129945635</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129945638</v>
       </c>
       <c r="B7" t="n">
-        <v>57985</v>
+        <v>57900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129945640</v>
       </c>
       <c r="B8" t="n">
-        <v>91941</v>
+        <v>91854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129945639</v>
       </c>
       <c r="B9" t="n">
-        <v>92026</v>
+        <v>91939</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129945641</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1777,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133152220</v>
+        <v>133152204</v>
       </c>
       <c r="B13" t="n">
-        <v>91932</v>
+        <v>91918</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,21 +1788,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630135</v>
+        <v>630265</v>
       </c>
       <c r="R13" t="n">
-        <v>6967160</v>
+        <v>6967240</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133152217</v>
+        <v>133152220</v>
       </c>
       <c r="B14" t="n">
-        <v>92217</v>
+        <v>91932</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1895,21 +1895,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630130</v>
+        <v>630135</v>
       </c>
       <c r="R14" t="n">
-        <v>6967217</v>
+        <v>6967160</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133152204</v>
+        <v>133152217</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2002,21 +2002,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630265</v>
+        <v>630130</v>
       </c>
       <c r="R15" t="n">
-        <v>6967240</v>
+        <v>6967217</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2098,10 +2098,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133152205</v>
+        <v>133152174</v>
       </c>
       <c r="B16" t="n">
-        <v>92217</v>
+        <v>83181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2109,21 +2109,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630269</v>
+        <v>630286</v>
       </c>
       <c r="R16" t="n">
-        <v>6967234</v>
+        <v>6967149</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>05:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>05:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,32 +2205,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133152225</v>
+        <v>133152185</v>
       </c>
       <c r="B17" t="n">
-        <v>79365</v>
+        <v>91881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630153</v>
+        <v>630303</v>
       </c>
       <c r="R17" t="n">
-        <v>6967136</v>
+        <v>6967279</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133152246</v>
+        <v>133152165</v>
       </c>
       <c r="B18" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630264</v>
+        <v>630325</v>
       </c>
       <c r="R18" t="n">
-        <v>6967100</v>
+        <v>6967107</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133152174</v>
+        <v>133152205</v>
       </c>
       <c r="B19" t="n">
-        <v>83181</v>
+        <v>92217</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630286</v>
+        <v>630269</v>
       </c>
       <c r="R19" t="n">
-        <v>6967149</v>
+        <v>6967234</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,7 +2526,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133152163</v>
+        <v>133152225</v>
       </c>
       <c r="B20" t="n">
         <v>79365</v>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630334</v>
+        <v>630153</v>
       </c>
       <c r="R20" t="n">
-        <v>6967097</v>
+        <v>6967136</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133152218</v>
+        <v>133152246</v>
       </c>
       <c r="B21" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630124</v>
+        <v>630264</v>
       </c>
       <c r="R21" t="n">
-        <v>6967208</v>
+        <v>6967100</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2740,32 +2740,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133152185</v>
+        <v>133152163</v>
       </c>
       <c r="B22" t="n">
-        <v>91881</v>
+        <v>79365</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630303</v>
+        <v>630334</v>
       </c>
       <c r="R22" t="n">
-        <v>6967279</v>
+        <v>6967097</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133152165</v>
+        <v>133152218</v>
       </c>
       <c r="B23" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630325</v>
+        <v>630124</v>
       </c>
       <c r="R23" t="n">
-        <v>6967107</v>
+        <v>6967208</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3489,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133152188</v>
+        <v>133152173</v>
       </c>
       <c r="B29" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,21 +3500,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630274</v>
+        <v>630300</v>
       </c>
       <c r="R29" t="n">
-        <v>6967324</v>
+        <v>6967133</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3596,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133152184</v>
+        <v>133152188</v>
       </c>
       <c r="B30" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630304</v>
+        <v>630274</v>
       </c>
       <c r="R30" t="n">
-        <v>6967273</v>
+        <v>6967324</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3703,10 +3703,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133152173</v>
+        <v>133152184</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630300</v>
+        <v>630304</v>
       </c>
       <c r="R31" t="n">
-        <v>6967133</v>
+        <v>6967273</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3810,10 +3810,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133152203</v>
+        <v>133152193</v>
       </c>
       <c r="B32" t="n">
-        <v>91932</v>
+        <v>83181</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3821,21 +3821,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630258</v>
+        <v>630280</v>
       </c>
       <c r="R32" t="n">
-        <v>6967247</v>
+        <v>6967356</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3917,10 +3917,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133152193</v>
+        <v>133152203</v>
       </c>
       <c r="B33" t="n">
-        <v>83181</v>
+        <v>91932</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3928,21 +3928,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630280</v>
+        <v>630258</v>
       </c>
       <c r="R33" t="n">
-        <v>6967356</v>
+        <v>6967247</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4024,10 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133152234</v>
+        <v>133152206</v>
       </c>
       <c r="B34" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630161</v>
+        <v>630256</v>
       </c>
       <c r="R34" t="n">
-        <v>6967098</v>
+        <v>6967220</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4131,7 +4131,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133152164</v>
+        <v>133152234</v>
       </c>
       <c r="B35" t="n">
         <v>79365</v>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630325</v>
+        <v>630161</v>
       </c>
       <c r="R35" t="n">
-        <v>6967107</v>
+        <v>6967098</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4238,7 +4238,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133152167</v>
+        <v>133152164</v>
       </c>
       <c r="B36" t="n">
         <v>79365</v>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630318</v>
+        <v>630325</v>
       </c>
       <c r="R36" t="n">
-        <v>6967112</v>
+        <v>6967107</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>04:51</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>04:51</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4345,10 +4345,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133152206</v>
+        <v>133152167</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4356,21 +4356,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630256</v>
+        <v>630318</v>
       </c>
       <c r="R37" t="n">
-        <v>6967220</v>
+        <v>6967112</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4452,10 +4452,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133152242</v>
+        <v>133152178</v>
       </c>
       <c r="B38" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4463,21 +4463,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4487,13 +4487,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630247</v>
+        <v>630300</v>
       </c>
       <c r="R38" t="n">
-        <v>6967129</v>
+        <v>6967148</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>05:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>05:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4559,10 +4559,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133152178</v>
+        <v>133152242</v>
       </c>
       <c r="B39" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,21 +4570,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4594,13 +4594,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630300</v>
+        <v>630247</v>
       </c>
       <c r="R39" t="n">
-        <v>6967148</v>
+        <v>6967129</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>05:16</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>05:16</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4987,32 +4987,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133152195</v>
+        <v>133152201</v>
       </c>
       <c r="B43" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630297</v>
+        <v>630261</v>
       </c>
       <c r="R43" t="n">
-        <v>6967347</v>
+        <v>6967251</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5094,32 +5094,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133152216</v>
+        <v>133152195</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>75433</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630149</v>
+        <v>630297</v>
       </c>
       <c r="R44" t="n">
-        <v>6967241</v>
+        <v>6967347</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5201,32 +5201,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133152197</v>
+        <v>133152216</v>
       </c>
       <c r="B45" t="n">
-        <v>75433</v>
+        <v>79333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630298</v>
+        <v>630149</v>
       </c>
       <c r="R45" t="n">
-        <v>6967342</v>
+        <v>6967241</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5308,32 +5308,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133152201</v>
+        <v>133152197</v>
       </c>
       <c r="B46" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5343,10 +5343,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630261</v>
+        <v>630298</v>
       </c>
       <c r="R46" t="n">
-        <v>6967251</v>
+        <v>6967342</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -7127,10 +7127,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133152215</v>
+        <v>133152227</v>
       </c>
       <c r="B63" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7138,21 +7138,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>630159</v>
+        <v>630148</v>
       </c>
       <c r="R63" t="n">
-        <v>6967229</v>
+        <v>6967117</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7234,7 +7234,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133152239</v>
+        <v>133152215</v>
       </c>
       <c r="B64" t="n">
         <v>91918</v>
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>630255</v>
+        <v>630159</v>
       </c>
       <c r="R64" t="n">
-        <v>6967168</v>
+        <v>6967229</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7341,10 +7341,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133152227</v>
+        <v>133152239</v>
       </c>
       <c r="B65" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7352,21 +7352,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>630148</v>
+        <v>630255</v>
       </c>
       <c r="R65" t="n">
-        <v>6967117</v>
+        <v>6967168</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7567,10 +7567,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133152199</v>
+        <v>133152190</v>
       </c>
       <c r="B67" t="n">
-        <v>79365</v>
+        <v>83181</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7578,21 +7578,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>630251</v>
+        <v>630270</v>
       </c>
       <c r="R67" t="n">
-        <v>6967351</v>
+        <v>6967330</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7674,10 +7674,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133152219</v>
+        <v>133152199</v>
       </c>
       <c r="B68" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7685,21 +7685,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>630121</v>
+        <v>630251</v>
       </c>
       <c r="R68" t="n">
-        <v>6967203</v>
+        <v>6967351</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7781,10 +7781,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133152190</v>
+        <v>133152219</v>
       </c>
       <c r="B69" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7792,21 +7792,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7816,10 +7816,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630270</v>
+        <v>630121</v>
       </c>
       <c r="R69" t="n">
-        <v>6967330</v>
+        <v>6967203</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8102,32 +8102,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133152200</v>
+        <v>133152187</v>
       </c>
       <c r="B72" t="n">
-        <v>83181</v>
+        <v>91881</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>630250</v>
+        <v>630305</v>
       </c>
       <c r="R72" t="n">
-        <v>6967263</v>
+        <v>6967310</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8209,10 +8209,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133152223</v>
+        <v>133152200</v>
       </c>
       <c r="B73" t="n">
-        <v>89300</v>
+        <v>83181</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8220,21 +8220,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>630159</v>
+        <v>630250</v>
       </c>
       <c r="R73" t="n">
-        <v>6967161</v>
+        <v>6967263</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8316,32 +8316,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133152187</v>
+        <v>133152223</v>
       </c>
       <c r="B74" t="n">
-        <v>91881</v>
+        <v>89300</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>630305</v>
+        <v>630159</v>
       </c>
       <c r="R74" t="n">
-        <v>6967310</v>
+        <v>6967161</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8423,10 +8423,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133152171</v>
+        <v>133152181</v>
       </c>
       <c r="B75" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8434,21 +8434,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8458,10 +8458,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>630307</v>
+        <v>630334</v>
       </c>
       <c r="R75" t="n">
-        <v>6967118</v>
+        <v>6967171</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8530,10 +8530,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133152212</v>
+        <v>133152182</v>
       </c>
       <c r="B76" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8541,21 +8541,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8565,13 +8565,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>630176</v>
+        <v>630324</v>
       </c>
       <c r="R76" t="n">
-        <v>6967173</v>
+        <v>6967248</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8637,10 +8637,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133152181</v>
+        <v>133152212</v>
       </c>
       <c r="B77" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8648,21 +8648,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8672,13 +8672,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>630334</v>
+        <v>630176</v>
       </c>
       <c r="R77" t="n">
-        <v>6967171</v>
+        <v>6967173</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8744,10 +8744,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133152182</v>
+        <v>133152171</v>
       </c>
       <c r="B78" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8755,21 +8755,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>630324</v>
+        <v>630307</v>
       </c>
       <c r="R78" t="n">
-        <v>6967248</v>
+        <v>6967118</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8851,10 +8851,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133152228</v>
+        <v>133152207</v>
       </c>
       <c r="B79" t="n">
-        <v>79365</v>
+        <v>58119</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8862,34 +8862,46 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>630092</v>
+        <v>630231</v>
       </c>
       <c r="R79" t="n">
-        <v>6967142</v>
+        <v>6967249</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8921,7 +8933,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8931,7 +8943,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8958,10 +8970,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133152207</v>
+        <v>133152169</v>
       </c>
       <c r="B80" t="n">
-        <v>58119</v>
+        <v>79333</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8969,46 +8981,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>630231</v>
+        <v>630316</v>
       </c>
       <c r="R80" t="n">
-        <v>6967249</v>
+        <v>6967112</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9040,7 +9040,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9077,7 +9077,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133152169</v>
+        <v>133152170</v>
       </c>
       <c r="B81" t="n">
         <v>79333</v>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>630316</v>
+        <v>630313</v>
       </c>
       <c r="R81" t="n">
-        <v>6967112</v>
+        <v>6967117</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9184,10 +9184,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133152170</v>
+        <v>133152228</v>
       </c>
       <c r="B82" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9195,21 +9195,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9219,10 +9219,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>630313</v>
+        <v>630092</v>
       </c>
       <c r="R82" t="n">
-        <v>6967117</v>
+        <v>6967142</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10254,32 +10254,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133202148</v>
+        <v>133202173</v>
       </c>
       <c r="B92" t="n">
-        <v>79333</v>
+        <v>92641</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>630099</v>
+        <v>630299</v>
       </c>
       <c r="R92" t="n">
-        <v>6967120</v>
+        <v>6967218</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10361,32 +10361,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133202173</v>
+        <v>133202145</v>
       </c>
       <c r="B93" t="n">
-        <v>92641</v>
+        <v>91932</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>630299</v>
+        <v>630093</v>
       </c>
       <c r="R93" t="n">
-        <v>6967218</v>
+        <v>6967070</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10468,10 +10468,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133202145</v>
+        <v>133202168</v>
       </c>
       <c r="B94" t="n">
-        <v>91932</v>
+        <v>83181</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10479,21 +10479,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>630093</v>
+        <v>630290</v>
       </c>
       <c r="R94" t="n">
-        <v>6967070</v>
+        <v>6967317</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10575,10 +10575,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133202168</v>
+        <v>133202155</v>
       </c>
       <c r="B95" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10586,21 +10586,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>630290</v>
+        <v>630210</v>
       </c>
       <c r="R95" t="n">
-        <v>6967317</v>
+        <v>6967196</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10682,10 +10682,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133202155</v>
+        <v>133202148</v>
       </c>
       <c r="B96" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10693,21 +10693,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10717,10 +10717,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>630210</v>
+        <v>630099</v>
       </c>
       <c r="R96" t="n">
-        <v>6967196</v>
+        <v>6967120</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11003,32 +11003,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133202150</v>
+        <v>133202163</v>
       </c>
       <c r="B99" t="n">
-        <v>79589</v>
+        <v>79333</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11038,10 +11038,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>630122</v>
+        <v>630344</v>
       </c>
       <c r="R99" t="n">
-        <v>6967138</v>
+        <v>6967158</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11110,32 +11110,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133202163</v>
+        <v>133202150</v>
       </c>
       <c r="B100" t="n">
-        <v>79333</v>
+        <v>79589</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11145,10 +11145,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>630344</v>
+        <v>630122</v>
       </c>
       <c r="R100" t="n">
-        <v>6967158</v>
+        <v>6967138</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11553,10 +11553,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133202152</v>
+        <v>133202171</v>
       </c>
       <c r="B104" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>630108</v>
+        <v>630271</v>
       </c>
       <c r="R104" t="n">
-        <v>6967186</v>
+        <v>6967309</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11660,10 +11660,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133202159</v>
+        <v>133202125</v>
       </c>
       <c r="B105" t="n">
-        <v>91932</v>
+        <v>79365</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11671,21 +11671,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>630290</v>
+        <v>630331</v>
       </c>
       <c r="R105" t="n">
-        <v>6967123</v>
+        <v>6967087</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11767,7 +11767,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133202125</v>
+        <v>133202152</v>
       </c>
       <c r="B106" t="n">
         <v>79365</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>630331</v>
+        <v>630108</v>
       </c>
       <c r="R106" t="n">
-        <v>6967087</v>
+        <v>6967186</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11874,10 +11874,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133202171</v>
+        <v>133202159</v>
       </c>
       <c r="B107" t="n">
-        <v>79333</v>
+        <v>91932</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>630271</v>
+        <v>630290</v>
       </c>
       <c r="R107" t="n">
-        <v>6967309</v>
+        <v>6967123</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13278,10 +13278,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133202141</v>
+        <v>133202164</v>
       </c>
       <c r="B120" t="n">
-        <v>89300</v>
+        <v>79333</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13289,21 +13289,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13313,10 +13313,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>630101</v>
+        <v>630329</v>
       </c>
       <c r="R120" t="n">
-        <v>6967092</v>
+        <v>6967216</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13348,7 +13348,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13385,10 +13385,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133202164</v>
+        <v>133202141</v>
       </c>
       <c r="B121" t="n">
-        <v>79333</v>
+        <v>89300</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13396,21 +13396,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13420,10 +13420,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>630329</v>
+        <v>630101</v>
       </c>
       <c r="R121" t="n">
-        <v>6967216</v>
+        <v>6967092</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13455,7 +13455,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13813,10 +13813,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133202137</v>
+        <v>133202136</v>
       </c>
       <c r="B125" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13824,21 +13824,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>630158</v>
+        <v>630184</v>
       </c>
       <c r="R125" t="n">
-        <v>6967093</v>
+        <v>6967090</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13920,10 +13920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133202136</v>
+        <v>133202137</v>
       </c>
       <c r="B126" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13931,21 +13931,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>630184</v>
+        <v>630158</v>
       </c>
       <c r="R126" t="n">
-        <v>6967090</v>
+        <v>6967093</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14776,7 +14776,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133240044</v>
+        <v>133240019</v>
       </c>
       <c r="B134" t="n">
         <v>79333</v>
@@ -14811,10 +14811,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>630257</v>
+        <v>630164</v>
       </c>
       <c r="R134" t="n">
-        <v>6967346</v>
+        <v>6967058</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14846,7 +14846,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14883,7 +14883,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133240019</v>
+        <v>133240044</v>
       </c>
       <c r="B135" t="n">
         <v>79333</v>
@@ -14918,10 +14918,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>630164</v>
+        <v>630257</v>
       </c>
       <c r="R135" t="n">
-        <v>6967058</v>
+        <v>6967346</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15525,10 +15525,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133240010</v>
+        <v>133240030</v>
       </c>
       <c r="B141" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15536,21 +15536,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15560,13 +15560,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>630202</v>
+        <v>630210</v>
       </c>
       <c r="R141" t="n">
-        <v>6967062</v>
+        <v>6967208</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15632,10 +15632,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133240037</v>
+        <v>133240010</v>
       </c>
       <c r="B142" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15643,21 +15643,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15667,10 +15667,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>630379</v>
+        <v>630202</v>
       </c>
       <c r="R142" t="n">
-        <v>6967127</v>
+        <v>6967062</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15739,7 +15739,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133240030</v>
+        <v>133240037</v>
       </c>
       <c r="B143" t="n">
         <v>79333</v>
@@ -15774,13 +15774,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>630210</v>
+        <v>630379</v>
       </c>
       <c r="R143" t="n">
-        <v>6967208</v>
+        <v>6967127</v>
       </c>
       <c r="S143" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16167,10 +16167,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133240020</v>
+        <v>133244099</v>
       </c>
       <c r="B147" t="n">
-        <v>79365</v>
+        <v>57958</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16178,37 +16178,53 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Gillemyrtjärnen, Ång</t>
+          <t>Gillermyrtjärnen, Lomtjärnsåsen, Sela, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>630162</v>
+        <v>630169</v>
       </c>
       <c r="R147" t="n">
-        <v>6967059</v>
+        <v>6967162</v>
       </c>
       <c r="S147" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16237,7 +16253,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16247,7 +16263,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Ljudbox har använts och trummande tretåig hackspett har registrerats. Programmet Audacity har använts för att analysera trumningarna som hördes tidigt på morgonen. Trumningarna är i genomsnitt 1,2 sekunder långa med en slagfrekvens på i genomsnitt 12,7 slag/sekund vilket stämmer väl in på tretåig hackspett. Bifogat finns en del av ljudupptagningen och en bild med ett utmarkerat grönt kryss där genomsnittsvärdena har placerats ut samt ett skärmklipp från analysprogrammet audacity där trumningarna syns.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16274,10 +16295,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133244099</v>
+        <v>133240020</v>
       </c>
       <c r="B148" t="n">
-        <v>57958</v>
+        <v>79365</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16285,53 +16306,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Gillermyrtjärnen, Lomtjärnsåsen, Sela, Ång</t>
+          <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>630169</v>
+        <v>630162</v>
       </c>
       <c r="R148" t="n">
-        <v>6967162</v>
+        <v>6967059</v>
       </c>
       <c r="S148" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16360,7 +16365,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16370,12 +16375,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Ljudbox har använts och trummande tretåig hackspett har registrerats. Programmet Audacity har använts för att analysera trumningarna som hördes tidigt på morgonen. Trumningarna är i genomsnitt 1,2 sekunder långa med en slagfrekvens på i genomsnitt 12,7 slag/sekund vilket stämmer väl in på tretåig hackspett. Bifogat finns en del av ljudupptagningen och en bild med ett utmarkerat grönt kryss där genomsnittsvärdena har placerats ut samt ett skärmklipp från analysprogrammet audacity där trumningarna syns.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16509,10 +16509,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133240038</v>
+        <v>133240024</v>
       </c>
       <c r="B150" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16520,21 +16520,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16544,13 +16544,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>630337</v>
+        <v>630079</v>
       </c>
       <c r="R150" t="n">
-        <v>6967201</v>
+        <v>6967088</v>
       </c>
       <c r="S150" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16616,10 +16616,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133240024</v>
+        <v>133240038</v>
       </c>
       <c r="B151" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16627,21 +16627,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16651,13 +16651,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>630079</v>
+        <v>630337</v>
       </c>
       <c r="R151" t="n">
-        <v>6967088</v>
+        <v>6967201</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17579,7 +17579,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133240036</v>
+        <v>133240028</v>
       </c>
       <c r="B160" t="n">
         <v>79333</v>
@@ -17614,10 +17614,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>630368</v>
+        <v>630174</v>
       </c>
       <c r="R160" t="n">
-        <v>6967120</v>
+        <v>6967208</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17686,7 +17686,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133240028</v>
+        <v>133240025</v>
       </c>
       <c r="B161" t="n">
         <v>79333</v>
@@ -17721,10 +17721,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>630174</v>
+        <v>630103</v>
       </c>
       <c r="R161" t="n">
-        <v>6967208</v>
+        <v>6967179</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17793,7 +17793,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133240025</v>
+        <v>133240036</v>
       </c>
       <c r="B162" t="n">
         <v>79333</v>
@@ -17828,10 +17828,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>630103</v>
+        <v>630368</v>
       </c>
       <c r="R162" t="n">
-        <v>6967179</v>
+        <v>6967120</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18221,7 +18221,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133240041</v>
+        <v>133240018</v>
       </c>
       <c r="B166" t="n">
         <v>79333</v>
@@ -18256,10 +18256,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>630250</v>
+        <v>630148</v>
       </c>
       <c r="R166" t="n">
-        <v>6967366</v>
+        <v>6967065</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18328,7 +18328,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>133240018</v>
+        <v>133240041</v>
       </c>
       <c r="B167" t="n">
         <v>79333</v>
@@ -18363,10 +18363,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>630148</v>
+        <v>630250</v>
       </c>
       <c r="R167" t="n">
-        <v>6967065</v>
+        <v>6967366</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1670,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133152222</v>
+        <v>133152204</v>
       </c>
       <c r="B12" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630156</v>
+        <v>630265</v>
       </c>
       <c r="R12" t="n">
-        <v>6967155</v>
+        <v>6967240</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133152204</v>
+        <v>133152222</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,21 +1788,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630265</v>
+        <v>630156</v>
       </c>
       <c r="R13" t="n">
-        <v>6967240</v>
+        <v>6967155</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2098,10 +2098,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133152174</v>
+        <v>133152205</v>
       </c>
       <c r="B16" t="n">
-        <v>83181</v>
+        <v>92217</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2109,21 +2109,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630286</v>
+        <v>630269</v>
       </c>
       <c r="R16" t="n">
-        <v>6967149</v>
+        <v>6967234</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,32 +2205,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133152185</v>
+        <v>133152225</v>
       </c>
       <c r="B17" t="n">
-        <v>91881</v>
+        <v>79365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630303</v>
+        <v>630153</v>
       </c>
       <c r="R17" t="n">
-        <v>6967279</v>
+        <v>6967136</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133152165</v>
+        <v>133152246</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630325</v>
+        <v>630264</v>
       </c>
       <c r="R18" t="n">
-        <v>6967107</v>
+        <v>6967100</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133152205</v>
+        <v>133152174</v>
       </c>
       <c r="B19" t="n">
-        <v>92217</v>
+        <v>83181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630269</v>
+        <v>630286</v>
       </c>
       <c r="R19" t="n">
-        <v>6967234</v>
+        <v>6967149</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>05:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>05:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,7 +2526,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133152225</v>
+        <v>133152163</v>
       </c>
       <c r="B20" t="n">
         <v>79365</v>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630153</v>
+        <v>630334</v>
       </c>
       <c r="R20" t="n">
-        <v>6967136</v>
+        <v>6967097</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133152246</v>
+        <v>133152218</v>
       </c>
       <c r="B21" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630264</v>
+        <v>630124</v>
       </c>
       <c r="R21" t="n">
-        <v>6967100</v>
+        <v>6967208</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2740,32 +2740,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133152163</v>
+        <v>133152185</v>
       </c>
       <c r="B22" t="n">
-        <v>79365</v>
+        <v>91881</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630334</v>
+        <v>630303</v>
       </c>
       <c r="R22" t="n">
-        <v>6967097</v>
+        <v>6967279</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133152218</v>
+        <v>133152165</v>
       </c>
       <c r="B23" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630124</v>
+        <v>630325</v>
       </c>
       <c r="R23" t="n">
-        <v>6967208</v>
+        <v>6967107</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2954,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133152231</v>
+        <v>133152226</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630146</v>
+        <v>630154</v>
       </c>
       <c r="R24" t="n">
-        <v>6967080</v>
+        <v>6967129</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133152226</v>
+        <v>133152231</v>
       </c>
       <c r="B25" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630154</v>
+        <v>630146</v>
       </c>
       <c r="R25" t="n">
-        <v>6967129</v>
+        <v>6967080</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3489,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133152173</v>
+        <v>133152188</v>
       </c>
       <c r="B29" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,21 +3500,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630300</v>
+        <v>630274</v>
       </c>
       <c r="R29" t="n">
-        <v>6967133</v>
+        <v>6967324</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3596,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133152188</v>
+        <v>133152184</v>
       </c>
       <c r="B30" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630274</v>
+        <v>630304</v>
       </c>
       <c r="R30" t="n">
-        <v>6967324</v>
+        <v>6967273</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3703,10 +3703,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133152184</v>
+        <v>133152173</v>
       </c>
       <c r="B31" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630304</v>
+        <v>630300</v>
       </c>
       <c r="R31" t="n">
-        <v>6967273</v>
+        <v>6967133</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3810,10 +3810,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133152193</v>
+        <v>133152203</v>
       </c>
       <c r="B32" t="n">
-        <v>83181</v>
+        <v>91932</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3821,21 +3821,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630280</v>
+        <v>630258</v>
       </c>
       <c r="R32" t="n">
-        <v>6967356</v>
+        <v>6967247</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3917,10 +3917,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133152203</v>
+        <v>133152193</v>
       </c>
       <c r="B33" t="n">
-        <v>91932</v>
+        <v>83181</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3928,21 +3928,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630258</v>
+        <v>630280</v>
       </c>
       <c r="R33" t="n">
-        <v>6967247</v>
+        <v>6967356</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4024,10 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133152206</v>
+        <v>133152234</v>
       </c>
       <c r="B34" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630256</v>
+        <v>630161</v>
       </c>
       <c r="R34" t="n">
-        <v>6967220</v>
+        <v>6967098</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4131,7 +4131,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133152234</v>
+        <v>133152164</v>
       </c>
       <c r="B35" t="n">
         <v>79365</v>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630161</v>
+        <v>630325</v>
       </c>
       <c r="R35" t="n">
-        <v>6967098</v>
+        <v>6967107</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4238,7 +4238,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133152164</v>
+        <v>133152167</v>
       </c>
       <c r="B36" t="n">
         <v>79365</v>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630325</v>
+        <v>630318</v>
       </c>
       <c r="R36" t="n">
-        <v>6967107</v>
+        <v>6967112</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4345,10 +4345,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133152167</v>
+        <v>133152206</v>
       </c>
       <c r="B37" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4356,21 +4356,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630318</v>
+        <v>630256</v>
       </c>
       <c r="R37" t="n">
-        <v>6967112</v>
+        <v>6967220</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>04:51</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>04:51</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4559,10 +4559,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133152242</v>
+        <v>133152243</v>
       </c>
       <c r="B39" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,21 +4570,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630247</v>
+        <v>630223</v>
       </c>
       <c r="R39" t="n">
-        <v>6967129</v>
+        <v>6967132</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4666,7 +4666,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133152243</v>
+        <v>133152196</v>
       </c>
       <c r="B40" t="n">
         <v>83181</v>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630223</v>
+        <v>630299</v>
       </c>
       <c r="R40" t="n">
-        <v>6967132</v>
+        <v>6967344</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4773,7 +4773,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133152196</v>
+        <v>133152210</v>
       </c>
       <c r="B41" t="n">
         <v>83181</v>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>630299</v>
+        <v>630184</v>
       </c>
       <c r="R41" t="n">
-        <v>6967344</v>
+        <v>6967161</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4880,10 +4880,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133152210</v>
+        <v>133152242</v>
       </c>
       <c r="B42" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4891,21 +4891,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630184</v>
+        <v>630247</v>
       </c>
       <c r="R42" t="n">
-        <v>6967161</v>
+        <v>6967129</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6271,32 +6271,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133152208</v>
+        <v>133152183</v>
       </c>
       <c r="B55" t="n">
-        <v>79333</v>
+        <v>75433</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6306,13 +6306,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630207</v>
+        <v>630308</v>
       </c>
       <c r="R55" t="n">
-        <v>6967295</v>
+        <v>6967259</v>
       </c>
       <c r="S55" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6378,32 +6378,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133152183</v>
+        <v>133152208</v>
       </c>
       <c r="B56" t="n">
-        <v>75433</v>
+        <v>79333</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6413,13 +6413,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630308</v>
+        <v>630207</v>
       </c>
       <c r="R56" t="n">
-        <v>6967259</v>
+        <v>6967295</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6699,10 +6699,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133152175</v>
+        <v>133152215</v>
       </c>
       <c r="B59" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6710,21 +6710,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6734,13 +6734,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630308</v>
+        <v>630159</v>
       </c>
       <c r="R59" t="n">
-        <v>6967163</v>
+        <v>6967229</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6806,10 +6806,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133152191</v>
+        <v>133152239</v>
       </c>
       <c r="B60" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6817,21 +6817,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>630272</v>
+        <v>630255</v>
       </c>
       <c r="R60" t="n">
-        <v>6967349</v>
+        <v>6967168</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6913,10 +6913,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133152180</v>
+        <v>133152227</v>
       </c>
       <c r="B61" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6924,21 +6924,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6948,13 +6948,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>630315</v>
+        <v>630148</v>
       </c>
       <c r="R61" t="n">
-        <v>6967166</v>
+        <v>6967117</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7020,7 +7020,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133152240</v>
+        <v>133152191</v>
       </c>
       <c r="B62" t="n">
         <v>79333</v>
@@ -7055,10 +7055,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630263</v>
+        <v>630272</v>
       </c>
       <c r="R62" t="n">
-        <v>6967142</v>
+        <v>6967349</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7127,10 +7127,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133152227</v>
+        <v>133152240</v>
       </c>
       <c r="B63" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7138,21 +7138,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>630148</v>
+        <v>630263</v>
       </c>
       <c r="R63" t="n">
-        <v>6967117</v>
+        <v>6967142</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7234,10 +7234,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133152215</v>
+        <v>133152180</v>
       </c>
       <c r="B64" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7245,21 +7245,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7269,13 +7269,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>630159</v>
+        <v>630315</v>
       </c>
       <c r="R64" t="n">
-        <v>6967229</v>
+        <v>6967166</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7341,10 +7341,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133152239</v>
+        <v>133152175</v>
       </c>
       <c r="B65" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7352,21 +7352,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7376,13 +7376,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>630255</v>
+        <v>630308</v>
       </c>
       <c r="R65" t="n">
-        <v>6967168</v>
+        <v>6967163</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7448,10 +7448,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133152177</v>
+        <v>133152199</v>
       </c>
       <c r="B66" t="n">
-        <v>58119</v>
+        <v>79365</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7459,46 +7459,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>630306</v>
+        <v>630251</v>
       </c>
       <c r="R66" t="n">
-        <v>6967160</v>
+        <v>6967351</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7530,7 +7518,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>05:13</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7540,7 +7528,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>05:13</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7567,10 +7555,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133152190</v>
+        <v>133152219</v>
       </c>
       <c r="B67" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7578,21 +7566,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7602,10 +7590,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>630270</v>
+        <v>630121</v>
       </c>
       <c r="R67" t="n">
-        <v>6967330</v>
+        <v>6967203</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7637,7 +7625,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7647,7 +7635,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7674,10 +7662,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133152199</v>
+        <v>133152190</v>
       </c>
       <c r="B68" t="n">
-        <v>79365</v>
+        <v>83181</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7685,21 +7673,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7709,10 +7697,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>630251</v>
+        <v>630270</v>
       </c>
       <c r="R68" t="n">
-        <v>6967351</v>
+        <v>6967330</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7744,7 +7732,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7754,7 +7742,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7781,10 +7769,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133152219</v>
+        <v>133152177</v>
       </c>
       <c r="B69" t="n">
-        <v>91918</v>
+        <v>58119</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7792,34 +7780,46 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630121</v>
+        <v>630306</v>
       </c>
       <c r="R69" t="n">
-        <v>6967203</v>
+        <v>6967160</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>05:13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>05:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8423,10 +8423,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133152181</v>
+        <v>133152171</v>
       </c>
       <c r="B75" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8434,21 +8434,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8458,10 +8458,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>630334</v>
+        <v>630307</v>
       </c>
       <c r="R75" t="n">
-        <v>6967171</v>
+        <v>6967118</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8530,10 +8530,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133152182</v>
+        <v>133152212</v>
       </c>
       <c r="B76" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8541,21 +8541,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8565,13 +8565,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>630324</v>
+        <v>630176</v>
       </c>
       <c r="R76" t="n">
-        <v>6967248</v>
+        <v>6967173</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8637,10 +8637,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133152212</v>
+        <v>133152182</v>
       </c>
       <c r="B77" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8648,21 +8648,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8672,13 +8672,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>630176</v>
+        <v>630324</v>
       </c>
       <c r="R77" t="n">
-        <v>6967173</v>
+        <v>6967248</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8744,10 +8744,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133152171</v>
+        <v>133152181</v>
       </c>
       <c r="B78" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8755,21 +8755,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>630307</v>
+        <v>630334</v>
       </c>
       <c r="R78" t="n">
-        <v>6967118</v>
+        <v>6967171</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8851,10 +8851,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133152207</v>
+        <v>133152170</v>
       </c>
       <c r="B79" t="n">
-        <v>58119</v>
+        <v>79333</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8862,46 +8862,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>630231</v>
+        <v>630313</v>
       </c>
       <c r="R79" t="n">
-        <v>6967249</v>
+        <v>6967117</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8933,7 +8921,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8943,7 +8931,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9077,10 +9065,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133152170</v>
+        <v>133152228</v>
       </c>
       <c r="B81" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9088,21 +9076,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9112,10 +9100,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>630313</v>
+        <v>630092</v>
       </c>
       <c r="R81" t="n">
-        <v>6967117</v>
+        <v>6967142</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9147,7 +9135,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9157,7 +9145,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9184,10 +9172,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133152228</v>
+        <v>133152207</v>
       </c>
       <c r="B82" t="n">
-        <v>79365</v>
+        <v>58119</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9195,34 +9183,46 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>630092</v>
+        <v>630231</v>
       </c>
       <c r="R82" t="n">
-        <v>6967142</v>
+        <v>6967249</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9398,10 +9398,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133152229</v>
+        <v>133152172</v>
       </c>
       <c r="B84" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9409,21 +9409,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9433,10 +9433,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>630095</v>
+        <v>630311</v>
       </c>
       <c r="R84" t="n">
-        <v>6967106</v>
+        <v>6967128</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>04:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>04:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9505,7 +9505,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133152172</v>
+        <v>133152162</v>
       </c>
       <c r="B85" t="n">
         <v>79365</v>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>630311</v>
+        <v>630337</v>
       </c>
       <c r="R85" t="n">
-        <v>6967128</v>
+        <v>6967096</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>04:56</t>
+          <t>04:43</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>04:56</t>
+          <t>04:43</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9612,10 +9612,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133152162</v>
+        <v>133152229</v>
       </c>
       <c r="B86" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9623,21 +9623,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9647,10 +9647,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>630337</v>
+        <v>630095</v>
       </c>
       <c r="R86" t="n">
-        <v>6967096</v>
+        <v>6967106</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>04:43</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>04:43</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9719,10 +9719,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133202135</v>
+        <v>133202128</v>
       </c>
       <c r="B87" t="n">
-        <v>83181</v>
+        <v>79365</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9730,21 +9730,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9754,10 +9754,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>630165</v>
+        <v>630304</v>
       </c>
       <c r="R87" t="n">
-        <v>6967141</v>
+        <v>6967096</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9826,10 +9826,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133202128</v>
+        <v>133202135</v>
       </c>
       <c r="B88" t="n">
-        <v>79365</v>
+        <v>83181</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9837,21 +9837,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9861,10 +9861,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>630304</v>
+        <v>630165</v>
       </c>
       <c r="R88" t="n">
-        <v>6967096</v>
+        <v>6967141</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10254,32 +10254,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133202173</v>
+        <v>133202155</v>
       </c>
       <c r="B92" t="n">
-        <v>92641</v>
+        <v>91918</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>630299</v>
+        <v>630210</v>
       </c>
       <c r="R92" t="n">
-        <v>6967218</v>
+        <v>6967196</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10575,32 +10575,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133202155</v>
+        <v>133202173</v>
       </c>
       <c r="B95" t="n">
-        <v>91918</v>
+        <v>92641</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>630210</v>
+        <v>630299</v>
       </c>
       <c r="R95" t="n">
-        <v>6967196</v>
+        <v>6967218</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11553,10 +11553,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133202171</v>
+        <v>133202152</v>
       </c>
       <c r="B104" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>630271</v>
+        <v>630108</v>
       </c>
       <c r="R104" t="n">
-        <v>6967309</v>
+        <v>6967186</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11767,10 +11767,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133202152</v>
+        <v>133202159</v>
       </c>
       <c r="B106" t="n">
-        <v>79365</v>
+        <v>91932</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11778,21 +11778,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>630108</v>
+        <v>630290</v>
       </c>
       <c r="R106" t="n">
-        <v>6967186</v>
+        <v>6967123</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11874,10 +11874,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133202159</v>
+        <v>133202171</v>
       </c>
       <c r="B107" t="n">
-        <v>91932</v>
+        <v>79333</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>630290</v>
+        <v>630271</v>
       </c>
       <c r="R107" t="n">
-        <v>6967123</v>
+        <v>6967309</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13051,45 +13051,53 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133202170</v>
+        <v>133202138</v>
       </c>
       <c r="B118" t="n">
-        <v>79357</v>
+        <v>57136</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6434</v>
+        <v>102612</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>630274</v>
+        <v>630143</v>
       </c>
       <c r="R118" t="n">
-        <v>6967318</v>
+        <v>6967085</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13121,7 +13129,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13131,7 +13139,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Sannolikt tagen av en rovfågel.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13158,53 +13171,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133202138</v>
+        <v>133202170</v>
       </c>
       <c r="B119" t="n">
-        <v>57136</v>
+        <v>79357</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>102612</v>
+        <v>6434</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>630143</v>
+        <v>630274</v>
       </c>
       <c r="R119" t="n">
-        <v>6967085</v>
+        <v>6967318</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13236,7 +13241,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13246,12 +13251,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Sannolikt tagen av en rovfågel.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13278,10 +13278,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133202164</v>
+        <v>133202141</v>
       </c>
       <c r="B120" t="n">
-        <v>79333</v>
+        <v>89300</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13289,21 +13289,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13313,10 +13313,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>630329</v>
+        <v>630101</v>
       </c>
       <c r="R120" t="n">
-        <v>6967216</v>
+        <v>6967092</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13348,7 +13348,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13385,10 +13385,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133202141</v>
+        <v>133202164</v>
       </c>
       <c r="B121" t="n">
-        <v>89300</v>
+        <v>79333</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13396,21 +13396,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13420,10 +13420,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>630101</v>
+        <v>630329</v>
       </c>
       <c r="R121" t="n">
-        <v>6967092</v>
+        <v>6967216</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13455,7 +13455,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13599,10 +13599,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133202130</v>
+        <v>133202137</v>
       </c>
       <c r="B123" t="n">
-        <v>83181</v>
+        <v>92217</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13610,21 +13610,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13634,10 +13634,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>630275</v>
+        <v>630158</v>
       </c>
       <c r="R123" t="n">
-        <v>6967143</v>
+        <v>6967093</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13706,10 +13706,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133202157</v>
+        <v>133202136</v>
       </c>
       <c r="B124" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13717,21 +13717,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>630257</v>
+        <v>630184</v>
       </c>
       <c r="R124" t="n">
-        <v>6967180</v>
+        <v>6967090</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13813,10 +13813,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133202136</v>
+        <v>133202157</v>
       </c>
       <c r="B125" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13824,21 +13824,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>630184</v>
+        <v>630257</v>
       </c>
       <c r="R125" t="n">
-        <v>6967090</v>
+        <v>6967180</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13920,10 +13920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133202137</v>
+        <v>133202130</v>
       </c>
       <c r="B126" t="n">
-        <v>92217</v>
+        <v>83181</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13931,21 +13931,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>630158</v>
+        <v>630275</v>
       </c>
       <c r="R126" t="n">
-        <v>6967093</v>
+        <v>6967143</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14776,7 +14776,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133240019</v>
+        <v>133240044</v>
       </c>
       <c r="B134" t="n">
         <v>79333</v>
@@ -14811,10 +14811,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>630164</v>
+        <v>630257</v>
       </c>
       <c r="R134" t="n">
-        <v>6967058</v>
+        <v>6967346</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14846,7 +14846,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14883,7 +14883,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133240044</v>
+        <v>133240019</v>
       </c>
       <c r="B135" t="n">
         <v>79333</v>
@@ -14918,10 +14918,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>630257</v>
+        <v>630164</v>
       </c>
       <c r="R135" t="n">
-        <v>6967346</v>
+        <v>6967058</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15418,10 +15418,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133240004</v>
+        <v>133240010</v>
       </c>
       <c r="B140" t="n">
-        <v>79365</v>
+        <v>91918</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15429,21 +15429,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15453,10 +15453,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>630287</v>
+        <v>630202</v>
       </c>
       <c r="R140" t="n">
-        <v>6967110</v>
+        <v>6967062</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15525,7 +15525,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133240030</v>
+        <v>133240037</v>
       </c>
       <c r="B141" t="n">
         <v>79333</v>
@@ -15560,13 +15560,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>630210</v>
+        <v>630379</v>
       </c>
       <c r="R141" t="n">
-        <v>6967208</v>
+        <v>6967127</v>
       </c>
       <c r="S141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15632,10 +15632,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133240010</v>
+        <v>133240004</v>
       </c>
       <c r="B142" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15643,21 +15643,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15667,10 +15667,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>630202</v>
+        <v>630287</v>
       </c>
       <c r="R142" t="n">
-        <v>6967062</v>
+        <v>6967110</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15739,7 +15739,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133240037</v>
+        <v>133240030</v>
       </c>
       <c r="B143" t="n">
         <v>79333</v>
@@ -15774,13 +15774,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>630379</v>
+        <v>630210</v>
       </c>
       <c r="R143" t="n">
-        <v>6967127</v>
+        <v>6967208</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16167,10 +16167,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133244099</v>
+        <v>133240020</v>
       </c>
       <c r="B147" t="n">
-        <v>57958</v>
+        <v>79365</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16178,53 +16178,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Gillermyrtjärnen, Lomtjärnsåsen, Sela, Ång</t>
+          <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>630169</v>
+        <v>630162</v>
       </c>
       <c r="R147" t="n">
-        <v>6967162</v>
+        <v>6967059</v>
       </c>
       <c r="S147" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16253,7 +16237,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16263,12 +16247,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Ljudbox har använts och trummande tretåig hackspett har registrerats. Programmet Audacity har använts för att analysera trumningarna som hördes tidigt på morgonen. Trumningarna är i genomsnitt 1,2 sekunder långa med en slagfrekvens på i genomsnitt 12,7 slag/sekund vilket stämmer väl in på tretåig hackspett. Bifogat finns en del av ljudupptagningen och en bild med ett utmarkerat grönt kryss där genomsnittsvärdena har placerats ut samt ett skärmklipp från analysprogrammet audacity där trumningarna syns.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16295,10 +16274,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133240020</v>
+        <v>133244099</v>
       </c>
       <c r="B148" t="n">
-        <v>79365</v>
+        <v>57958</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16306,37 +16285,53 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Gillemyrtjärnen, Ång</t>
+          <t>Gillermyrtjärnen, Lomtjärnsåsen, Sela, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>630162</v>
+        <v>630169</v>
       </c>
       <c r="R148" t="n">
-        <v>6967059</v>
+        <v>6967162</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16365,7 +16360,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16375,7 +16370,12 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Ljudbox har använts och trummande tretåig hackspett har registrerats. Programmet Audacity har använts för att analysera trumningarna som hördes tidigt på morgonen. Trumningarna är i genomsnitt 1,2 sekunder långa med en slagfrekvens på i genomsnitt 12,7 slag/sekund vilket stämmer väl in på tretåig hackspett. Bifogat finns en del av ljudupptagningen och en bild med ett utmarkerat grönt kryss där genomsnittsvärdena har placerats ut samt ett skärmklipp från analysprogrammet audacity där trumningarna syns.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17365,10 +17365,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133240039</v>
+        <v>133240036</v>
       </c>
       <c r="B158" t="n">
-        <v>89300</v>
+        <v>79333</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17376,21 +17376,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17400,10 +17400,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>630317</v>
+        <v>630368</v>
       </c>
       <c r="R158" t="n">
-        <v>6967329</v>
+        <v>6967120</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -17435,7 +17435,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17472,10 +17472,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>133240007</v>
+        <v>133240025</v>
       </c>
       <c r="B159" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17483,21 +17483,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17507,13 +17507,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>630244</v>
+        <v>630103</v>
       </c>
       <c r="R159" t="n">
-        <v>6967085</v>
+        <v>6967179</v>
       </c>
       <c r="S159" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17579,10 +17579,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133240028</v>
+        <v>133240007</v>
       </c>
       <c r="B160" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17590,21 +17590,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17614,13 +17614,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>630174</v>
+        <v>630244</v>
       </c>
       <c r="R160" t="n">
-        <v>6967208</v>
+        <v>6967085</v>
       </c>
       <c r="S160" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17686,10 +17686,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133240025</v>
+        <v>133240039</v>
       </c>
       <c r="B161" t="n">
-        <v>79333</v>
+        <v>89300</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17697,21 +17697,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17721,10 +17721,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>630103</v>
+        <v>630317</v>
       </c>
       <c r="R161" t="n">
-        <v>6967179</v>
+        <v>6967329</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17793,7 +17793,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133240036</v>
+        <v>133240028</v>
       </c>
       <c r="B162" t="n">
         <v>79333</v>
@@ -17828,10 +17828,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>630368</v>
+        <v>630174</v>
       </c>
       <c r="R162" t="n">
-        <v>6967120</v>
+        <v>6967208</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18221,7 +18221,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133240018</v>
+        <v>133240041</v>
       </c>
       <c r="B166" t="n">
         <v>79333</v>
@@ -18256,10 +18256,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>630148</v>
+        <v>630250</v>
       </c>
       <c r="R166" t="n">
-        <v>6967065</v>
+        <v>6967366</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18328,7 +18328,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>133240041</v>
+        <v>133240018</v>
       </c>
       <c r="B167" t="n">
         <v>79333</v>
@@ -18363,10 +18363,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>630250</v>
+        <v>630148</v>
       </c>
       <c r="R167" t="n">
-        <v>6967366</v>
+        <v>6967065</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -2954,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133152226</v>
+        <v>133152231</v>
       </c>
       <c r="B24" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630154</v>
+        <v>630146</v>
       </c>
       <c r="R24" t="n">
-        <v>6967129</v>
+        <v>6967080</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133152231</v>
+        <v>133152226</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630146</v>
+        <v>630154</v>
       </c>
       <c r="R25" t="n">
-        <v>6967080</v>
+        <v>6967129</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4452,10 +4452,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133152178</v>
+        <v>133152242</v>
       </c>
       <c r="B38" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4463,21 +4463,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4487,13 +4487,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630300</v>
+        <v>630247</v>
       </c>
       <c r="R38" t="n">
-        <v>6967148</v>
+        <v>6967129</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>05:16</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>05:16</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4559,10 +4559,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133152243</v>
+        <v>133152178</v>
       </c>
       <c r="B39" t="n">
-        <v>83181</v>
+        <v>79365</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,21 +4570,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4594,13 +4594,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630223</v>
+        <v>630300</v>
       </c>
       <c r="R39" t="n">
-        <v>6967132</v>
+        <v>6967148</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>05:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>05:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4666,7 +4666,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133152196</v>
+        <v>133152243</v>
       </c>
       <c r="B40" t="n">
         <v>83181</v>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630299</v>
+        <v>630223</v>
       </c>
       <c r="R40" t="n">
-        <v>6967344</v>
+        <v>6967132</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4773,7 +4773,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133152210</v>
+        <v>133152196</v>
       </c>
       <c r="B41" t="n">
         <v>83181</v>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>630184</v>
+        <v>630299</v>
       </c>
       <c r="R41" t="n">
-        <v>6967161</v>
+        <v>6967344</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4880,10 +4880,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133152242</v>
+        <v>133152210</v>
       </c>
       <c r="B42" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4891,21 +4891,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630247</v>
+        <v>630184</v>
       </c>
       <c r="R42" t="n">
-        <v>6967129</v>
+        <v>6967161</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5522,7 +5522,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133152159</v>
+        <v>133152198</v>
       </c>
       <c r="B48" t="n">
         <v>79365</v>
@@ -5557,13 +5557,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>630350</v>
+        <v>630231</v>
       </c>
       <c r="R48" t="n">
-        <v>6967090</v>
+        <v>6967393</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5629,7 +5629,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133152198</v>
+        <v>133152232</v>
       </c>
       <c r="B49" t="n">
         <v>79365</v>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>630231</v>
+        <v>630147</v>
       </c>
       <c r="R49" t="n">
-        <v>6967393</v>
+        <v>6967088</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5736,7 +5736,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133152232</v>
+        <v>133152159</v>
       </c>
       <c r="B50" t="n">
         <v>79365</v>
@@ -5771,13 +5771,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>630147</v>
+        <v>630350</v>
       </c>
       <c r="R50" t="n">
-        <v>6967088</v>
+        <v>6967090</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5843,10 +5843,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133152209</v>
+        <v>133152189</v>
       </c>
       <c r="B51" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5854,21 +5854,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>630184</v>
+        <v>630270</v>
       </c>
       <c r="R51" t="n">
-        <v>6967242</v>
+        <v>6967330</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>05:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>05:56</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5950,7 +5950,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133152189</v>
+        <v>133152235</v>
       </c>
       <c r="B52" t="n">
         <v>91918</v>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>630270</v>
+        <v>630162</v>
       </c>
       <c r="R52" t="n">
-        <v>6967330</v>
+        <v>6967096</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>05:56</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>05:56</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6057,7 +6057,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133152235</v>
+        <v>133152194</v>
       </c>
       <c r="B53" t="n">
         <v>91918</v>
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>630162</v>
+        <v>630296</v>
       </c>
       <c r="R53" t="n">
-        <v>6967096</v>
+        <v>6967350</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6164,10 +6164,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133152194</v>
+        <v>133152209</v>
       </c>
       <c r="B54" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6175,21 +6175,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>630296</v>
+        <v>630184</v>
       </c>
       <c r="R54" t="n">
-        <v>6967350</v>
+        <v>6967242</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6271,32 +6271,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133152183</v>
+        <v>133152238</v>
       </c>
       <c r="B55" t="n">
-        <v>75433</v>
+        <v>83181</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6426</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6306,13 +6306,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630308</v>
+        <v>630180</v>
       </c>
       <c r="R55" t="n">
-        <v>6967259</v>
+        <v>6967130</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6378,10 +6378,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133152208</v>
+        <v>133152168</v>
       </c>
       <c r="B56" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6389,21 +6389,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6413,13 +6413,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630207</v>
+        <v>630316</v>
       </c>
       <c r="R56" t="n">
-        <v>6967295</v>
+        <v>6967112</v>
       </c>
       <c r="S56" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6485,10 +6485,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133152238</v>
+        <v>133152208</v>
       </c>
       <c r="B57" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6496,21 +6496,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6520,13 +6520,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>630180</v>
+        <v>630207</v>
       </c>
       <c r="R57" t="n">
-        <v>6967130</v>
+        <v>6967295</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6592,32 +6592,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133152168</v>
+        <v>133152183</v>
       </c>
       <c r="B58" t="n">
-        <v>79365</v>
+        <v>75433</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6627,13 +6627,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>630316</v>
+        <v>630308</v>
       </c>
       <c r="R58" t="n">
-        <v>6967112</v>
+        <v>6967259</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6699,10 +6699,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133152215</v>
+        <v>133152175</v>
       </c>
       <c r="B59" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6710,21 +6710,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6734,13 +6734,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630159</v>
+        <v>630308</v>
       </c>
       <c r="R59" t="n">
-        <v>6967229</v>
+        <v>6967163</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6806,10 +6806,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133152239</v>
+        <v>133152191</v>
       </c>
       <c r="B60" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6817,21 +6817,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>630255</v>
+        <v>630272</v>
       </c>
       <c r="R60" t="n">
-        <v>6967168</v>
+        <v>6967349</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6913,10 +6913,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133152227</v>
+        <v>133152180</v>
       </c>
       <c r="B61" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6924,21 +6924,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6948,13 +6948,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>630148</v>
+        <v>630315</v>
       </c>
       <c r="R61" t="n">
-        <v>6967117</v>
+        <v>6967166</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7020,7 +7020,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133152191</v>
+        <v>133152240</v>
       </c>
       <c r="B62" t="n">
         <v>79333</v>
@@ -7055,10 +7055,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630272</v>
+        <v>630263</v>
       </c>
       <c r="R62" t="n">
-        <v>6967349</v>
+        <v>6967142</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7127,10 +7127,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133152240</v>
+        <v>133152215</v>
       </c>
       <c r="B63" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7138,21 +7138,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>630263</v>
+        <v>630159</v>
       </c>
       <c r="R63" t="n">
-        <v>6967142</v>
+        <v>6967229</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7234,10 +7234,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133152180</v>
+        <v>133152239</v>
       </c>
       <c r="B64" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7245,21 +7245,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7269,13 +7269,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>630315</v>
+        <v>630255</v>
       </c>
       <c r="R64" t="n">
-        <v>6967166</v>
+        <v>6967168</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7341,10 +7341,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133152175</v>
+        <v>133152227</v>
       </c>
       <c r="B65" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7352,21 +7352,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7376,13 +7376,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>630308</v>
+        <v>630148</v>
       </c>
       <c r="R65" t="n">
-        <v>6967163</v>
+        <v>6967117</v>
       </c>
       <c r="S65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8102,32 +8102,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133152187</v>
+        <v>133152200</v>
       </c>
       <c r="B72" t="n">
-        <v>91881</v>
+        <v>83181</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>630305</v>
+        <v>630250</v>
       </c>
       <c r="R72" t="n">
-        <v>6967310</v>
+        <v>6967263</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8209,10 +8209,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133152200</v>
+        <v>133152223</v>
       </c>
       <c r="B73" t="n">
-        <v>83181</v>
+        <v>89300</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8220,21 +8220,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>630250</v>
+        <v>630159</v>
       </c>
       <c r="R73" t="n">
-        <v>6967263</v>
+        <v>6967161</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8316,32 +8316,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133152223</v>
+        <v>133152187</v>
       </c>
       <c r="B74" t="n">
-        <v>89300</v>
+        <v>91881</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>630159</v>
+        <v>630305</v>
       </c>
       <c r="R74" t="n">
-        <v>6967161</v>
+        <v>6967310</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8637,7 +8637,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133152182</v>
+        <v>133152181</v>
       </c>
       <c r="B77" t="n">
         <v>79333</v>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>630324</v>
+        <v>630334</v>
       </c>
       <c r="R77" t="n">
-        <v>6967248</v>
+        <v>6967171</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8744,7 +8744,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133152181</v>
+        <v>133152182</v>
       </c>
       <c r="B78" t="n">
         <v>79333</v>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>630334</v>
+        <v>630324</v>
       </c>
       <c r="R78" t="n">
-        <v>6967171</v>
+        <v>6967248</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8851,7 +8851,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133152170</v>
+        <v>133152169</v>
       </c>
       <c r="B79" t="n">
         <v>79333</v>
@@ -8886,10 +8886,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>630313</v>
+        <v>630316</v>
       </c>
       <c r="R79" t="n">
-        <v>6967117</v>
+        <v>6967112</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8958,7 +8958,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133152169</v>
+        <v>133152170</v>
       </c>
       <c r="B80" t="n">
         <v>79333</v>
@@ -8993,10 +8993,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>630316</v>
+        <v>630313</v>
       </c>
       <c r="R80" t="n">
-        <v>6967112</v>
+        <v>6967117</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9065,10 +9065,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133152228</v>
+        <v>133152207</v>
       </c>
       <c r="B81" t="n">
-        <v>79365</v>
+        <v>58119</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9076,34 +9076,46 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>630092</v>
+        <v>630231</v>
       </c>
       <c r="R81" t="n">
-        <v>6967142</v>
+        <v>6967249</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9135,7 +9147,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9145,7 +9157,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9172,10 +9184,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133152207</v>
+        <v>133152228</v>
       </c>
       <c r="B82" t="n">
-        <v>58119</v>
+        <v>79365</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9183,46 +9195,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>630231</v>
+        <v>630092</v>
       </c>
       <c r="R82" t="n">
-        <v>6967249</v>
+        <v>6967142</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9933,10 +9933,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133202134</v>
+        <v>133202147</v>
       </c>
       <c r="B89" t="n">
-        <v>83181</v>
+        <v>91932</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9944,21 +9944,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>630178</v>
+        <v>630094</v>
       </c>
       <c r="R89" t="n">
-        <v>6967146</v>
+        <v>6967070</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10003,7 +10003,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10040,10 +10040,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133202147</v>
+        <v>133202134</v>
       </c>
       <c r="B90" t="n">
-        <v>91932</v>
+        <v>83181</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10051,21 +10051,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>630094</v>
+        <v>630178</v>
       </c>
       <c r="R90" t="n">
-        <v>6967070</v>
+        <v>6967146</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10254,10 +10254,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133202155</v>
+        <v>133202148</v>
       </c>
       <c r="B92" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10265,21 +10265,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>630210</v>
+        <v>630099</v>
       </c>
       <c r="R92" t="n">
-        <v>6967196</v>
+        <v>6967120</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10361,32 +10361,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133202145</v>
+        <v>133202173</v>
       </c>
       <c r="B93" t="n">
-        <v>91932</v>
+        <v>92641</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>630093</v>
+        <v>630299</v>
       </c>
       <c r="R93" t="n">
-        <v>6967070</v>
+        <v>6967218</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10468,10 +10468,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133202168</v>
+        <v>133202145</v>
       </c>
       <c r="B94" t="n">
-        <v>83181</v>
+        <v>91932</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10479,21 +10479,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>630290</v>
+        <v>630093</v>
       </c>
       <c r="R94" t="n">
-        <v>6967317</v>
+        <v>6967070</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10575,32 +10575,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133202173</v>
+        <v>133202168</v>
       </c>
       <c r="B95" t="n">
-        <v>92641</v>
+        <v>83181</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>630299</v>
+        <v>630290</v>
       </c>
       <c r="R95" t="n">
-        <v>6967218</v>
+        <v>6967317</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10682,10 +10682,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133202148</v>
+        <v>133202155</v>
       </c>
       <c r="B96" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10693,21 +10693,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10717,10 +10717,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>630099</v>
+        <v>630210</v>
       </c>
       <c r="R96" t="n">
-        <v>6967120</v>
+        <v>6967196</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11003,32 +11003,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133202163</v>
+        <v>133202150</v>
       </c>
       <c r="B99" t="n">
-        <v>79333</v>
+        <v>79589</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11038,10 +11038,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>630344</v>
+        <v>630122</v>
       </c>
       <c r="R99" t="n">
-        <v>6967158</v>
+        <v>6967138</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11110,32 +11110,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133202150</v>
+        <v>133202163</v>
       </c>
       <c r="B100" t="n">
-        <v>79589</v>
+        <v>79333</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11145,10 +11145,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>630122</v>
+        <v>630344</v>
       </c>
       <c r="R100" t="n">
-        <v>6967138</v>
+        <v>6967158</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11217,45 +11217,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133202169</v>
+        <v>133202127</v>
       </c>
       <c r="B101" t="n">
-        <v>91932</v>
+        <v>5199</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1204</v>
+        <v>105930</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>630259</v>
+        <v>630318</v>
       </c>
       <c r="R101" t="n">
-        <v>6967344</v>
+        <v>6967099</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11287,7 +11296,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11297,7 +11306,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11306,6 +11320,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11431,54 +11446,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133202127</v>
+        <v>133202169</v>
       </c>
       <c r="B103" t="n">
-        <v>5199</v>
+        <v>91932</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>105930</v>
+        <v>1204</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>630318</v>
+        <v>630259</v>
       </c>
       <c r="R103" t="n">
-        <v>6967099</v>
+        <v>6967344</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11510,7 +11516,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11520,12 +11526,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11534,7 +11535,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133202152</v>
+        <v>133202171</v>
       </c>
       <c r="B104" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>630108</v>
+        <v>630271</v>
       </c>
       <c r="R104" t="n">
-        <v>6967186</v>
+        <v>6967309</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11660,10 +11660,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133202125</v>
+        <v>133202159</v>
       </c>
       <c r="B105" t="n">
-        <v>79365</v>
+        <v>91932</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11671,21 +11671,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>630331</v>
+        <v>630290</v>
       </c>
       <c r="R105" t="n">
-        <v>6967087</v>
+        <v>6967123</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11767,10 +11767,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133202159</v>
+        <v>133202152</v>
       </c>
       <c r="B106" t="n">
-        <v>91932</v>
+        <v>79365</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11778,21 +11778,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>630290</v>
+        <v>630108</v>
       </c>
       <c r="R106" t="n">
-        <v>6967123</v>
+        <v>6967186</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11874,10 +11874,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133202171</v>
+        <v>133202125</v>
       </c>
       <c r="B107" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>630271</v>
+        <v>630331</v>
       </c>
       <c r="R107" t="n">
-        <v>6967309</v>
+        <v>6967087</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133202161</v>
+        <v>133202139</v>
       </c>
       <c r="B109" t="n">
-        <v>91918</v>
+        <v>91932</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12099,21 +12099,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12123,10 +12123,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>630352</v>
+        <v>630104</v>
       </c>
       <c r="R109" t="n">
-        <v>6967119</v>
+        <v>6967096</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12195,10 +12195,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133202139</v>
+        <v>133202161</v>
       </c>
       <c r="B110" t="n">
-        <v>91932</v>
+        <v>91918</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12206,21 +12206,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12230,10 +12230,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>630104</v>
+        <v>630352</v>
       </c>
       <c r="R110" t="n">
-        <v>6967096</v>
+        <v>6967119</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12516,10 +12516,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133202158</v>
+        <v>133202132</v>
       </c>
       <c r="B113" t="n">
-        <v>83181</v>
+        <v>91932</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12527,21 +12527,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12551,10 +12551,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>630269</v>
+        <v>630247</v>
       </c>
       <c r="R113" t="n">
-        <v>6967158</v>
+        <v>6967157</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12623,10 +12623,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>133202132</v>
+        <v>133202158</v>
       </c>
       <c r="B114" t="n">
-        <v>91932</v>
+        <v>83181</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12634,21 +12634,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>630247</v>
+        <v>630269</v>
       </c>
       <c r="R114" t="n">
-        <v>6967157</v>
+        <v>6967158</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12693,7 +12693,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13051,53 +13051,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133202138</v>
+        <v>133202170</v>
       </c>
       <c r="B118" t="n">
-        <v>57136</v>
+        <v>79357</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>102612</v>
+        <v>6434</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>630143</v>
+        <v>630274</v>
       </c>
       <c r="R118" t="n">
-        <v>6967085</v>
+        <v>6967318</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13129,7 +13121,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13139,12 +13131,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Sannolikt tagen av en rovfågel.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13171,45 +13158,53 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133202170</v>
+        <v>133202138</v>
       </c>
       <c r="B119" t="n">
-        <v>79357</v>
+        <v>57136</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6434</v>
+        <v>102612</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>630274</v>
+        <v>630143</v>
       </c>
       <c r="R119" t="n">
-        <v>6967318</v>
+        <v>6967085</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13241,7 +13236,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13251,7 +13246,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Sannolikt tagen av en rovfågel.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13278,10 +13278,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133202141</v>
+        <v>133202164</v>
       </c>
       <c r="B120" t="n">
-        <v>89300</v>
+        <v>79333</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13289,21 +13289,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13313,10 +13313,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>630101</v>
+        <v>630329</v>
       </c>
       <c r="R120" t="n">
-        <v>6967092</v>
+        <v>6967216</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13348,7 +13348,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13385,10 +13385,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133202164</v>
+        <v>133202141</v>
       </c>
       <c r="B121" t="n">
-        <v>79333</v>
+        <v>89300</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13396,21 +13396,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13420,10 +13420,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>630329</v>
+        <v>630101</v>
       </c>
       <c r="R121" t="n">
-        <v>6967216</v>
+        <v>6967092</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13455,7 +13455,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13492,10 +13492,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133202149</v>
+        <v>133202136</v>
       </c>
       <c r="B122" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13503,21 +13503,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13527,10 +13527,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>630102</v>
+        <v>630184</v>
       </c>
       <c r="R122" t="n">
-        <v>6967124</v>
+        <v>6967090</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13599,10 +13599,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133202137</v>
+        <v>133202149</v>
       </c>
       <c r="B123" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13610,21 +13610,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13634,10 +13634,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>630158</v>
+        <v>630102</v>
       </c>
       <c r="R123" t="n">
-        <v>6967093</v>
+        <v>6967124</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13706,10 +13706,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133202136</v>
+        <v>133202137</v>
       </c>
       <c r="B124" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13717,21 +13717,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>630184</v>
+        <v>630158</v>
       </c>
       <c r="R124" t="n">
-        <v>6967090</v>
+        <v>6967093</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13813,10 +13813,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133202157</v>
+        <v>133202130</v>
       </c>
       <c r="B125" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13824,21 +13824,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>630257</v>
+        <v>630275</v>
       </c>
       <c r="R125" t="n">
-        <v>6967180</v>
+        <v>6967143</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13920,10 +13920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133202130</v>
+        <v>133202157</v>
       </c>
       <c r="B126" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13931,21 +13931,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>630275</v>
+        <v>630257</v>
       </c>
       <c r="R126" t="n">
-        <v>6967143</v>
+        <v>6967180</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14027,10 +14027,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133202131</v>
+        <v>133202133</v>
       </c>
       <c r="B127" t="n">
-        <v>83181</v>
+        <v>83315</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14038,21 +14038,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14062,10 +14062,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>630252</v>
+        <v>630226</v>
       </c>
       <c r="R127" t="n">
-        <v>6967151</v>
+        <v>6967128</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14097,7 +14097,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14134,10 +14134,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133202133</v>
+        <v>133202131</v>
       </c>
       <c r="B128" t="n">
-        <v>83315</v>
+        <v>83181</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14145,21 +14145,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14169,10 +14169,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>630226</v>
+        <v>630252</v>
       </c>
       <c r="R128" t="n">
-        <v>6967128</v>
+        <v>6967151</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15204,7 +15204,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133240009</v>
+        <v>133240034</v>
       </c>
       <c r="B138" t="n">
         <v>79333</v>
@@ -15239,10 +15239,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>630210</v>
+        <v>630375</v>
       </c>
       <c r="R138" t="n">
-        <v>6967061</v>
+        <v>6967109</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15311,7 +15311,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133240034</v>
+        <v>133240009</v>
       </c>
       <c r="B139" t="n">
         <v>79333</v>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>630375</v>
+        <v>630210</v>
       </c>
       <c r="R139" t="n">
-        <v>6967109</v>
+        <v>6967061</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15418,10 +15418,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133240010</v>
+        <v>133240037</v>
       </c>
       <c r="B140" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15429,21 +15429,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15453,10 +15453,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>630202</v>
+        <v>630379</v>
       </c>
       <c r="R140" t="n">
-        <v>6967062</v>
+        <v>6967127</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15525,7 +15525,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133240037</v>
+        <v>133240030</v>
       </c>
       <c r="B141" t="n">
         <v>79333</v>
@@ -15560,13 +15560,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>630379</v>
+        <v>630210</v>
       </c>
       <c r="R141" t="n">
-        <v>6967127</v>
+        <v>6967208</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15739,10 +15739,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133240030</v>
+        <v>133240010</v>
       </c>
       <c r="B143" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15750,21 +15750,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15774,13 +15774,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>630210</v>
+        <v>630202</v>
       </c>
       <c r="R143" t="n">
-        <v>6967208</v>
+        <v>6967062</v>
       </c>
       <c r="S143" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17365,10 +17365,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133240036</v>
+        <v>133240007</v>
       </c>
       <c r="B158" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17376,21 +17376,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17400,13 +17400,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>630368</v>
+        <v>630244</v>
       </c>
       <c r="R158" t="n">
-        <v>6967120</v>
+        <v>6967085</v>
       </c>
       <c r="S158" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17472,10 +17472,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>133240025</v>
+        <v>133240039</v>
       </c>
       <c r="B159" t="n">
-        <v>79333</v>
+        <v>89300</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17483,21 +17483,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17507,10 +17507,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>630103</v>
+        <v>630317</v>
       </c>
       <c r="R159" t="n">
-        <v>6967179</v>
+        <v>6967329</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17579,10 +17579,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133240007</v>
+        <v>133240036</v>
       </c>
       <c r="B160" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17590,21 +17590,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17614,13 +17614,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>630244</v>
+        <v>630368</v>
       </c>
       <c r="R160" t="n">
-        <v>6967085</v>
+        <v>6967120</v>
       </c>
       <c r="S160" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17686,10 +17686,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133240039</v>
+        <v>133240028</v>
       </c>
       <c r="B161" t="n">
-        <v>89300</v>
+        <v>79333</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17697,21 +17697,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17721,10 +17721,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>630317</v>
+        <v>630174</v>
       </c>
       <c r="R161" t="n">
-        <v>6967329</v>
+        <v>6967208</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17793,7 +17793,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133240028</v>
+        <v>133240025</v>
       </c>
       <c r="B162" t="n">
         <v>79333</v>
@@ -17828,10 +17828,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>630174</v>
+        <v>630103</v>
       </c>
       <c r="R162" t="n">
-        <v>6967208</v>
+        <v>6967179</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18114,10 +18114,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133240029</v>
+        <v>133240041</v>
       </c>
       <c r="B165" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18125,21 +18125,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18149,10 +18149,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>630179</v>
+        <v>630250</v>
       </c>
       <c r="R165" t="n">
-        <v>6967208</v>
+        <v>6967366</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18221,7 +18221,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133240041</v>
+        <v>133240018</v>
       </c>
       <c r="B166" t="n">
         <v>79333</v>
@@ -18256,10 +18256,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>630250</v>
+        <v>630148</v>
       </c>
       <c r="R166" t="n">
-        <v>6967366</v>
+        <v>6967065</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18328,10 +18328,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>133240018</v>
+        <v>133240029</v>
       </c>
       <c r="B167" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18339,21 +18339,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18363,10 +18363,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>630148</v>
+        <v>630179</v>
       </c>
       <c r="R167" t="n">
-        <v>6967065</v>
+        <v>6967208</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133152237</v>
+        <v>133152204</v>
       </c>
       <c r="B11" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630189</v>
+        <v>630265</v>
       </c>
       <c r="R11" t="n">
-        <v>6967121</v>
+        <v>6967240</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1638,12 +1638,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133152204</v>
+        <v>133152222</v>
       </c>
       <c r="B12" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630265</v>
+        <v>630156</v>
       </c>
       <c r="R12" t="n">
-        <v>6967240</v>
+        <v>6967155</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1740,7 +1735,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1750,7 +1745,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133152222</v>
+        <v>133152220</v>
       </c>
       <c r="B13" t="n">
-        <v>83181</v>
+        <v>91932</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630156</v>
+        <v>630135</v>
       </c>
       <c r="R13" t="n">
-        <v>6967155</v>
+        <v>6967160</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1847,7 +1842,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1857,7 +1852,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133152220</v>
+        <v>133152217</v>
       </c>
       <c r="B14" t="n">
-        <v>91932</v>
+        <v>92217</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1895,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1919,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630135</v>
+        <v>630130</v>
       </c>
       <c r="R14" t="n">
-        <v>6967160</v>
+        <v>6967217</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1954,7 +1949,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1964,7 +1959,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,10 +1986,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133152217</v>
+        <v>133152237</v>
       </c>
       <c r="B15" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2002,21 +1997,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630130</v>
+        <v>630189</v>
       </c>
       <c r="R15" t="n">
-        <v>6967217</v>
+        <v>6967121</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2061,7 +2056,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2071,7 +2066,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2954,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133152231</v>
+        <v>133152226</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630146</v>
+        <v>630154</v>
       </c>
       <c r="R24" t="n">
-        <v>6967080</v>
+        <v>6967129</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133152226</v>
+        <v>133152231</v>
       </c>
       <c r="B25" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630154</v>
+        <v>630146</v>
       </c>
       <c r="R25" t="n">
-        <v>6967129</v>
+        <v>6967080</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4452,10 +4452,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133152242</v>
+        <v>133152178</v>
       </c>
       <c r="B38" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4463,21 +4463,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4487,13 +4487,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630247</v>
+        <v>630300</v>
       </c>
       <c r="R38" t="n">
-        <v>6967129</v>
+        <v>6967148</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>05:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>05:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4559,10 +4559,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133152178</v>
+        <v>133152243</v>
       </c>
       <c r="B39" t="n">
-        <v>79365</v>
+        <v>83181</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,21 +4570,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4594,13 +4594,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630300</v>
+        <v>630223</v>
       </c>
       <c r="R39" t="n">
-        <v>6967148</v>
+        <v>6967132</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>05:16</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>05:16</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4666,7 +4666,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133152243</v>
+        <v>133152196</v>
       </c>
       <c r="B40" t="n">
         <v>83181</v>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630223</v>
+        <v>630299</v>
       </c>
       <c r="R40" t="n">
-        <v>6967132</v>
+        <v>6967344</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4773,7 +4773,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133152196</v>
+        <v>133152210</v>
       </c>
       <c r="B41" t="n">
         <v>83181</v>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>630299</v>
+        <v>630184</v>
       </c>
       <c r="R41" t="n">
-        <v>6967344</v>
+        <v>6967161</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4880,10 +4880,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133152210</v>
+        <v>133152242</v>
       </c>
       <c r="B42" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4891,21 +4891,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630184</v>
+        <v>630247</v>
       </c>
       <c r="R42" t="n">
-        <v>6967161</v>
+        <v>6967129</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5522,7 +5522,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133152198</v>
+        <v>133152159</v>
       </c>
       <c r="B48" t="n">
         <v>79365</v>
@@ -5557,13 +5557,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>630231</v>
+        <v>630350</v>
       </c>
       <c r="R48" t="n">
-        <v>6967393</v>
+        <v>6967090</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5629,7 +5629,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133152232</v>
+        <v>133152198</v>
       </c>
       <c r="B49" t="n">
         <v>79365</v>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>630147</v>
+        <v>630231</v>
       </c>
       <c r="R49" t="n">
-        <v>6967088</v>
+        <v>6967393</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5736,7 +5736,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133152159</v>
+        <v>133152232</v>
       </c>
       <c r="B50" t="n">
         <v>79365</v>
@@ -5771,13 +5771,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>630350</v>
+        <v>630147</v>
       </c>
       <c r="R50" t="n">
-        <v>6967090</v>
+        <v>6967088</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6271,10 +6271,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133152238</v>
+        <v>133152208</v>
       </c>
       <c r="B55" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6282,21 +6282,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6306,13 +6306,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630180</v>
+        <v>630207</v>
       </c>
       <c r="R55" t="n">
-        <v>6967130</v>
+        <v>6967295</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6378,32 +6378,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133152168</v>
+        <v>133152183</v>
       </c>
       <c r="B56" t="n">
-        <v>79365</v>
+        <v>75433</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6413,13 +6413,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630316</v>
+        <v>630308</v>
       </c>
       <c r="R56" t="n">
-        <v>6967112</v>
+        <v>6967259</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6485,10 +6485,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133152208</v>
+        <v>133152238</v>
       </c>
       <c r="B57" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6496,21 +6496,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6520,13 +6520,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>630207</v>
+        <v>630180</v>
       </c>
       <c r="R57" t="n">
-        <v>6967295</v>
+        <v>6967130</v>
       </c>
       <c r="S57" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6592,32 +6592,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133152183</v>
+        <v>133152168</v>
       </c>
       <c r="B58" t="n">
-        <v>75433</v>
+        <v>79365</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6627,13 +6627,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>630308</v>
+        <v>630316</v>
       </c>
       <c r="R58" t="n">
-        <v>6967259</v>
+        <v>6967112</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6699,10 +6699,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133152175</v>
+        <v>133152215</v>
       </c>
       <c r="B59" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6710,21 +6710,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6734,13 +6734,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630308</v>
+        <v>630159</v>
       </c>
       <c r="R59" t="n">
-        <v>6967163</v>
+        <v>6967229</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6806,10 +6806,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133152191</v>
+        <v>133152239</v>
       </c>
       <c r="B60" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6817,21 +6817,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>630272</v>
+        <v>630255</v>
       </c>
       <c r="R60" t="n">
-        <v>6967349</v>
+        <v>6967168</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6913,10 +6913,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133152180</v>
+        <v>133152227</v>
       </c>
       <c r="B61" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6924,21 +6924,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6948,13 +6948,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>630315</v>
+        <v>630148</v>
       </c>
       <c r="R61" t="n">
-        <v>6967166</v>
+        <v>6967117</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7020,7 +7020,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133152240</v>
+        <v>133152175</v>
       </c>
       <c r="B62" t="n">
         <v>79333</v>
@@ -7055,13 +7055,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630263</v>
+        <v>630308</v>
       </c>
       <c r="R62" t="n">
-        <v>6967142</v>
+        <v>6967163</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7127,10 +7127,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133152215</v>
+        <v>133152191</v>
       </c>
       <c r="B63" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7138,21 +7138,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>630159</v>
+        <v>630272</v>
       </c>
       <c r="R63" t="n">
-        <v>6967229</v>
+        <v>6967349</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7234,10 +7234,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133152239</v>
+        <v>133152180</v>
       </c>
       <c r="B64" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7245,21 +7245,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7269,13 +7269,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>630255</v>
+        <v>630315</v>
       </c>
       <c r="R64" t="n">
-        <v>6967168</v>
+        <v>6967166</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7341,10 +7341,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133152227</v>
+        <v>133152240</v>
       </c>
       <c r="B65" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7352,21 +7352,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>630148</v>
+        <v>630263</v>
       </c>
       <c r="R65" t="n">
-        <v>6967117</v>
+        <v>6967142</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8851,10 +8851,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133152169</v>
+        <v>133152228</v>
       </c>
       <c r="B79" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8862,21 +8862,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8886,10 +8886,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>630316</v>
+        <v>630092</v>
       </c>
       <c r="R79" t="n">
-        <v>6967112</v>
+        <v>6967142</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8958,7 +8958,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133152170</v>
+        <v>133152169</v>
       </c>
       <c r="B80" t="n">
         <v>79333</v>
@@ -8993,10 +8993,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>630313</v>
+        <v>630316</v>
       </c>
       <c r="R80" t="n">
-        <v>6967117</v>
+        <v>6967112</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9065,10 +9065,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133152207</v>
+        <v>133152170</v>
       </c>
       <c r="B81" t="n">
-        <v>58119</v>
+        <v>79333</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9076,46 +9076,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>630231</v>
+        <v>630313</v>
       </c>
       <c r="R81" t="n">
-        <v>6967249</v>
+        <v>6967117</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9147,7 +9135,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9157,7 +9145,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9184,10 +9172,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133152228</v>
+        <v>133152207</v>
       </c>
       <c r="B82" t="n">
-        <v>79365</v>
+        <v>58119</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9195,34 +9183,46 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>630092</v>
+        <v>630231</v>
       </c>
       <c r="R82" t="n">
-        <v>6967142</v>
+        <v>6967249</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9933,10 +9933,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133202147</v>
+        <v>133202134</v>
       </c>
       <c r="B89" t="n">
-        <v>91932</v>
+        <v>83181</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9944,21 +9944,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>630094</v>
+        <v>630178</v>
       </c>
       <c r="R89" t="n">
-        <v>6967070</v>
+        <v>6967146</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10003,7 +10003,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10040,10 +10040,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133202134</v>
+        <v>133202147</v>
       </c>
       <c r="B90" t="n">
-        <v>83181</v>
+        <v>91932</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10051,21 +10051,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>630178</v>
+        <v>630094</v>
       </c>
       <c r="R90" t="n">
-        <v>6967146</v>
+        <v>6967070</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11217,54 +11217,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133202127</v>
+        <v>133202169</v>
       </c>
       <c r="B101" t="n">
-        <v>5199</v>
+        <v>91932</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>105930</v>
+        <v>1204</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>630318</v>
+        <v>630259</v>
       </c>
       <c r="R101" t="n">
-        <v>6967099</v>
+        <v>6967344</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11296,7 +11287,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11306,12 +11297,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11320,7 +11306,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11446,45 +11431,54 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133202169</v>
+        <v>133202127</v>
       </c>
       <c r="B103" t="n">
-        <v>91932</v>
+        <v>5199</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1204</v>
+        <v>105930</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>630259</v>
+        <v>630318</v>
       </c>
       <c r="R103" t="n">
-        <v>6967344</v>
+        <v>6967099</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11516,7 +11510,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11526,7 +11520,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11535,6 +11534,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133202171</v>
+        <v>133202152</v>
       </c>
       <c r="B104" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>630271</v>
+        <v>630108</v>
       </c>
       <c r="R104" t="n">
-        <v>6967309</v>
+        <v>6967186</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11660,10 +11660,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133202159</v>
+        <v>133202125</v>
       </c>
       <c r="B105" t="n">
-        <v>91932</v>
+        <v>79365</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11671,21 +11671,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>630290</v>
+        <v>630331</v>
       </c>
       <c r="R105" t="n">
-        <v>6967123</v>
+        <v>6967087</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11767,10 +11767,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133202152</v>
+        <v>133202171</v>
       </c>
       <c r="B106" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11778,21 +11778,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>630108</v>
+        <v>630271</v>
       </c>
       <c r="R106" t="n">
-        <v>6967186</v>
+        <v>6967309</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11874,10 +11874,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133202125</v>
+        <v>133202159</v>
       </c>
       <c r="B107" t="n">
-        <v>79365</v>
+        <v>91932</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>630331</v>
+        <v>630290</v>
       </c>
       <c r="R107" t="n">
-        <v>6967087</v>
+        <v>6967123</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133202139</v>
+        <v>133202161</v>
       </c>
       <c r="B109" t="n">
-        <v>91932</v>
+        <v>91918</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12099,21 +12099,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12123,10 +12123,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>630104</v>
+        <v>630352</v>
       </c>
       <c r="R109" t="n">
-        <v>6967096</v>
+        <v>6967119</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12195,10 +12195,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133202161</v>
+        <v>133202139</v>
       </c>
       <c r="B110" t="n">
-        <v>91918</v>
+        <v>91932</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12206,21 +12206,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12230,10 +12230,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>630352</v>
+        <v>630104</v>
       </c>
       <c r="R110" t="n">
-        <v>6967119</v>
+        <v>6967096</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12516,10 +12516,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133202132</v>
+        <v>133202158</v>
       </c>
       <c r="B113" t="n">
-        <v>91932</v>
+        <v>83181</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12527,21 +12527,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12551,10 +12551,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>630247</v>
+        <v>630269</v>
       </c>
       <c r="R113" t="n">
-        <v>6967157</v>
+        <v>6967158</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12623,10 +12623,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>133202158</v>
+        <v>133202132</v>
       </c>
       <c r="B114" t="n">
-        <v>83181</v>
+        <v>91932</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12634,21 +12634,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>630269</v>
+        <v>630247</v>
       </c>
       <c r="R114" t="n">
-        <v>6967158</v>
+        <v>6967157</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12693,7 +12693,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12837,10 +12837,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>133202144</v>
+        <v>133202153</v>
       </c>
       <c r="B116" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12848,21 +12848,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12872,10 +12872,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>630098</v>
+        <v>630160</v>
       </c>
       <c r="R116" t="n">
-        <v>6967075</v>
+        <v>6967163</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12917,7 +12917,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12944,10 +12944,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>133202153</v>
+        <v>133202144</v>
       </c>
       <c r="B117" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12955,21 +12955,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>630160</v>
+        <v>630098</v>
       </c>
       <c r="R117" t="n">
-        <v>6967163</v>
+        <v>6967075</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13278,10 +13278,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133202164</v>
+        <v>133202141</v>
       </c>
       <c r="B120" t="n">
-        <v>79333</v>
+        <v>89300</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13289,21 +13289,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13313,10 +13313,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>630329</v>
+        <v>630101</v>
       </c>
       <c r="R120" t="n">
-        <v>6967216</v>
+        <v>6967092</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13348,7 +13348,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13385,10 +13385,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133202141</v>
+        <v>133202164</v>
       </c>
       <c r="B121" t="n">
-        <v>89300</v>
+        <v>79333</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13396,21 +13396,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13420,10 +13420,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>630101</v>
+        <v>630329</v>
       </c>
       <c r="R121" t="n">
-        <v>6967092</v>
+        <v>6967216</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13455,7 +13455,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13492,10 +13492,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133202136</v>
+        <v>133202149</v>
       </c>
       <c r="B122" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13503,21 +13503,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13527,10 +13527,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>630184</v>
+        <v>630102</v>
       </c>
       <c r="R122" t="n">
-        <v>6967090</v>
+        <v>6967124</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13599,10 +13599,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133202149</v>
+        <v>133202137</v>
       </c>
       <c r="B123" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13610,21 +13610,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13634,10 +13634,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>630102</v>
+        <v>630158</v>
       </c>
       <c r="R123" t="n">
-        <v>6967124</v>
+        <v>6967093</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13706,10 +13706,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133202137</v>
+        <v>133202136</v>
       </c>
       <c r="B124" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13717,21 +13717,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>630158</v>
+        <v>630184</v>
       </c>
       <c r="R124" t="n">
-        <v>6967093</v>
+        <v>6967090</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15204,7 +15204,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133240034</v>
+        <v>133240009</v>
       </c>
       <c r="B138" t="n">
         <v>79333</v>
@@ -15239,10 +15239,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>630375</v>
+        <v>630210</v>
       </c>
       <c r="R138" t="n">
-        <v>6967109</v>
+        <v>6967061</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15311,7 +15311,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133240009</v>
+        <v>133240034</v>
       </c>
       <c r="B139" t="n">
         <v>79333</v>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>630210</v>
+        <v>630375</v>
       </c>
       <c r="R139" t="n">
-        <v>6967061</v>
+        <v>6967109</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15418,10 +15418,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133240037</v>
+        <v>133240010</v>
       </c>
       <c r="B140" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15429,21 +15429,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15453,10 +15453,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>630379</v>
+        <v>630202</v>
       </c>
       <c r="R140" t="n">
-        <v>6967127</v>
+        <v>6967062</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15525,10 +15525,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133240030</v>
+        <v>133240004</v>
       </c>
       <c r="B141" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15536,21 +15536,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15560,13 +15560,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>630210</v>
+        <v>630287</v>
       </c>
       <c r="R141" t="n">
-        <v>6967208</v>
+        <v>6967110</v>
       </c>
       <c r="S141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15632,10 +15632,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133240004</v>
+        <v>133240037</v>
       </c>
       <c r="B142" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15643,21 +15643,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15667,10 +15667,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>630287</v>
+        <v>630379</v>
       </c>
       <c r="R142" t="n">
-        <v>6967110</v>
+        <v>6967127</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15739,10 +15739,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133240010</v>
+        <v>133240030</v>
       </c>
       <c r="B143" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15750,21 +15750,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15774,13 +15774,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>630202</v>
+        <v>630210</v>
       </c>
       <c r="R143" t="n">
-        <v>6967062</v>
+        <v>6967208</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17365,10 +17365,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133240007</v>
+        <v>133240039</v>
       </c>
       <c r="B158" t="n">
-        <v>79365</v>
+        <v>89300</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17376,21 +17376,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17400,13 +17400,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>630244</v>
+        <v>630317</v>
       </c>
       <c r="R158" t="n">
-        <v>6967085</v>
+        <v>6967329</v>
       </c>
       <c r="S158" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17472,10 +17472,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>133240039</v>
+        <v>133240007</v>
       </c>
       <c r="B159" t="n">
-        <v>89300</v>
+        <v>79365</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17483,21 +17483,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17507,13 +17507,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>630317</v>
+        <v>630244</v>
       </c>
       <c r="R159" t="n">
-        <v>6967329</v>
+        <v>6967085</v>
       </c>
       <c r="S159" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18114,7 +18114,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133240041</v>
+        <v>133240018</v>
       </c>
       <c r="B165" t="n">
         <v>79333</v>
@@ -18149,10 +18149,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>630250</v>
+        <v>630148</v>
       </c>
       <c r="R165" t="n">
-        <v>6967366</v>
+        <v>6967065</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18221,7 +18221,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133240018</v>
+        <v>133240041</v>
       </c>
       <c r="B166" t="n">
         <v>79333</v>
@@ -18256,10 +18256,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>630148</v>
+        <v>630250</v>
       </c>
       <c r="R166" t="n">
-        <v>6967065</v>
+        <v>6967366</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD166" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -2954,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133152226</v>
+        <v>133152231</v>
       </c>
       <c r="B24" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630154</v>
+        <v>630146</v>
       </c>
       <c r="R24" t="n">
-        <v>6967129</v>
+        <v>6967080</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133152231</v>
+        <v>133152226</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630146</v>
+        <v>630154</v>
       </c>
       <c r="R25" t="n">
-        <v>6967080</v>
+        <v>6967129</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4987,32 +4987,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133152201</v>
+        <v>133152195</v>
       </c>
       <c r="B43" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630261</v>
+        <v>630297</v>
       </c>
       <c r="R43" t="n">
-        <v>6967251</v>
+        <v>6967347</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5094,32 +5094,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133152195</v>
+        <v>133152216</v>
       </c>
       <c r="B44" t="n">
-        <v>75433</v>
+        <v>79333</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630297</v>
+        <v>630149</v>
       </c>
       <c r="R44" t="n">
-        <v>6967347</v>
+        <v>6967241</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5201,32 +5201,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133152216</v>
+        <v>133152197</v>
       </c>
       <c r="B45" t="n">
-        <v>79333</v>
+        <v>75433</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630149</v>
+        <v>630298</v>
       </c>
       <c r="R45" t="n">
-        <v>6967241</v>
+        <v>6967342</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5308,32 +5308,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133152197</v>
+        <v>133152201</v>
       </c>
       <c r="B46" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5343,10 +5343,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630298</v>
+        <v>630261</v>
       </c>
       <c r="R46" t="n">
-        <v>6967342</v>
+        <v>6967251</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6271,10 +6271,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133152208</v>
+        <v>133152238</v>
       </c>
       <c r="B55" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6282,21 +6282,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6306,13 +6306,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630207</v>
+        <v>630180</v>
       </c>
       <c r="R55" t="n">
-        <v>6967295</v>
+        <v>6967130</v>
       </c>
       <c r="S55" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6378,32 +6378,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133152183</v>
+        <v>133152168</v>
       </c>
       <c r="B56" t="n">
-        <v>75433</v>
+        <v>79365</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6413,13 +6413,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630308</v>
+        <v>630316</v>
       </c>
       <c r="R56" t="n">
-        <v>6967259</v>
+        <v>6967112</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6485,10 +6485,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133152238</v>
+        <v>133152208</v>
       </c>
       <c r="B57" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6496,21 +6496,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6520,13 +6520,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>630180</v>
+        <v>630207</v>
       </c>
       <c r="R57" t="n">
-        <v>6967130</v>
+        <v>6967295</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6592,32 +6592,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133152168</v>
+        <v>133152183</v>
       </c>
       <c r="B58" t="n">
-        <v>79365</v>
+        <v>75433</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6627,13 +6627,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>630316</v>
+        <v>630308</v>
       </c>
       <c r="R58" t="n">
-        <v>6967112</v>
+        <v>6967259</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8102,32 +8102,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133152200</v>
+        <v>133152187</v>
       </c>
       <c r="B72" t="n">
-        <v>83181</v>
+        <v>91881</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>630250</v>
+        <v>630305</v>
       </c>
       <c r="R72" t="n">
-        <v>6967263</v>
+        <v>6967310</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8209,10 +8209,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133152223</v>
+        <v>133152200</v>
       </c>
       <c r="B73" t="n">
-        <v>89300</v>
+        <v>83181</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8220,21 +8220,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>630159</v>
+        <v>630250</v>
       </c>
       <c r="R73" t="n">
-        <v>6967161</v>
+        <v>6967263</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8316,32 +8316,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133152187</v>
+        <v>133152223</v>
       </c>
       <c r="B74" t="n">
-        <v>91881</v>
+        <v>89300</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>630305</v>
+        <v>630159</v>
       </c>
       <c r="R74" t="n">
-        <v>6967310</v>
+        <v>6967161</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9719,10 +9719,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133202128</v>
+        <v>133202135</v>
       </c>
       <c r="B87" t="n">
-        <v>79365</v>
+        <v>83181</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9730,21 +9730,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9754,10 +9754,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>630304</v>
+        <v>630165</v>
       </c>
       <c r="R87" t="n">
-        <v>6967096</v>
+        <v>6967141</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9826,10 +9826,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133202135</v>
+        <v>133202128</v>
       </c>
       <c r="B88" t="n">
-        <v>83181</v>
+        <v>79365</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9837,21 +9837,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9861,10 +9861,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>630165</v>
+        <v>630304</v>
       </c>
       <c r="R88" t="n">
-        <v>6967141</v>
+        <v>6967096</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10254,10 +10254,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133202148</v>
+        <v>133202145</v>
       </c>
       <c r="B92" t="n">
-        <v>79333</v>
+        <v>91932</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10265,21 +10265,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>630099</v>
+        <v>630093</v>
       </c>
       <c r="R92" t="n">
-        <v>6967120</v>
+        <v>6967070</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10361,32 +10361,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133202173</v>
+        <v>133202168</v>
       </c>
       <c r="B93" t="n">
-        <v>92641</v>
+        <v>83181</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>630299</v>
+        <v>630290</v>
       </c>
       <c r="R93" t="n">
-        <v>6967218</v>
+        <v>6967317</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10468,10 +10468,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133202145</v>
+        <v>133202155</v>
       </c>
       <c r="B94" t="n">
-        <v>91932</v>
+        <v>91918</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10479,21 +10479,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>630093</v>
+        <v>630210</v>
       </c>
       <c r="R94" t="n">
-        <v>6967070</v>
+        <v>6967196</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10575,10 +10575,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133202168</v>
+        <v>133202148</v>
       </c>
       <c r="B95" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10586,21 +10586,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>630290</v>
+        <v>630099</v>
       </c>
       <c r="R95" t="n">
-        <v>6967317</v>
+        <v>6967120</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10682,32 +10682,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133202155</v>
+        <v>133202173</v>
       </c>
       <c r="B96" t="n">
-        <v>91918</v>
+        <v>92641</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10717,10 +10717,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>630210</v>
+        <v>630299</v>
       </c>
       <c r="R96" t="n">
-        <v>6967196</v>
+        <v>6967218</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11217,45 +11217,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133202169</v>
+        <v>133202127</v>
       </c>
       <c r="B101" t="n">
-        <v>91932</v>
+        <v>5199</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1204</v>
+        <v>105930</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>630259</v>
+        <v>630318</v>
       </c>
       <c r="R101" t="n">
-        <v>6967344</v>
+        <v>6967099</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11287,7 +11296,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11297,7 +11306,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11306,6 +11320,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11324,10 +11339,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133202151</v>
+        <v>133202169</v>
       </c>
       <c r="B102" t="n">
-        <v>83181</v>
+        <v>91932</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11335,21 +11350,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11359,10 +11374,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>630118</v>
+        <v>630259</v>
       </c>
       <c r="R102" t="n">
-        <v>6967158</v>
+        <v>6967344</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11394,7 +11409,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11404,7 +11419,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11431,54 +11446,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133202127</v>
+        <v>133202151</v>
       </c>
       <c r="B103" t="n">
-        <v>5199</v>
+        <v>83181</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>105930</v>
+        <v>1312</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>630318</v>
+        <v>630118</v>
       </c>
       <c r="R103" t="n">
-        <v>6967099</v>
+        <v>6967158</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11510,7 +11516,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11520,12 +11526,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11534,7 +11535,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -15418,10 +15418,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133240010</v>
+        <v>133240004</v>
       </c>
       <c r="B140" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15429,21 +15429,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15453,10 +15453,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>630202</v>
+        <v>630287</v>
       </c>
       <c r="R140" t="n">
-        <v>6967062</v>
+        <v>6967110</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15525,10 +15525,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133240004</v>
+        <v>133240037</v>
       </c>
       <c r="B141" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15536,21 +15536,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15560,10 +15560,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>630287</v>
+        <v>630379</v>
       </c>
       <c r="R141" t="n">
-        <v>6967110</v>
+        <v>6967127</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15632,7 +15632,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133240037</v>
+        <v>133240030</v>
       </c>
       <c r="B142" t="n">
         <v>79333</v>
@@ -15667,13 +15667,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>630379</v>
+        <v>630210</v>
       </c>
       <c r="R142" t="n">
-        <v>6967127</v>
+        <v>6967208</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15739,10 +15739,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133240030</v>
+        <v>133240010</v>
       </c>
       <c r="B143" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15750,21 +15750,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15774,13 +15774,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>630210</v>
+        <v>630202</v>
       </c>
       <c r="R143" t="n">
-        <v>6967208</v>
+        <v>6967062</v>
       </c>
       <c r="S143" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17044,10 +17044,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133240040</v>
+        <v>133240043</v>
       </c>
       <c r="B155" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17055,21 +17055,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17079,10 +17079,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>630295</v>
+        <v>630242</v>
       </c>
       <c r="R155" t="n">
-        <v>6967374</v>
+        <v>6967369</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17151,7 +17151,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133240043</v>
+        <v>133240013</v>
       </c>
       <c r="B156" t="n">
         <v>79333</v>
@@ -17186,10 +17186,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>630242</v>
+        <v>630166</v>
       </c>
       <c r="R156" t="n">
-        <v>6967369</v>
+        <v>6967049</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -17221,7 +17221,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17258,10 +17258,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133240013</v>
+        <v>133240040</v>
       </c>
       <c r="B157" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17269,21 +17269,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17293,10 +17293,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>630166</v>
+        <v>630295</v>
       </c>
       <c r="R157" t="n">
-        <v>6967049</v>
+        <v>6967374</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -17328,7 +17328,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17338,7 +17338,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD157" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133152204</v>
+        <v>133152237</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630265</v>
+        <v>630189</v>
       </c>
       <c r="R11" t="n">
-        <v>6967240</v>
+        <v>6967121</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1638,7 +1638,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1879,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133152217</v>
+        <v>133152204</v>
       </c>
       <c r="B14" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1895,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630130</v>
+        <v>630265</v>
       </c>
       <c r="R14" t="n">
-        <v>6967217</v>
+        <v>6967240</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1949,7 +1954,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1959,7 +1964,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1986,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133152237</v>
+        <v>133152217</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,21 +2002,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630189</v>
+        <v>630130</v>
       </c>
       <c r="R15" t="n">
-        <v>6967121</v>
+        <v>6967217</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2056,7 +2061,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2066,12 +2071,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133152174</v>
+        <v>133152163</v>
       </c>
       <c r="B19" t="n">
-        <v>83181</v>
+        <v>79365</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630286</v>
+        <v>630334</v>
       </c>
       <c r="R19" t="n">
-        <v>6967149</v>
+        <v>6967097</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133152163</v>
+        <v>133152218</v>
       </c>
       <c r="B20" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630334</v>
+        <v>630124</v>
       </c>
       <c r="R20" t="n">
-        <v>6967097</v>
+        <v>6967208</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2633,32 +2633,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133152218</v>
+        <v>133152185</v>
       </c>
       <c r="B21" t="n">
-        <v>92217</v>
+        <v>91881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630124</v>
+        <v>630303</v>
       </c>
       <c r="R21" t="n">
-        <v>6967208</v>
+        <v>6967279</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2740,32 +2740,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133152185</v>
+        <v>133152174</v>
       </c>
       <c r="B22" t="n">
-        <v>91881</v>
+        <v>83181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630303</v>
+        <v>630286</v>
       </c>
       <c r="R22" t="n">
-        <v>6967279</v>
+        <v>6967149</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>05:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>05:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2954,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133152231</v>
+        <v>133152226</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630146</v>
+        <v>630154</v>
       </c>
       <c r="R24" t="n">
-        <v>6967080</v>
+        <v>6967129</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133152226</v>
+        <v>133152231</v>
       </c>
       <c r="B25" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630154</v>
+        <v>630146</v>
       </c>
       <c r="R25" t="n">
-        <v>6967129</v>
+        <v>6967080</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3489,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133152188</v>
+        <v>133152173</v>
       </c>
       <c r="B29" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,21 +3500,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630274</v>
+        <v>630300</v>
       </c>
       <c r="R29" t="n">
-        <v>6967324</v>
+        <v>6967133</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3596,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133152184</v>
+        <v>133152188</v>
       </c>
       <c r="B30" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630304</v>
+        <v>630274</v>
       </c>
       <c r="R30" t="n">
-        <v>6967273</v>
+        <v>6967324</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3703,10 +3703,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133152173</v>
+        <v>133152184</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630300</v>
+        <v>630304</v>
       </c>
       <c r="R31" t="n">
-        <v>6967133</v>
+        <v>6967273</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3810,10 +3810,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133152203</v>
+        <v>133152193</v>
       </c>
       <c r="B32" t="n">
-        <v>91932</v>
+        <v>83181</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3821,21 +3821,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630258</v>
+        <v>630280</v>
       </c>
       <c r="R32" t="n">
-        <v>6967247</v>
+        <v>6967356</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3917,10 +3917,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133152193</v>
+        <v>133152203</v>
       </c>
       <c r="B33" t="n">
-        <v>83181</v>
+        <v>91932</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3928,21 +3928,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630280</v>
+        <v>630258</v>
       </c>
       <c r="R33" t="n">
-        <v>6967356</v>
+        <v>6967247</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4024,10 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133152234</v>
+        <v>133152206</v>
       </c>
       <c r="B34" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630161</v>
+        <v>630256</v>
       </c>
       <c r="R34" t="n">
-        <v>6967098</v>
+        <v>6967220</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4131,7 +4131,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133152164</v>
+        <v>133152234</v>
       </c>
       <c r="B35" t="n">
         <v>79365</v>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630325</v>
+        <v>630161</v>
       </c>
       <c r="R35" t="n">
-        <v>6967107</v>
+        <v>6967098</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4238,7 +4238,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133152167</v>
+        <v>133152164</v>
       </c>
       <c r="B36" t="n">
         <v>79365</v>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630318</v>
+        <v>630325</v>
       </c>
       <c r="R36" t="n">
-        <v>6967112</v>
+        <v>6967107</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>04:51</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>04:51</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4345,10 +4345,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133152206</v>
+        <v>133152167</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4356,21 +4356,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630256</v>
+        <v>630318</v>
       </c>
       <c r="R37" t="n">
-        <v>6967220</v>
+        <v>6967112</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4452,10 +4452,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133152178</v>
+        <v>133152196</v>
       </c>
       <c r="B38" t="n">
-        <v>79365</v>
+        <v>83181</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4463,21 +4463,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4487,13 +4487,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630300</v>
+        <v>630299</v>
       </c>
       <c r="R38" t="n">
-        <v>6967148</v>
+        <v>6967344</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>05:16</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>05:16</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4666,10 +4666,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133152196</v>
+        <v>133152242</v>
       </c>
       <c r="B40" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630299</v>
+        <v>630247</v>
       </c>
       <c r="R40" t="n">
-        <v>6967344</v>
+        <v>6967129</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4880,10 +4880,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133152242</v>
+        <v>133152178</v>
       </c>
       <c r="B42" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4891,21 +4891,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4915,13 +4915,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630247</v>
+        <v>630300</v>
       </c>
       <c r="R42" t="n">
-        <v>6967129</v>
+        <v>6967148</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>05:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>05:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5201,32 +5201,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133152197</v>
+        <v>133152201</v>
       </c>
       <c r="B45" t="n">
-        <v>75433</v>
+        <v>91918</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630298</v>
+        <v>630261</v>
       </c>
       <c r="R45" t="n">
-        <v>6967342</v>
+        <v>6967251</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5308,32 +5308,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133152201</v>
+        <v>133152197</v>
       </c>
       <c r="B46" t="n">
-        <v>91918</v>
+        <v>75433</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5343,10 +5343,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630261</v>
+        <v>630298</v>
       </c>
       <c r="R46" t="n">
-        <v>6967251</v>
+        <v>6967342</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5950,10 +5950,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133152235</v>
+        <v>133152209</v>
       </c>
       <c r="B52" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5961,21 +5961,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>630162</v>
+        <v>630184</v>
       </c>
       <c r="R52" t="n">
-        <v>6967096</v>
+        <v>6967242</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6057,7 +6057,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133152194</v>
+        <v>133152235</v>
       </c>
       <c r="B53" t="n">
         <v>91918</v>
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>630296</v>
+        <v>630162</v>
       </c>
       <c r="R53" t="n">
-        <v>6967350</v>
+        <v>6967096</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6164,10 +6164,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133152209</v>
+        <v>133152194</v>
       </c>
       <c r="B54" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6175,21 +6175,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>630184</v>
+        <v>630296</v>
       </c>
       <c r="R54" t="n">
-        <v>6967242</v>
+        <v>6967350</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6271,32 +6271,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133152238</v>
+        <v>133152183</v>
       </c>
       <c r="B55" t="n">
-        <v>83181</v>
+        <v>75433</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>6426</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6306,13 +6306,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630180</v>
+        <v>630308</v>
       </c>
       <c r="R55" t="n">
-        <v>6967130</v>
+        <v>6967259</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6378,10 +6378,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133152168</v>
+        <v>133152208</v>
       </c>
       <c r="B56" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6389,21 +6389,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6413,13 +6413,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630316</v>
+        <v>630207</v>
       </c>
       <c r="R56" t="n">
-        <v>6967112</v>
+        <v>6967295</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6485,10 +6485,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133152208</v>
+        <v>133152238</v>
       </c>
       <c r="B57" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6496,21 +6496,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6520,13 +6520,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>630207</v>
+        <v>630180</v>
       </c>
       <c r="R57" t="n">
-        <v>6967295</v>
+        <v>6967130</v>
       </c>
       <c r="S57" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6592,32 +6592,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133152183</v>
+        <v>133152168</v>
       </c>
       <c r="B58" t="n">
-        <v>75433</v>
+        <v>79365</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6627,13 +6627,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>630308</v>
+        <v>630316</v>
       </c>
       <c r="R58" t="n">
-        <v>6967259</v>
+        <v>6967112</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6699,10 +6699,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133152215</v>
+        <v>133152227</v>
       </c>
       <c r="B59" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6710,21 +6710,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630159</v>
+        <v>630148</v>
       </c>
       <c r="R59" t="n">
-        <v>6967229</v>
+        <v>6967117</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6806,10 +6806,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133152239</v>
+        <v>133152191</v>
       </c>
       <c r="B60" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6817,21 +6817,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>630255</v>
+        <v>630272</v>
       </c>
       <c r="R60" t="n">
-        <v>6967168</v>
+        <v>6967349</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6913,10 +6913,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133152227</v>
+        <v>133152240</v>
       </c>
       <c r="B61" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6924,21 +6924,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>630148</v>
+        <v>630263</v>
       </c>
       <c r="R61" t="n">
-        <v>6967117</v>
+        <v>6967142</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7020,10 +7020,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133152175</v>
+        <v>133152215</v>
       </c>
       <c r="B62" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7031,21 +7031,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7055,13 +7055,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630308</v>
+        <v>630159</v>
       </c>
       <c r="R62" t="n">
-        <v>6967163</v>
+        <v>6967229</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7127,7 +7127,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133152191</v>
+        <v>133152180</v>
       </c>
       <c r="B63" t="n">
         <v>79333</v>
@@ -7162,13 +7162,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>630272</v>
+        <v>630315</v>
       </c>
       <c r="R63" t="n">
-        <v>6967349</v>
+        <v>6967166</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7234,10 +7234,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133152180</v>
+        <v>133152239</v>
       </c>
       <c r="B64" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7245,21 +7245,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7269,13 +7269,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>630315</v>
+        <v>630255</v>
       </c>
       <c r="R64" t="n">
-        <v>6967166</v>
+        <v>6967168</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7341,7 +7341,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133152240</v>
+        <v>133152175</v>
       </c>
       <c r="B65" t="n">
         <v>79333</v>
@@ -7376,13 +7376,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>630263</v>
+        <v>630308</v>
       </c>
       <c r="R65" t="n">
-        <v>6967142</v>
+        <v>6967163</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7448,10 +7448,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133152199</v>
+        <v>133152177</v>
       </c>
       <c r="B66" t="n">
-        <v>79365</v>
+        <v>58119</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7459,34 +7459,46 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>630251</v>
+        <v>630306</v>
       </c>
       <c r="R66" t="n">
-        <v>6967351</v>
+        <v>6967160</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7518,7 +7530,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>05:13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7528,7 +7540,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>05:13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7555,10 +7567,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133152219</v>
+        <v>133152190</v>
       </c>
       <c r="B67" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7566,21 +7578,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7590,10 +7602,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>630121</v>
+        <v>630270</v>
       </c>
       <c r="R67" t="n">
-        <v>6967203</v>
+        <v>6967330</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7625,7 +7637,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7635,7 +7647,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7662,10 +7674,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133152190</v>
+        <v>133152199</v>
       </c>
       <c r="B68" t="n">
-        <v>83181</v>
+        <v>79365</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7673,21 +7685,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7697,10 +7709,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>630270</v>
+        <v>630251</v>
       </c>
       <c r="R68" t="n">
-        <v>6967330</v>
+        <v>6967351</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7732,7 +7744,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7742,7 +7754,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7769,10 +7781,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133152177</v>
+        <v>133152219</v>
       </c>
       <c r="B69" t="n">
-        <v>58119</v>
+        <v>91918</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7780,46 +7792,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630306</v>
+        <v>630121</v>
       </c>
       <c r="R69" t="n">
-        <v>6967160</v>
+        <v>6967203</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>05:13</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>05:13</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8102,32 +8102,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133152187</v>
+        <v>133152223</v>
       </c>
       <c r="B72" t="n">
-        <v>91881</v>
+        <v>89300</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>630305</v>
+        <v>630159</v>
       </c>
       <c r="R72" t="n">
-        <v>6967310</v>
+        <v>6967161</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8209,32 +8209,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133152200</v>
+        <v>133152187</v>
       </c>
       <c r="B73" t="n">
-        <v>83181</v>
+        <v>91881</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>630250</v>
+        <v>630305</v>
       </c>
       <c r="R73" t="n">
-        <v>6967263</v>
+        <v>6967310</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8316,10 +8316,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133152223</v>
+        <v>133152200</v>
       </c>
       <c r="B74" t="n">
-        <v>89300</v>
+        <v>83181</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8327,21 +8327,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>630159</v>
+        <v>630250</v>
       </c>
       <c r="R74" t="n">
-        <v>6967161</v>
+        <v>6967263</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8637,7 +8637,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133152181</v>
+        <v>133152182</v>
       </c>
       <c r="B77" t="n">
         <v>79333</v>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>630334</v>
+        <v>630324</v>
       </c>
       <c r="R77" t="n">
-        <v>6967171</v>
+        <v>6967248</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8744,7 +8744,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133152182</v>
+        <v>133152181</v>
       </c>
       <c r="B78" t="n">
         <v>79333</v>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>630324</v>
+        <v>630334</v>
       </c>
       <c r="R78" t="n">
-        <v>6967248</v>
+        <v>6967171</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8958,10 +8958,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133152169</v>
+        <v>133152207</v>
       </c>
       <c r="B80" t="n">
-        <v>79333</v>
+        <v>58119</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8969,34 +8969,46 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>630316</v>
+        <v>630231</v>
       </c>
       <c r="R80" t="n">
-        <v>6967112</v>
+        <v>6967249</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9028,7 +9040,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9038,7 +9050,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9172,10 +9184,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133152207</v>
+        <v>133152169</v>
       </c>
       <c r="B82" t="n">
-        <v>58119</v>
+        <v>79333</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9183,46 +9195,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>630231</v>
+        <v>630316</v>
       </c>
       <c r="R82" t="n">
-        <v>6967249</v>
+        <v>6967112</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10254,10 +10254,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133202145</v>
+        <v>133202148</v>
       </c>
       <c r="B92" t="n">
-        <v>91932</v>
+        <v>79333</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10265,21 +10265,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>630093</v>
+        <v>630099</v>
       </c>
       <c r="R92" t="n">
-        <v>6967070</v>
+        <v>6967120</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10361,32 +10361,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133202168</v>
+        <v>133202173</v>
       </c>
       <c r="B93" t="n">
-        <v>83181</v>
+        <v>92641</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>630290</v>
+        <v>630299</v>
       </c>
       <c r="R93" t="n">
-        <v>6967317</v>
+        <v>6967218</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10468,10 +10468,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133202155</v>
+        <v>133202145</v>
       </c>
       <c r="B94" t="n">
-        <v>91918</v>
+        <v>91932</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10479,21 +10479,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>630210</v>
+        <v>630093</v>
       </c>
       <c r="R94" t="n">
-        <v>6967196</v>
+        <v>6967070</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10575,10 +10575,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133202148</v>
+        <v>133202168</v>
       </c>
       <c r="B95" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10586,21 +10586,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>630099</v>
+        <v>630290</v>
       </c>
       <c r="R95" t="n">
-        <v>6967120</v>
+        <v>6967317</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10682,32 +10682,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133202173</v>
+        <v>133202155</v>
       </c>
       <c r="B96" t="n">
-        <v>92641</v>
+        <v>91918</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10717,10 +10717,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>630299</v>
+        <v>630210</v>
       </c>
       <c r="R96" t="n">
-        <v>6967218</v>
+        <v>6967196</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11003,32 +11003,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133202150</v>
+        <v>133202163</v>
       </c>
       <c r="B99" t="n">
-        <v>79589</v>
+        <v>79333</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11038,10 +11038,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>630122</v>
+        <v>630344</v>
       </c>
       <c r="R99" t="n">
-        <v>6967138</v>
+        <v>6967158</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11110,32 +11110,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133202163</v>
+        <v>133202150</v>
       </c>
       <c r="B100" t="n">
-        <v>79333</v>
+        <v>79589</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11145,10 +11145,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>630344</v>
+        <v>630122</v>
       </c>
       <c r="R100" t="n">
-        <v>6967158</v>
+        <v>6967138</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11553,10 +11553,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133202152</v>
+        <v>133202171</v>
       </c>
       <c r="B104" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>630108</v>
+        <v>630271</v>
       </c>
       <c r="R104" t="n">
-        <v>6967186</v>
+        <v>6967309</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11660,10 +11660,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133202125</v>
+        <v>133202159</v>
       </c>
       <c r="B105" t="n">
-        <v>79365</v>
+        <v>91932</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11671,21 +11671,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>630331</v>
+        <v>630290</v>
       </c>
       <c r="R105" t="n">
-        <v>6967087</v>
+        <v>6967123</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11767,10 +11767,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133202171</v>
+        <v>133202152</v>
       </c>
       <c r="B106" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11778,21 +11778,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>630271</v>
+        <v>630108</v>
       </c>
       <c r="R106" t="n">
-        <v>6967309</v>
+        <v>6967186</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11874,10 +11874,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133202159</v>
+        <v>133202125</v>
       </c>
       <c r="B107" t="n">
-        <v>91932</v>
+        <v>79365</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>630290</v>
+        <v>630331</v>
       </c>
       <c r="R107" t="n">
-        <v>6967123</v>
+        <v>6967087</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11981,10 +11981,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133202172</v>
+        <v>133202161</v>
       </c>
       <c r="B108" t="n">
-        <v>79365</v>
+        <v>91918</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11992,21 +11992,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12016,10 +12016,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>630285</v>
+        <v>630352</v>
       </c>
       <c r="R108" t="n">
-        <v>6967276</v>
+        <v>6967119</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133202161</v>
+        <v>133202139</v>
       </c>
       <c r="B109" t="n">
-        <v>91918</v>
+        <v>91932</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12099,21 +12099,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12123,10 +12123,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>630352</v>
+        <v>630104</v>
       </c>
       <c r="R109" t="n">
-        <v>6967119</v>
+        <v>6967096</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12195,32 +12195,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133202139</v>
+        <v>133202156</v>
       </c>
       <c r="B110" t="n">
-        <v>91932</v>
+        <v>92378</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12230,13 +12230,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>630104</v>
+        <v>630219</v>
       </c>
       <c r="R110" t="n">
-        <v>6967096</v>
+        <v>6967208</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12302,32 +12302,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133202156</v>
+        <v>133202172</v>
       </c>
       <c r="B111" t="n">
-        <v>92378</v>
+        <v>79365</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12337,13 +12337,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>630219</v>
+        <v>630285</v>
       </c>
       <c r="R111" t="n">
-        <v>6967208</v>
+        <v>6967276</v>
       </c>
       <c r="S111" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12837,10 +12837,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>133202153</v>
+        <v>133202144</v>
       </c>
       <c r="B116" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12848,21 +12848,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12872,10 +12872,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>630160</v>
+        <v>630098</v>
       </c>
       <c r="R116" t="n">
-        <v>6967163</v>
+        <v>6967075</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12917,7 +12917,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12944,10 +12944,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>133202144</v>
+        <v>133202153</v>
       </c>
       <c r="B117" t="n">
-        <v>79365</v>
+        <v>92217</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12955,21 +12955,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>630098</v>
+        <v>630160</v>
       </c>
       <c r="R117" t="n">
-        <v>6967075</v>
+        <v>6967163</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13278,10 +13278,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133202141</v>
+        <v>133202164</v>
       </c>
       <c r="B120" t="n">
-        <v>89300</v>
+        <v>79333</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13289,21 +13289,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13313,10 +13313,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>630101</v>
+        <v>630329</v>
       </c>
       <c r="R120" t="n">
-        <v>6967092</v>
+        <v>6967216</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13348,7 +13348,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13385,10 +13385,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133202164</v>
+        <v>133202141</v>
       </c>
       <c r="B121" t="n">
-        <v>79333</v>
+        <v>89300</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13396,21 +13396,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13420,10 +13420,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>630329</v>
+        <v>630101</v>
       </c>
       <c r="R121" t="n">
-        <v>6967216</v>
+        <v>6967092</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13455,7 +13455,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13492,10 +13492,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133202149</v>
+        <v>133202130</v>
       </c>
       <c r="B122" t="n">
-        <v>79365</v>
+        <v>83181</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13503,21 +13503,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13527,10 +13527,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>630102</v>
+        <v>630275</v>
       </c>
       <c r="R122" t="n">
-        <v>6967124</v>
+        <v>6967143</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13599,10 +13599,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133202137</v>
+        <v>133202149</v>
       </c>
       <c r="B123" t="n">
-        <v>92217</v>
+        <v>79365</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13610,21 +13610,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13634,10 +13634,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>630158</v>
+        <v>630102</v>
       </c>
       <c r="R123" t="n">
-        <v>6967093</v>
+        <v>6967124</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13706,10 +13706,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133202136</v>
+        <v>133202157</v>
       </c>
       <c r="B124" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13717,21 +13717,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>630184</v>
+        <v>630257</v>
       </c>
       <c r="R124" t="n">
-        <v>6967090</v>
+        <v>6967180</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13813,10 +13813,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133202130</v>
+        <v>133202137</v>
       </c>
       <c r="B125" t="n">
-        <v>83181</v>
+        <v>92217</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13824,21 +13824,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>630275</v>
+        <v>630158</v>
       </c>
       <c r="R125" t="n">
-        <v>6967143</v>
+        <v>6967093</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13920,10 +13920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133202157</v>
+        <v>133202136</v>
       </c>
       <c r="B126" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13931,21 +13931,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>630257</v>
+        <v>630184</v>
       </c>
       <c r="R126" t="n">
-        <v>6967180</v>
+        <v>6967090</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14027,10 +14027,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133202133</v>
+        <v>133202131</v>
       </c>
       <c r="B127" t="n">
-        <v>83315</v>
+        <v>83181</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14038,21 +14038,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14062,10 +14062,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>630226</v>
+        <v>630252</v>
       </c>
       <c r="R127" t="n">
-        <v>6967128</v>
+        <v>6967151</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14097,7 +14097,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14134,10 +14134,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133202131</v>
+        <v>133202133</v>
       </c>
       <c r="B128" t="n">
-        <v>83181</v>
+        <v>83315</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14145,21 +14145,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14169,10 +14169,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>630252</v>
+        <v>630226</v>
       </c>
       <c r="R128" t="n">
-        <v>6967151</v>
+        <v>6967128</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14455,10 +14455,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133240011</v>
+        <v>133240027</v>
       </c>
       <c r="B131" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14466,21 +14466,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>630186</v>
+        <v>630159</v>
       </c>
       <c r="R131" t="n">
-        <v>6967049</v>
+        <v>6967184</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14562,10 +14562,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133240026</v>
+        <v>133240011</v>
       </c>
       <c r="B132" t="n">
-        <v>91868</v>
+        <v>79365</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14573,21 +14573,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14597,10 +14597,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>630151</v>
+        <v>630186</v>
       </c>
       <c r="R132" t="n">
-        <v>6967182</v>
+        <v>6967049</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14669,10 +14669,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133240027</v>
+        <v>133240026</v>
       </c>
       <c r="B133" t="n">
-        <v>79333</v>
+        <v>91868</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14680,21 +14680,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14704,13 +14704,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>630159</v>
+        <v>630151</v>
       </c>
       <c r="R133" t="n">
-        <v>6967184</v>
+        <v>6967182</v>
       </c>
       <c r="S133" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14990,10 +14990,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133240006</v>
+        <v>133240009</v>
       </c>
       <c r="B136" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15001,21 +15001,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15025,10 +15025,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>630259</v>
+        <v>630210</v>
       </c>
       <c r="R136" t="n">
-        <v>6967095</v>
+        <v>6967061</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -15060,7 +15060,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15070,7 +15070,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15097,10 +15097,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133240003</v>
+        <v>133240034</v>
       </c>
       <c r="B137" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15108,21 +15108,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15132,10 +15132,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>630320</v>
+        <v>630375</v>
       </c>
       <c r="R137" t="n">
-        <v>6967080</v>
+        <v>6967109</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15204,10 +15204,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133240009</v>
+        <v>133240006</v>
       </c>
       <c r="B138" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15215,21 +15215,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15239,10 +15239,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>630210</v>
+        <v>630259</v>
       </c>
       <c r="R138" t="n">
-        <v>6967061</v>
+        <v>6967095</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15311,10 +15311,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133240034</v>
+        <v>133240003</v>
       </c>
       <c r="B139" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>630375</v>
+        <v>630320</v>
       </c>
       <c r="R139" t="n">
-        <v>6967109</v>
+        <v>6967080</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15418,10 +15418,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133240004</v>
+        <v>133240037</v>
       </c>
       <c r="B140" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15429,21 +15429,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15453,10 +15453,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>630287</v>
+        <v>630379</v>
       </c>
       <c r="R140" t="n">
-        <v>6967110</v>
+        <v>6967127</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15525,7 +15525,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133240037</v>
+        <v>133240030</v>
       </c>
       <c r="B141" t="n">
         <v>79333</v>
@@ -15560,13 +15560,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>630379</v>
+        <v>630210</v>
       </c>
       <c r="R141" t="n">
-        <v>6967127</v>
+        <v>6967208</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15632,10 +15632,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133240030</v>
+        <v>133240004</v>
       </c>
       <c r="B142" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15643,21 +15643,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15667,13 +15667,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>630210</v>
+        <v>630287</v>
       </c>
       <c r="R142" t="n">
-        <v>6967208</v>
+        <v>6967110</v>
       </c>
       <c r="S142" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15953,10 +15953,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>133240032</v>
+        <v>133240008</v>
       </c>
       <c r="B145" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15964,21 +15964,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15988,10 +15988,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>630247</v>
+        <v>630229</v>
       </c>
       <c r="R145" t="n">
-        <v>6967189</v>
+        <v>6967080</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16060,10 +16060,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133240008</v>
+        <v>133240032</v>
       </c>
       <c r="B146" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16071,21 +16071,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16095,10 +16095,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>630229</v>
+        <v>630247</v>
       </c>
       <c r="R146" t="n">
-        <v>6967080</v>
+        <v>6967189</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16167,10 +16167,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133240020</v>
+        <v>133244099</v>
       </c>
       <c r="B147" t="n">
-        <v>79365</v>
+        <v>57958</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16178,37 +16178,53 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Gillemyrtjärnen, Ång</t>
+          <t>Gillermyrtjärnen, Lomtjärnsåsen, Sela, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>630162</v>
+        <v>630169</v>
       </c>
       <c r="R147" t="n">
-        <v>6967059</v>
+        <v>6967162</v>
       </c>
       <c r="S147" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16237,7 +16253,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16247,7 +16263,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Ljudbox har använts och trummande tretåig hackspett har registrerats. Programmet Audacity har använts för att analysera trumningarna som hördes tidigt på morgonen. Trumningarna är i genomsnitt 1,2 sekunder långa med en slagfrekvens på i genomsnitt 12,7 slag/sekund vilket stämmer väl in på tretåig hackspett. Bifogat finns en del av ljudupptagningen och en bild med ett utmarkerat grönt kryss där genomsnittsvärdena har placerats ut samt ett skärmklipp från analysprogrammet audacity där trumningarna syns.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16274,10 +16295,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133244099</v>
+        <v>133240020</v>
       </c>
       <c r="B148" t="n">
-        <v>57958</v>
+        <v>79365</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16285,53 +16306,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Gillermyrtjärnen, Lomtjärnsåsen, Sela, Ång</t>
+          <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>630169</v>
+        <v>630162</v>
       </c>
       <c r="R148" t="n">
-        <v>6967162</v>
+        <v>6967059</v>
       </c>
       <c r="S148" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16360,7 +16365,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16370,12 +16375,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Ljudbox har använts och trummande tretåig hackspett har registrerats. Programmet Audacity har använts för att analysera trumningarna som hördes tidigt på morgonen. Trumningarna är i genomsnitt 1,2 sekunder långa med en slagfrekvens på i genomsnitt 12,7 slag/sekund vilket stämmer väl in på tretåig hackspett. Bifogat finns en del av ljudupptagningen och en bild med ett utmarkerat grönt kryss där genomsnittsvärdena har placerats ut samt ett skärmklipp från analysprogrammet audacity där trumningarna syns.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16509,10 +16509,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133240024</v>
+        <v>133240038</v>
       </c>
       <c r="B150" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16520,21 +16520,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16544,13 +16544,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>630079</v>
+        <v>630337</v>
       </c>
       <c r="R150" t="n">
-        <v>6967088</v>
+        <v>6967201</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16616,10 +16616,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133240038</v>
+        <v>133240024</v>
       </c>
       <c r="B151" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16627,21 +16627,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16651,13 +16651,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>630337</v>
+        <v>630079</v>
       </c>
       <c r="R151" t="n">
-        <v>6967201</v>
+        <v>6967088</v>
       </c>
       <c r="S151" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16723,10 +16723,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133240002</v>
+        <v>133240022</v>
       </c>
       <c r="B152" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16734,21 +16734,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16758,10 +16758,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>630334</v>
+        <v>630082</v>
       </c>
       <c r="R152" t="n">
-        <v>6967084</v>
+        <v>6967056</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16830,7 +16830,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133240022</v>
+        <v>133240033</v>
       </c>
       <c r="B153" t="n">
         <v>79333</v>
@@ -16865,10 +16865,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>630082</v>
+        <v>630273</v>
       </c>
       <c r="R153" t="n">
-        <v>6967056</v>
+        <v>6967142</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -16900,7 +16900,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16937,10 +16937,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133240033</v>
+        <v>133240002</v>
       </c>
       <c r="B154" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16948,21 +16948,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16972,10 +16972,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>630273</v>
+        <v>630334</v>
       </c>
       <c r="R154" t="n">
-        <v>6967142</v>
+        <v>6967084</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -17007,7 +17007,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17017,7 +17017,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17044,10 +17044,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133240043</v>
+        <v>133240040</v>
       </c>
       <c r="B155" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17055,21 +17055,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17079,10 +17079,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>630242</v>
+        <v>630295</v>
       </c>
       <c r="R155" t="n">
-        <v>6967369</v>
+        <v>6967374</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17151,7 +17151,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133240013</v>
+        <v>133240043</v>
       </c>
       <c r="B156" t="n">
         <v>79333</v>
@@ -17186,10 +17186,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>630166</v>
+        <v>630242</v>
       </c>
       <c r="R156" t="n">
-        <v>6967049</v>
+        <v>6967369</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -17221,7 +17221,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17258,10 +17258,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133240040</v>
+        <v>133240013</v>
       </c>
       <c r="B157" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17269,21 +17269,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17293,10 +17293,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>630295</v>
+        <v>630166</v>
       </c>
       <c r="R157" t="n">
-        <v>6967374</v>
+        <v>6967049</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -17328,7 +17328,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17338,7 +17338,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17365,10 +17365,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133240039</v>
+        <v>133240036</v>
       </c>
       <c r="B158" t="n">
-        <v>89300</v>
+        <v>79333</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17376,21 +17376,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17400,10 +17400,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>630317</v>
+        <v>630368</v>
       </c>
       <c r="R158" t="n">
-        <v>6967329</v>
+        <v>6967120</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -17435,7 +17435,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17472,10 +17472,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>133240007</v>
+        <v>133240028</v>
       </c>
       <c r="B159" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17483,21 +17483,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17507,13 +17507,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>630244</v>
+        <v>630174</v>
       </c>
       <c r="R159" t="n">
-        <v>6967085</v>
+        <v>6967208</v>
       </c>
       <c r="S159" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17579,7 +17579,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133240036</v>
+        <v>133240025</v>
       </c>
       <c r="B160" t="n">
         <v>79333</v>
@@ -17614,10 +17614,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>630368</v>
+        <v>630103</v>
       </c>
       <c r="R160" t="n">
-        <v>6967120</v>
+        <v>6967179</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17686,10 +17686,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133240028</v>
+        <v>133240039</v>
       </c>
       <c r="B161" t="n">
-        <v>79333</v>
+        <v>89300</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17697,21 +17697,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17721,10 +17721,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>630174</v>
+        <v>630317</v>
       </c>
       <c r="R161" t="n">
-        <v>6967208</v>
+        <v>6967329</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17793,10 +17793,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133240025</v>
+        <v>133240007</v>
       </c>
       <c r="B162" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17804,21 +17804,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17828,13 +17828,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>630103</v>
+        <v>630244</v>
       </c>
       <c r="R162" t="n">
-        <v>6967179</v>
+        <v>6967085</v>
       </c>
       <c r="S162" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18114,10 +18114,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133240018</v>
+        <v>133240029</v>
       </c>
       <c r="B165" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18125,21 +18125,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18149,10 +18149,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>630148</v>
+        <v>630179</v>
       </c>
       <c r="R165" t="n">
-        <v>6967065</v>
+        <v>6967208</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18328,10 +18328,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>133240029</v>
+        <v>133240018</v>
       </c>
       <c r="B167" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18339,21 +18339,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18363,10 +18363,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>630179</v>
+        <v>630148</v>
       </c>
       <c r="R167" t="n">
-        <v>6967208</v>
+        <v>6967065</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -8102,32 +8102,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133152223</v>
+        <v>133152187</v>
       </c>
       <c r="B72" t="n">
-        <v>89300</v>
+        <v>91881</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>630159</v>
+        <v>630305</v>
       </c>
       <c r="R72" t="n">
-        <v>6967161</v>
+        <v>6967310</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8209,32 +8209,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133152187</v>
+        <v>133152200</v>
       </c>
       <c r="B73" t="n">
-        <v>91881</v>
+        <v>83181</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>630305</v>
+        <v>630250</v>
       </c>
       <c r="R73" t="n">
-        <v>6967310</v>
+        <v>6967263</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8316,10 +8316,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133152200</v>
+        <v>133152223</v>
       </c>
       <c r="B74" t="n">
-        <v>83181</v>
+        <v>89300</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8327,21 +8327,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>630250</v>
+        <v>630159</v>
       </c>
       <c r="R74" t="n">
-        <v>6967263</v>
+        <v>6967161</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9719,10 +9719,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133202135</v>
+        <v>133202128</v>
       </c>
       <c r="B87" t="n">
-        <v>83181</v>
+        <v>79365</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9730,21 +9730,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9754,10 +9754,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>630165</v>
+        <v>630304</v>
       </c>
       <c r="R87" t="n">
-        <v>6967141</v>
+        <v>6967096</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9826,10 +9826,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133202128</v>
+        <v>133202135</v>
       </c>
       <c r="B88" t="n">
-        <v>79365</v>
+        <v>83181</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9837,21 +9837,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9861,10 +9861,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>630304</v>
+        <v>630165</v>
       </c>
       <c r="R88" t="n">
-        <v>6967096</v>
+        <v>6967141</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10361,32 +10361,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133202173</v>
+        <v>133202145</v>
       </c>
       <c r="B93" t="n">
-        <v>92641</v>
+        <v>91932</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>630299</v>
+        <v>630093</v>
       </c>
       <c r="R93" t="n">
-        <v>6967218</v>
+        <v>6967070</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10468,10 +10468,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133202145</v>
+        <v>133202168</v>
       </c>
       <c r="B94" t="n">
-        <v>91932</v>
+        <v>83181</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10479,21 +10479,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>630093</v>
+        <v>630290</v>
       </c>
       <c r="R94" t="n">
-        <v>6967070</v>
+        <v>6967317</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10575,32 +10575,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133202168</v>
+        <v>133202173</v>
       </c>
       <c r="B95" t="n">
-        <v>83181</v>
+        <v>92641</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>630290</v>
+        <v>630299</v>
       </c>
       <c r="R95" t="n">
-        <v>6967317</v>
+        <v>6967218</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11217,54 +11217,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133202127</v>
+        <v>133202169</v>
       </c>
       <c r="B101" t="n">
-        <v>5199</v>
+        <v>91932</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>105930</v>
+        <v>1204</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>630318</v>
+        <v>630259</v>
       </c>
       <c r="R101" t="n">
-        <v>6967099</v>
+        <v>6967344</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11296,7 +11287,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11306,12 +11297,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11320,7 +11306,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11339,10 +11324,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133202169</v>
+        <v>133202151</v>
       </c>
       <c r="B102" t="n">
-        <v>91932</v>
+        <v>83181</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11350,21 +11335,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11374,10 +11359,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>630259</v>
+        <v>630118</v>
       </c>
       <c r="R102" t="n">
-        <v>6967344</v>
+        <v>6967158</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11409,7 +11394,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11419,7 +11404,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11446,45 +11431,54 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133202151</v>
+        <v>133202127</v>
       </c>
       <c r="B103" t="n">
-        <v>83181</v>
+        <v>5199</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1312</v>
+        <v>105930</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>630118</v>
+        <v>630318</v>
       </c>
       <c r="R103" t="n">
-        <v>6967158</v>
+        <v>6967099</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11516,7 +11510,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11526,7 +11520,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11535,6 +11534,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133202171</v>
+        <v>133202152</v>
       </c>
       <c r="B104" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>630271</v>
+        <v>630108</v>
       </c>
       <c r="R104" t="n">
-        <v>6967309</v>
+        <v>6967186</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11660,10 +11660,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133202159</v>
+        <v>133202125</v>
       </c>
       <c r="B105" t="n">
-        <v>91932</v>
+        <v>79365</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11671,21 +11671,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>630290</v>
+        <v>630331</v>
       </c>
       <c r="R105" t="n">
-        <v>6967123</v>
+        <v>6967087</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11767,10 +11767,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133202152</v>
+        <v>133202171</v>
       </c>
       <c r="B106" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11778,21 +11778,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>630108</v>
+        <v>630271</v>
       </c>
       <c r="R106" t="n">
-        <v>6967186</v>
+        <v>6967309</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11874,10 +11874,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133202125</v>
+        <v>133202159</v>
       </c>
       <c r="B107" t="n">
-        <v>79365</v>
+        <v>91932</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>630331</v>
+        <v>630290</v>
       </c>
       <c r="R107" t="n">
-        <v>6967087</v>
+        <v>6967123</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13051,45 +13051,53 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133202170</v>
+        <v>133202138</v>
       </c>
       <c r="B118" t="n">
-        <v>79357</v>
+        <v>57136</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6434</v>
+        <v>102612</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>630274</v>
+        <v>630143</v>
       </c>
       <c r="R118" t="n">
-        <v>6967318</v>
+        <v>6967085</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13121,7 +13129,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13131,7 +13139,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Sannolikt tagen av en rovfågel.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13158,53 +13171,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133202138</v>
+        <v>133202170</v>
       </c>
       <c r="B119" t="n">
-        <v>57136</v>
+        <v>79357</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>102612</v>
+        <v>6434</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>630143</v>
+        <v>630274</v>
       </c>
       <c r="R119" t="n">
-        <v>6967085</v>
+        <v>6967318</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13236,7 +13241,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13246,12 +13251,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Sannolikt tagen av en rovfågel.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13599,10 +13599,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133202149</v>
+        <v>133202136</v>
       </c>
       <c r="B123" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13610,21 +13610,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13634,10 +13634,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>630102</v>
+        <v>630184</v>
       </c>
       <c r="R123" t="n">
-        <v>6967124</v>
+        <v>6967090</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13706,10 +13706,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133202157</v>
+        <v>133202149</v>
       </c>
       <c r="B124" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13717,21 +13717,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>630257</v>
+        <v>630102</v>
       </c>
       <c r="R124" t="n">
-        <v>6967180</v>
+        <v>6967124</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13813,10 +13813,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133202137</v>
+        <v>133202157</v>
       </c>
       <c r="B125" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13824,21 +13824,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>630158</v>
+        <v>630257</v>
       </c>
       <c r="R125" t="n">
-        <v>6967093</v>
+        <v>6967180</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13920,10 +13920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133202136</v>
+        <v>133202137</v>
       </c>
       <c r="B126" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13931,21 +13931,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>630184</v>
+        <v>630158</v>
       </c>
       <c r="R126" t="n">
-        <v>6967090</v>
+        <v>6967093</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14990,10 +14990,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133240009</v>
+        <v>133240006</v>
       </c>
       <c r="B136" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15001,21 +15001,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15025,10 +15025,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>630210</v>
+        <v>630259</v>
       </c>
       <c r="R136" t="n">
-        <v>6967061</v>
+        <v>6967095</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -15060,7 +15060,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15070,7 +15070,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15097,10 +15097,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133240034</v>
+        <v>133240003</v>
       </c>
       <c r="B137" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15108,21 +15108,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15132,10 +15132,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>630375</v>
+        <v>630320</v>
       </c>
       <c r="R137" t="n">
-        <v>6967109</v>
+        <v>6967080</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15204,10 +15204,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133240006</v>
+        <v>133240009</v>
       </c>
       <c r="B138" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15215,21 +15215,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15239,10 +15239,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>630259</v>
+        <v>630210</v>
       </c>
       <c r="R138" t="n">
-        <v>6967095</v>
+        <v>6967061</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15311,10 +15311,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133240003</v>
+        <v>133240034</v>
       </c>
       <c r="B139" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>630320</v>
+        <v>630375</v>
       </c>
       <c r="R139" t="n">
-        <v>6967080</v>
+        <v>6967109</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15953,10 +15953,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>133240008</v>
+        <v>133240032</v>
       </c>
       <c r="B145" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15964,21 +15964,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15988,10 +15988,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>630229</v>
+        <v>630247</v>
       </c>
       <c r="R145" t="n">
-        <v>6967080</v>
+        <v>6967189</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16060,10 +16060,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133240032</v>
+        <v>133240008</v>
       </c>
       <c r="B146" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16071,21 +16071,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16095,10 +16095,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>630247</v>
+        <v>630229</v>
       </c>
       <c r="R146" t="n">
-        <v>6967189</v>
+        <v>6967080</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18114,10 +18114,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133240029</v>
+        <v>133240041</v>
       </c>
       <c r="B165" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18125,21 +18125,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18149,10 +18149,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>630179</v>
+        <v>630250</v>
       </c>
       <c r="R165" t="n">
-        <v>6967208</v>
+        <v>6967366</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18221,7 +18221,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133240041</v>
+        <v>133240018</v>
       </c>
       <c r="B166" t="n">
         <v>79333</v>
@@ -18256,10 +18256,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>630250</v>
+        <v>630148</v>
       </c>
       <c r="R166" t="n">
-        <v>6967366</v>
+        <v>6967065</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18328,10 +18328,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>133240018</v>
+        <v>133240029</v>
       </c>
       <c r="B167" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18339,21 +18339,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18363,10 +18363,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>630148</v>
+        <v>630179</v>
       </c>
       <c r="R167" t="n">
-        <v>6967065</v>
+        <v>6967208</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -2954,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133152226</v>
+        <v>133152231</v>
       </c>
       <c r="B24" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630154</v>
+        <v>630146</v>
       </c>
       <c r="R24" t="n">
-        <v>6967129</v>
+        <v>6967080</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133152231</v>
+        <v>133152226</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630146</v>
+        <v>630154</v>
       </c>
       <c r="R25" t="n">
-        <v>6967080</v>
+        <v>6967129</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -7448,10 +7448,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133152177</v>
+        <v>133152190</v>
       </c>
       <c r="B66" t="n">
-        <v>58119</v>
+        <v>83181</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7459,46 +7459,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>630306</v>
+        <v>630270</v>
       </c>
       <c r="R66" t="n">
-        <v>6967160</v>
+        <v>6967330</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7530,7 +7518,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>05:13</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7540,7 +7528,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>05:13</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7567,10 +7555,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133152190</v>
+        <v>133152199</v>
       </c>
       <c r="B67" t="n">
-        <v>83181</v>
+        <v>79365</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7578,21 +7566,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7602,10 +7590,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>630270</v>
+        <v>630251</v>
       </c>
       <c r="R67" t="n">
-        <v>6967330</v>
+        <v>6967351</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7637,7 +7625,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7647,7 +7635,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7674,10 +7662,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133152199</v>
+        <v>133152219</v>
       </c>
       <c r="B68" t="n">
-        <v>79365</v>
+        <v>91918</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7685,21 +7673,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7709,10 +7697,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>630251</v>
+        <v>630121</v>
       </c>
       <c r="R68" t="n">
-        <v>6967351</v>
+        <v>6967203</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7744,7 +7732,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7754,7 +7742,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7781,10 +7769,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133152219</v>
+        <v>133152177</v>
       </c>
       <c r="B69" t="n">
-        <v>91918</v>
+        <v>58119</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7792,34 +7780,46 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630121</v>
+        <v>630306</v>
       </c>
       <c r="R69" t="n">
-        <v>6967203</v>
+        <v>6967160</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>05:13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>05:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8423,10 +8423,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133152171</v>
+        <v>133152212</v>
       </c>
       <c r="B75" t="n">
-        <v>79365</v>
+        <v>83181</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8434,21 +8434,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8458,13 +8458,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>630307</v>
+        <v>630176</v>
       </c>
       <c r="R75" t="n">
-        <v>6967118</v>
+        <v>6967173</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8530,10 +8530,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133152212</v>
+        <v>133152182</v>
       </c>
       <c r="B76" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8541,21 +8541,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8565,13 +8565,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>630176</v>
+        <v>630324</v>
       </c>
       <c r="R76" t="n">
-        <v>6967173</v>
+        <v>6967248</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8637,7 +8637,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133152182</v>
+        <v>133152181</v>
       </c>
       <c r="B77" t="n">
         <v>79333</v>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>630324</v>
+        <v>630334</v>
       </c>
       <c r="R77" t="n">
-        <v>6967248</v>
+        <v>6967171</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8744,10 +8744,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133152181</v>
+        <v>133152171</v>
       </c>
       <c r="B78" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8755,21 +8755,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>630334</v>
+        <v>630307</v>
       </c>
       <c r="R78" t="n">
-        <v>6967171</v>
+        <v>6967118</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9398,10 +9398,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133152172</v>
+        <v>133152229</v>
       </c>
       <c r="B84" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9409,21 +9409,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9433,10 +9433,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>630311</v>
+        <v>630095</v>
       </c>
       <c r="R84" t="n">
-        <v>6967128</v>
+        <v>6967106</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>04:56</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>04:56</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9505,7 +9505,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133152162</v>
+        <v>133152172</v>
       </c>
       <c r="B85" t="n">
         <v>79365</v>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>630337</v>
+        <v>630311</v>
       </c>
       <c r="R85" t="n">
-        <v>6967096</v>
+        <v>6967128</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>04:43</t>
+          <t>04:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>04:43</t>
+          <t>04:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9612,10 +9612,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133152229</v>
+        <v>133152162</v>
       </c>
       <c r="B86" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9623,21 +9623,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9647,10 +9647,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>630095</v>
+        <v>630337</v>
       </c>
       <c r="R86" t="n">
-        <v>6967106</v>
+        <v>6967096</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>04:43</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>04:43</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9719,10 +9719,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133202128</v>
+        <v>133202135</v>
       </c>
       <c r="B87" t="n">
-        <v>79365</v>
+        <v>83181</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9730,21 +9730,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9754,10 +9754,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>630304</v>
+        <v>630165</v>
       </c>
       <c r="R87" t="n">
-        <v>6967096</v>
+        <v>6967141</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9826,10 +9826,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133202135</v>
+        <v>133202128</v>
       </c>
       <c r="B88" t="n">
-        <v>83181</v>
+        <v>79365</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9837,21 +9837,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9861,10 +9861,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>630165</v>
+        <v>630304</v>
       </c>
       <c r="R88" t="n">
-        <v>6967141</v>
+        <v>6967096</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10361,32 +10361,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133202145</v>
+        <v>133202173</v>
       </c>
       <c r="B93" t="n">
-        <v>91932</v>
+        <v>92641</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>630093</v>
+        <v>630299</v>
       </c>
       <c r="R93" t="n">
-        <v>6967070</v>
+        <v>6967218</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10468,10 +10468,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133202168</v>
+        <v>133202145</v>
       </c>
       <c r="B94" t="n">
-        <v>83181</v>
+        <v>91932</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10479,21 +10479,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>630290</v>
+        <v>630093</v>
       </c>
       <c r="R94" t="n">
-        <v>6967317</v>
+        <v>6967070</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10575,32 +10575,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133202173</v>
+        <v>133202168</v>
       </c>
       <c r="B95" t="n">
-        <v>92641</v>
+        <v>83181</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>630299</v>
+        <v>630290</v>
       </c>
       <c r="R95" t="n">
-        <v>6967218</v>
+        <v>6967317</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11553,10 +11553,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133202152</v>
+        <v>133202171</v>
       </c>
       <c r="B104" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>630108</v>
+        <v>630271</v>
       </c>
       <c r="R104" t="n">
-        <v>6967186</v>
+        <v>6967309</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11660,10 +11660,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133202125</v>
+        <v>133202159</v>
       </c>
       <c r="B105" t="n">
-        <v>79365</v>
+        <v>91932</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11671,21 +11671,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>630331</v>
+        <v>630290</v>
       </c>
       <c r="R105" t="n">
-        <v>6967087</v>
+        <v>6967123</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11767,10 +11767,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133202171</v>
+        <v>133202152</v>
       </c>
       <c r="B106" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11778,21 +11778,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>630271</v>
+        <v>630108</v>
       </c>
       <c r="R106" t="n">
-        <v>6967309</v>
+        <v>6967186</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11874,10 +11874,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133202159</v>
+        <v>133202125</v>
       </c>
       <c r="B107" t="n">
-        <v>91932</v>
+        <v>79365</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>630290</v>
+        <v>630331</v>
       </c>
       <c r="R107" t="n">
-        <v>6967123</v>
+        <v>6967087</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13599,10 +13599,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133202136</v>
+        <v>133202149</v>
       </c>
       <c r="B123" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13610,21 +13610,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13634,10 +13634,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>630184</v>
+        <v>630102</v>
       </c>
       <c r="R123" t="n">
-        <v>6967090</v>
+        <v>6967124</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13706,10 +13706,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133202149</v>
+        <v>133202157</v>
       </c>
       <c r="B124" t="n">
-        <v>79365</v>
+        <v>91918</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13717,21 +13717,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>630102</v>
+        <v>630257</v>
       </c>
       <c r="R124" t="n">
-        <v>6967124</v>
+        <v>6967180</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13813,10 +13813,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133202157</v>
+        <v>133202137</v>
       </c>
       <c r="B125" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13824,21 +13824,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>630257</v>
+        <v>630158</v>
       </c>
       <c r="R125" t="n">
-        <v>6967180</v>
+        <v>6967093</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13920,10 +13920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133202137</v>
+        <v>133202136</v>
       </c>
       <c r="B126" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13931,21 +13931,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>630158</v>
+        <v>630184</v>
       </c>
       <c r="R126" t="n">
-        <v>6967093</v>
+        <v>6967090</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14990,10 +14990,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133240006</v>
+        <v>133240009</v>
       </c>
       <c r="B136" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15001,21 +15001,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15025,10 +15025,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>630259</v>
+        <v>630210</v>
       </c>
       <c r="R136" t="n">
-        <v>6967095</v>
+        <v>6967061</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -15060,7 +15060,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15070,7 +15070,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15097,10 +15097,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133240003</v>
+        <v>133240034</v>
       </c>
       <c r="B137" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15108,21 +15108,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15132,10 +15132,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>630320</v>
+        <v>630375</v>
       </c>
       <c r="R137" t="n">
-        <v>6967080</v>
+        <v>6967109</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15204,10 +15204,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133240009</v>
+        <v>133240006</v>
       </c>
       <c r="B138" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15215,21 +15215,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15239,10 +15239,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>630210</v>
+        <v>630259</v>
       </c>
       <c r="R138" t="n">
-        <v>6967061</v>
+        <v>6967095</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15311,10 +15311,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133240034</v>
+        <v>133240003</v>
       </c>
       <c r="B139" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>630375</v>
+        <v>630320</v>
       </c>
       <c r="R139" t="n">
-        <v>6967109</v>
+        <v>6967080</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16167,10 +16167,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133244099</v>
+        <v>133240020</v>
       </c>
       <c r="B147" t="n">
-        <v>57958</v>
+        <v>79365</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16178,53 +16178,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Gillermyrtjärnen, Lomtjärnsåsen, Sela, Ång</t>
+          <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>630169</v>
+        <v>630162</v>
       </c>
       <c r="R147" t="n">
-        <v>6967162</v>
+        <v>6967059</v>
       </c>
       <c r="S147" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16253,7 +16237,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16263,12 +16247,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Ljudbox har använts och trummande tretåig hackspett har registrerats. Programmet Audacity har använts för att analysera trumningarna som hördes tidigt på morgonen. Trumningarna är i genomsnitt 1,2 sekunder långa med en slagfrekvens på i genomsnitt 12,7 slag/sekund vilket stämmer väl in på tretåig hackspett. Bifogat finns en del av ljudupptagningen och en bild med ett utmarkerat grönt kryss där genomsnittsvärdena har placerats ut samt ett skärmklipp från analysprogrammet audacity där trumningarna syns.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16295,10 +16274,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133240020</v>
+        <v>133244099</v>
       </c>
       <c r="B148" t="n">
-        <v>79365</v>
+        <v>57958</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16306,37 +16285,53 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Gillemyrtjärnen, Ång</t>
+          <t>Gillermyrtjärnen, Lomtjärnsåsen, Sela, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>630162</v>
+        <v>630169</v>
       </c>
       <c r="R148" t="n">
-        <v>6967059</v>
+        <v>6967162</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16365,7 +16360,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16375,7 +16370,12 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Ljudbox har använts och trummande tretåig hackspett har registrerats. Programmet Audacity har använts för att analysera trumningarna som hördes tidigt på morgonen. Trumningarna är i genomsnitt 1,2 sekunder långa med en slagfrekvens på i genomsnitt 12,7 slag/sekund vilket stämmer väl in på tretåig hackspett. Bifogat finns en del av ljudupptagningen och en bild med ett utmarkerat grönt kryss där genomsnittsvärdena har placerats ut samt ett skärmklipp från analysprogrammet audacity där trumningarna syns.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17365,10 +17365,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133240036</v>
+        <v>133240039</v>
       </c>
       <c r="B158" t="n">
-        <v>79333</v>
+        <v>89300</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17376,21 +17376,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17400,10 +17400,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>630368</v>
+        <v>630317</v>
       </c>
       <c r="R158" t="n">
-        <v>6967120</v>
+        <v>6967329</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -17435,7 +17435,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17472,10 +17472,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>133240028</v>
+        <v>133240007</v>
       </c>
       <c r="B159" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17483,21 +17483,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17507,13 +17507,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>630174</v>
+        <v>630244</v>
       </c>
       <c r="R159" t="n">
-        <v>6967208</v>
+        <v>6967085</v>
       </c>
       <c r="S159" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17579,7 +17579,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133240025</v>
+        <v>133240036</v>
       </c>
       <c r="B160" t="n">
         <v>79333</v>
@@ -17614,10 +17614,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>630103</v>
+        <v>630368</v>
       </c>
       <c r="R160" t="n">
-        <v>6967179</v>
+        <v>6967120</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17686,10 +17686,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133240039</v>
+        <v>133240028</v>
       </c>
       <c r="B161" t="n">
-        <v>89300</v>
+        <v>79333</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17697,21 +17697,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17721,10 +17721,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>630317</v>
+        <v>630174</v>
       </c>
       <c r="R161" t="n">
-        <v>6967329</v>
+        <v>6967208</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17793,10 +17793,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133240007</v>
+        <v>133240025</v>
       </c>
       <c r="B162" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17804,21 +17804,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17828,13 +17828,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>630244</v>
+        <v>630103</v>
       </c>
       <c r="R162" t="n">
-        <v>6967085</v>
+        <v>6967179</v>
       </c>
       <c r="S162" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD162" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -2954,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133152231</v>
+        <v>133152226</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630146</v>
+        <v>630154</v>
       </c>
       <c r="R24" t="n">
-        <v>6967080</v>
+        <v>6967129</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133152226</v>
+        <v>133152231</v>
       </c>
       <c r="B25" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630154</v>
+        <v>630146</v>
       </c>
       <c r="R25" t="n">
-        <v>6967129</v>
+        <v>6967080</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -8423,10 +8423,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133152212</v>
+        <v>133152171</v>
       </c>
       <c r="B75" t="n">
-        <v>83181</v>
+        <v>79365</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8434,21 +8434,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8458,13 +8458,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>630176</v>
+        <v>630307</v>
       </c>
       <c r="R75" t="n">
-        <v>6967173</v>
+        <v>6967118</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8530,10 +8530,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133152182</v>
+        <v>133152212</v>
       </c>
       <c r="B76" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8541,21 +8541,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8565,13 +8565,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>630324</v>
+        <v>630176</v>
       </c>
       <c r="R76" t="n">
-        <v>6967248</v>
+        <v>6967173</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8637,7 +8637,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133152181</v>
+        <v>133152182</v>
       </c>
       <c r="B77" t="n">
         <v>79333</v>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>630334</v>
+        <v>630324</v>
       </c>
       <c r="R77" t="n">
-        <v>6967171</v>
+        <v>6967248</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8744,10 +8744,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133152171</v>
+        <v>133152181</v>
       </c>
       <c r="B78" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8755,21 +8755,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>630307</v>
+        <v>630334</v>
       </c>
       <c r="R78" t="n">
-        <v>6967118</v>
+        <v>6967171</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8958,10 +8958,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133152207</v>
+        <v>133152170</v>
       </c>
       <c r="B80" t="n">
-        <v>58119</v>
+        <v>79333</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8969,46 +8969,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>630231</v>
+        <v>630313</v>
       </c>
       <c r="R80" t="n">
-        <v>6967249</v>
+        <v>6967117</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9040,7 +9028,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9050,7 +9038,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9077,7 +9065,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133152170</v>
+        <v>133152169</v>
       </c>
       <c r="B81" t="n">
         <v>79333</v>
@@ -9112,10 +9100,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>630313</v>
+        <v>630316</v>
       </c>
       <c r="R81" t="n">
-        <v>6967117</v>
+        <v>6967112</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9147,7 +9135,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9157,7 +9145,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9184,10 +9172,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133152169</v>
+        <v>133152207</v>
       </c>
       <c r="B82" t="n">
-        <v>79333</v>
+        <v>58119</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9195,34 +9183,46 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>630316</v>
+        <v>630231</v>
       </c>
       <c r="R82" t="n">
-        <v>6967112</v>
+        <v>6967249</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9719,10 +9719,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133202135</v>
+        <v>133202128</v>
       </c>
       <c r="B87" t="n">
-        <v>83181</v>
+        <v>79365</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9730,21 +9730,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9754,10 +9754,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>630165</v>
+        <v>630304</v>
       </c>
       <c r="R87" t="n">
-        <v>6967141</v>
+        <v>6967096</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9826,10 +9826,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133202128</v>
+        <v>133202135</v>
       </c>
       <c r="B88" t="n">
-        <v>79365</v>
+        <v>83181</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9837,21 +9837,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9861,10 +9861,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>630304</v>
+        <v>630165</v>
       </c>
       <c r="R88" t="n">
-        <v>6967096</v>
+        <v>6967141</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10361,32 +10361,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133202173</v>
+        <v>133202145</v>
       </c>
       <c r="B93" t="n">
-        <v>92641</v>
+        <v>91932</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>630299</v>
+        <v>630093</v>
       </c>
       <c r="R93" t="n">
-        <v>6967218</v>
+        <v>6967070</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10468,10 +10468,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133202145</v>
+        <v>133202168</v>
       </c>
       <c r="B94" t="n">
-        <v>91932</v>
+        <v>83181</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10479,21 +10479,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>630093</v>
+        <v>630290</v>
       </c>
       <c r="R94" t="n">
-        <v>6967070</v>
+        <v>6967317</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10575,32 +10575,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133202168</v>
+        <v>133202173</v>
       </c>
       <c r="B95" t="n">
-        <v>83181</v>
+        <v>92641</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>630290</v>
+        <v>630299</v>
       </c>
       <c r="R95" t="n">
-        <v>6967317</v>
+        <v>6967218</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11217,45 +11217,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133202169</v>
+        <v>133202127</v>
       </c>
       <c r="B101" t="n">
-        <v>91932</v>
+        <v>5199</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1204</v>
+        <v>105930</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>630259</v>
+        <v>630318</v>
       </c>
       <c r="R101" t="n">
-        <v>6967344</v>
+        <v>6967099</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11287,7 +11296,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11297,7 +11306,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11306,6 +11320,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11324,10 +11339,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133202151</v>
+        <v>133202169</v>
       </c>
       <c r="B102" t="n">
-        <v>83181</v>
+        <v>91932</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11335,21 +11350,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11359,10 +11374,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>630118</v>
+        <v>630259</v>
       </c>
       <c r="R102" t="n">
-        <v>6967158</v>
+        <v>6967344</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11394,7 +11409,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11404,7 +11419,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11431,54 +11446,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133202127</v>
+        <v>133202151</v>
       </c>
       <c r="B103" t="n">
-        <v>5199</v>
+        <v>83181</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>105930</v>
+        <v>1312</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>630318</v>
+        <v>630118</v>
       </c>
       <c r="R103" t="n">
-        <v>6967099</v>
+        <v>6967158</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11510,7 +11516,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11520,12 +11526,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11534,7 +11535,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133202171</v>
+        <v>133202152</v>
       </c>
       <c r="B104" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>630271</v>
+        <v>630108</v>
       </c>
       <c r="R104" t="n">
-        <v>6967309</v>
+        <v>6967186</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11660,10 +11660,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133202159</v>
+        <v>133202125</v>
       </c>
       <c r="B105" t="n">
-        <v>91932</v>
+        <v>79365</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11671,21 +11671,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>630290</v>
+        <v>630331</v>
       </c>
       <c r="R105" t="n">
-        <v>6967123</v>
+        <v>6967087</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11767,10 +11767,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133202152</v>
+        <v>133202171</v>
       </c>
       <c r="B106" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11778,21 +11778,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>630108</v>
+        <v>630271</v>
       </c>
       <c r="R106" t="n">
-        <v>6967186</v>
+        <v>6967309</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11874,10 +11874,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133202125</v>
+        <v>133202159</v>
       </c>
       <c r="B107" t="n">
-        <v>79365</v>
+        <v>91932</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>630331</v>
+        <v>630290</v>
       </c>
       <c r="R107" t="n">
-        <v>6967087</v>
+        <v>6967123</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13599,10 +13599,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133202149</v>
+        <v>133202136</v>
       </c>
       <c r="B123" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13610,21 +13610,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13634,10 +13634,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>630102</v>
+        <v>630184</v>
       </c>
       <c r="R123" t="n">
-        <v>6967124</v>
+        <v>6967090</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13706,10 +13706,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133202157</v>
+        <v>133202149</v>
       </c>
       <c r="B124" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13717,21 +13717,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>630257</v>
+        <v>630102</v>
       </c>
       <c r="R124" t="n">
-        <v>6967180</v>
+        <v>6967124</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13813,10 +13813,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133202137</v>
+        <v>133202157</v>
       </c>
       <c r="B125" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13824,21 +13824,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>630158</v>
+        <v>630257</v>
       </c>
       <c r="R125" t="n">
-        <v>6967093</v>
+        <v>6967180</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13920,10 +13920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133202136</v>
+        <v>133202137</v>
       </c>
       <c r="B126" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13931,21 +13931,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>630184</v>
+        <v>630158</v>
       </c>
       <c r="R126" t="n">
-        <v>6967090</v>
+        <v>6967093</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14027,10 +14027,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133202131</v>
+        <v>133202133</v>
       </c>
       <c r="B127" t="n">
-        <v>83181</v>
+        <v>83315</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14038,21 +14038,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14062,10 +14062,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>630252</v>
+        <v>630226</v>
       </c>
       <c r="R127" t="n">
-        <v>6967151</v>
+        <v>6967128</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14097,7 +14097,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14134,10 +14134,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133202133</v>
+        <v>133202131</v>
       </c>
       <c r="B128" t="n">
-        <v>83315</v>
+        <v>83181</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14145,21 +14145,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14169,10 +14169,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>630226</v>
+        <v>630252</v>
       </c>
       <c r="R128" t="n">
-        <v>6967128</v>
+        <v>6967151</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16509,10 +16509,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133240038</v>
+        <v>133240024</v>
       </c>
       <c r="B150" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16520,21 +16520,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16544,13 +16544,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>630337</v>
+        <v>630079</v>
       </c>
       <c r="R150" t="n">
-        <v>6967201</v>
+        <v>6967088</v>
       </c>
       <c r="S150" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16616,10 +16616,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133240024</v>
+        <v>133240038</v>
       </c>
       <c r="B151" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16627,21 +16627,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16651,13 +16651,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>630079</v>
+        <v>630337</v>
       </c>
       <c r="R151" t="n">
-        <v>6967088</v>
+        <v>6967201</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18114,10 +18114,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133240041</v>
+        <v>133240029</v>
       </c>
       <c r="B165" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18125,21 +18125,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18149,10 +18149,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>630250</v>
+        <v>630179</v>
       </c>
       <c r="R165" t="n">
-        <v>6967366</v>
+        <v>6967208</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18221,7 +18221,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133240018</v>
+        <v>133240041</v>
       </c>
       <c r="B166" t="n">
         <v>79333</v>
@@ -18256,10 +18256,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>630148</v>
+        <v>630250</v>
       </c>
       <c r="R166" t="n">
-        <v>6967065</v>
+        <v>6967366</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18328,10 +18328,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>133240029</v>
+        <v>133240018</v>
       </c>
       <c r="B167" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18339,21 +18339,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18363,10 +18363,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>630179</v>
+        <v>630148</v>
       </c>
       <c r="R167" t="n">
-        <v>6967208</v>
+        <v>6967065</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -7448,10 +7448,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133152190</v>
+        <v>133152177</v>
       </c>
       <c r="B66" t="n">
-        <v>83181</v>
+        <v>58119</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7459,34 +7459,46 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>630270</v>
+        <v>630306</v>
       </c>
       <c r="R66" t="n">
-        <v>6967330</v>
+        <v>6967160</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7518,7 +7530,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>05:13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7528,7 +7540,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>05:13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7555,10 +7567,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133152199</v>
+        <v>133152190</v>
       </c>
       <c r="B67" t="n">
-        <v>79365</v>
+        <v>83181</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7566,21 +7578,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7590,10 +7602,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>630251</v>
+        <v>630270</v>
       </c>
       <c r="R67" t="n">
-        <v>6967351</v>
+        <v>6967330</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7625,7 +7637,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7635,7 +7647,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7662,10 +7674,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133152219</v>
+        <v>133152199</v>
       </c>
       <c r="B68" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7673,21 +7685,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7697,10 +7709,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>630121</v>
+        <v>630251</v>
       </c>
       <c r="R68" t="n">
-        <v>6967203</v>
+        <v>6967351</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7732,7 +7744,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7742,7 +7754,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7769,10 +7781,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133152177</v>
+        <v>133152219</v>
       </c>
       <c r="B69" t="n">
-        <v>58119</v>
+        <v>91918</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7780,46 +7792,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630306</v>
+        <v>630121</v>
       </c>
       <c r="R69" t="n">
-        <v>6967160</v>
+        <v>6967203</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>05:13</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>05:13</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8423,10 +8423,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133152171</v>
+        <v>133152212</v>
       </c>
       <c r="B75" t="n">
-        <v>79365</v>
+        <v>83181</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8434,21 +8434,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8458,13 +8458,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>630307</v>
+        <v>630176</v>
       </c>
       <c r="R75" t="n">
-        <v>6967118</v>
+        <v>6967173</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8530,10 +8530,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133152212</v>
+        <v>133152182</v>
       </c>
       <c r="B76" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8541,21 +8541,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8565,13 +8565,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>630176</v>
+        <v>630324</v>
       </c>
       <c r="R76" t="n">
-        <v>6967173</v>
+        <v>6967248</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8637,7 +8637,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133152182</v>
+        <v>133152181</v>
       </c>
       <c r="B77" t="n">
         <v>79333</v>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>630324</v>
+        <v>630334</v>
       </c>
       <c r="R77" t="n">
-        <v>6967248</v>
+        <v>6967171</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8744,10 +8744,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133152181</v>
+        <v>133152171</v>
       </c>
       <c r="B78" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8755,21 +8755,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>630334</v>
+        <v>630307</v>
       </c>
       <c r="R78" t="n">
-        <v>6967171</v>
+        <v>6967118</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8958,10 +8958,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133152170</v>
+        <v>133152207</v>
       </c>
       <c r="B80" t="n">
-        <v>79333</v>
+        <v>58119</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8969,34 +8969,46 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>630313</v>
+        <v>630231</v>
       </c>
       <c r="R80" t="n">
-        <v>6967117</v>
+        <v>6967249</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9028,7 +9040,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9038,7 +9050,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9065,7 +9077,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133152169</v>
+        <v>133152170</v>
       </c>
       <c r="B81" t="n">
         <v>79333</v>
@@ -9100,10 +9112,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>630316</v>
+        <v>630313</v>
       </c>
       <c r="R81" t="n">
-        <v>6967112</v>
+        <v>6967117</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9135,7 +9147,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9145,7 +9157,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9172,10 +9184,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133152207</v>
+        <v>133152169</v>
       </c>
       <c r="B82" t="n">
-        <v>58119</v>
+        <v>79333</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9183,46 +9195,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>630231</v>
+        <v>630316</v>
       </c>
       <c r="R82" t="n">
-        <v>6967249</v>
+        <v>6967112</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10361,32 +10361,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133202145</v>
+        <v>133202173</v>
       </c>
       <c r="B93" t="n">
-        <v>91932</v>
+        <v>92641</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>630093</v>
+        <v>630299</v>
       </c>
       <c r="R93" t="n">
-        <v>6967070</v>
+        <v>6967218</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10468,10 +10468,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133202168</v>
+        <v>133202145</v>
       </c>
       <c r="B94" t="n">
-        <v>83181</v>
+        <v>91932</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10479,21 +10479,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>630290</v>
+        <v>630093</v>
       </c>
       <c r="R94" t="n">
-        <v>6967317</v>
+        <v>6967070</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10575,32 +10575,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133202173</v>
+        <v>133202168</v>
       </c>
       <c r="B95" t="n">
-        <v>92641</v>
+        <v>83181</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>630299</v>
+        <v>630290</v>
       </c>
       <c r="R95" t="n">
-        <v>6967218</v>
+        <v>6967317</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11553,10 +11553,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133202152</v>
+        <v>133202171</v>
       </c>
       <c r="B104" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>630108</v>
+        <v>630271</v>
       </c>
       <c r="R104" t="n">
-        <v>6967186</v>
+        <v>6967309</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11660,10 +11660,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133202125</v>
+        <v>133202159</v>
       </c>
       <c r="B105" t="n">
-        <v>79365</v>
+        <v>91932</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11671,21 +11671,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>630331</v>
+        <v>630290</v>
       </c>
       <c r="R105" t="n">
-        <v>6967087</v>
+        <v>6967123</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11767,10 +11767,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133202171</v>
+        <v>133202152</v>
       </c>
       <c r="B106" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11778,21 +11778,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>630271</v>
+        <v>630108</v>
       </c>
       <c r="R106" t="n">
-        <v>6967309</v>
+        <v>6967186</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11874,10 +11874,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133202159</v>
+        <v>133202125</v>
       </c>
       <c r="B107" t="n">
-        <v>91932</v>
+        <v>79365</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>630290</v>
+        <v>630331</v>
       </c>
       <c r="R107" t="n">
-        <v>6967123</v>
+        <v>6967087</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13599,10 +13599,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133202136</v>
+        <v>133202149</v>
       </c>
       <c r="B123" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13610,21 +13610,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13634,10 +13634,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>630184</v>
+        <v>630102</v>
       </c>
       <c r="R123" t="n">
-        <v>6967090</v>
+        <v>6967124</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13706,10 +13706,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133202149</v>
+        <v>133202157</v>
       </c>
       <c r="B124" t="n">
-        <v>79365</v>
+        <v>91918</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13717,21 +13717,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>630102</v>
+        <v>630257</v>
       </c>
       <c r="R124" t="n">
-        <v>6967124</v>
+        <v>6967180</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13813,10 +13813,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133202157</v>
+        <v>133202137</v>
       </c>
       <c r="B125" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13824,21 +13824,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>630257</v>
+        <v>630158</v>
       </c>
       <c r="R125" t="n">
-        <v>6967180</v>
+        <v>6967093</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13920,10 +13920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133202137</v>
+        <v>133202136</v>
       </c>
       <c r="B126" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13931,21 +13931,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>630158</v>
+        <v>630184</v>
       </c>
       <c r="R126" t="n">
-        <v>6967093</v>
+        <v>6967090</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14027,10 +14027,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133202133</v>
+        <v>133202131</v>
       </c>
       <c r="B127" t="n">
-        <v>83315</v>
+        <v>83181</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14038,21 +14038,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14062,10 +14062,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>630226</v>
+        <v>630252</v>
       </c>
       <c r="R127" t="n">
-        <v>6967128</v>
+        <v>6967151</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14097,7 +14097,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14134,10 +14134,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133202131</v>
+        <v>133202133</v>
       </c>
       <c r="B128" t="n">
-        <v>83181</v>
+        <v>83315</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14145,21 +14145,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14169,10 +14169,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>630252</v>
+        <v>630226</v>
       </c>
       <c r="R128" t="n">
-        <v>6967151</v>
+        <v>6967128</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14990,10 +14990,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133240009</v>
+        <v>133240006</v>
       </c>
       <c r="B136" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15001,21 +15001,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15025,10 +15025,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>630210</v>
+        <v>630259</v>
       </c>
       <c r="R136" t="n">
-        <v>6967061</v>
+        <v>6967095</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -15060,7 +15060,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15070,7 +15070,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15097,10 +15097,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133240034</v>
+        <v>133240003</v>
       </c>
       <c r="B137" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15108,21 +15108,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15132,10 +15132,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>630375</v>
+        <v>630320</v>
       </c>
       <c r="R137" t="n">
-        <v>6967109</v>
+        <v>6967080</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15204,10 +15204,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133240006</v>
+        <v>133240009</v>
       </c>
       <c r="B138" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15215,21 +15215,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15239,10 +15239,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>630259</v>
+        <v>630210</v>
       </c>
       <c r="R138" t="n">
-        <v>6967095</v>
+        <v>6967061</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15311,10 +15311,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133240003</v>
+        <v>133240034</v>
       </c>
       <c r="B139" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>630320</v>
+        <v>630375</v>
       </c>
       <c r="R139" t="n">
-        <v>6967080</v>
+        <v>6967109</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16509,10 +16509,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133240024</v>
+        <v>133240038</v>
       </c>
       <c r="B150" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16520,21 +16520,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16544,13 +16544,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>630079</v>
+        <v>630337</v>
       </c>
       <c r="R150" t="n">
-        <v>6967088</v>
+        <v>6967201</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16616,10 +16616,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133240038</v>
+        <v>133240024</v>
       </c>
       <c r="B151" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16627,21 +16627,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16651,13 +16651,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>630337</v>
+        <v>630079</v>
       </c>
       <c r="R151" t="n">
-        <v>6967201</v>
+        <v>6967088</v>
       </c>
       <c r="S151" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17365,10 +17365,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133240039</v>
+        <v>133240036</v>
       </c>
       <c r="B158" t="n">
-        <v>89300</v>
+        <v>79333</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17376,21 +17376,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17400,10 +17400,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>630317</v>
+        <v>630368</v>
       </c>
       <c r="R158" t="n">
-        <v>6967329</v>
+        <v>6967120</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -17435,7 +17435,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17472,10 +17472,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>133240007</v>
+        <v>133240028</v>
       </c>
       <c r="B159" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17483,21 +17483,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17507,13 +17507,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>630244</v>
+        <v>630174</v>
       </c>
       <c r="R159" t="n">
-        <v>6967085</v>
+        <v>6967208</v>
       </c>
       <c r="S159" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17579,7 +17579,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133240036</v>
+        <v>133240025</v>
       </c>
       <c r="B160" t="n">
         <v>79333</v>
@@ -17614,10 +17614,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>630368</v>
+        <v>630103</v>
       </c>
       <c r="R160" t="n">
-        <v>6967120</v>
+        <v>6967179</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17686,10 +17686,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133240028</v>
+        <v>133240039</v>
       </c>
       <c r="B161" t="n">
-        <v>79333</v>
+        <v>89300</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17697,21 +17697,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17721,10 +17721,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>630174</v>
+        <v>630317</v>
       </c>
       <c r="R161" t="n">
-        <v>6967208</v>
+        <v>6967329</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17793,10 +17793,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133240025</v>
+        <v>133240007</v>
       </c>
       <c r="B162" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17804,21 +17804,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17828,13 +17828,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>630103</v>
+        <v>630244</v>
       </c>
       <c r="R162" t="n">
-        <v>6967179</v>
+        <v>6967085</v>
       </c>
       <c r="S162" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18114,10 +18114,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133240029</v>
+        <v>133240041</v>
       </c>
       <c r="B165" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18125,21 +18125,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18149,10 +18149,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>630179</v>
+        <v>630250</v>
       </c>
       <c r="R165" t="n">
-        <v>6967208</v>
+        <v>6967366</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18221,7 +18221,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133240041</v>
+        <v>133240018</v>
       </c>
       <c r="B166" t="n">
         <v>79333</v>
@@ -18256,10 +18256,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>630250</v>
+        <v>630148</v>
       </c>
       <c r="R166" t="n">
-        <v>6967366</v>
+        <v>6967065</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18328,10 +18328,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>133240018</v>
+        <v>133240029</v>
       </c>
       <c r="B167" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18339,21 +18339,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18363,10 +18363,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>630148</v>
+        <v>630179</v>
       </c>
       <c r="R167" t="n">
-        <v>6967065</v>
+        <v>6967208</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133152237</v>
+        <v>133152204</v>
       </c>
       <c r="B11" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630189</v>
+        <v>630265</v>
       </c>
       <c r="R11" t="n">
-        <v>6967121</v>
+        <v>6967240</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1638,12 +1638,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,7 +1668,7 @@
         <v>133152222</v>
       </c>
       <c r="B12" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133152220</v>
+        <v>133152237</v>
       </c>
       <c r="B13" t="n">
-        <v>91932</v>
+        <v>79334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630135</v>
+        <v>630189</v>
       </c>
       <c r="R13" t="n">
-        <v>6967160</v>
+        <v>6967121</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1847,7 +1842,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1857,7 +1852,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133152204</v>
+        <v>133152220</v>
       </c>
       <c r="B14" t="n">
-        <v>91918</v>
+        <v>91934</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1895,21 +1895,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630265</v>
+        <v>630135</v>
       </c>
       <c r="R14" t="n">
-        <v>6967240</v>
+        <v>6967160</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1994,7 +1994,7 @@
         <v>133152217</v>
       </c>
       <c r="B15" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,10 +2098,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133152205</v>
+        <v>133152225</v>
       </c>
       <c r="B16" t="n">
-        <v>92217</v>
+        <v>79366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2109,21 +2109,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630269</v>
+        <v>630153</v>
       </c>
       <c r="R16" t="n">
-        <v>6967234</v>
+        <v>6967136</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133152225</v>
+        <v>133152246</v>
       </c>
       <c r="B17" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630153</v>
+        <v>630264</v>
       </c>
       <c r="R17" t="n">
-        <v>6967136</v>
+        <v>6967100</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133152246</v>
+        <v>133152163</v>
       </c>
       <c r="B18" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630264</v>
+        <v>630334</v>
       </c>
       <c r="R18" t="n">
-        <v>6967100</v>
+        <v>6967097</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2419,32 +2419,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133152163</v>
+        <v>133152185</v>
       </c>
       <c r="B19" t="n">
-        <v>79365</v>
+        <v>91883</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630334</v>
+        <v>630303</v>
       </c>
       <c r="R19" t="n">
-        <v>6967097</v>
+        <v>6967279</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133152218</v>
+        <v>133152205</v>
       </c>
       <c r="B20" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630124</v>
+        <v>630269</v>
       </c>
       <c r="R20" t="n">
-        <v>6967208</v>
+        <v>6967234</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2633,32 +2633,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133152185</v>
+        <v>133152165</v>
       </c>
       <c r="B21" t="n">
-        <v>91881</v>
+        <v>79334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630303</v>
+        <v>630325</v>
       </c>
       <c r="R21" t="n">
-        <v>6967279</v>
+        <v>6967107</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2743,7 +2743,7 @@
         <v>133152174</v>
       </c>
       <c r="B22" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2847,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133152165</v>
+        <v>133152218</v>
       </c>
       <c r="B23" t="n">
-        <v>79333</v>
+        <v>92219</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630325</v>
+        <v>630124</v>
       </c>
       <c r="R23" t="n">
-        <v>6967107</v>
+        <v>6967208</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2954,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133152226</v>
+        <v>133152231</v>
       </c>
       <c r="B24" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630154</v>
+        <v>630146</v>
       </c>
       <c r="R24" t="n">
-        <v>6967129</v>
+        <v>6967080</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133152231</v>
+        <v>133152226</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630146</v>
+        <v>630154</v>
       </c>
       <c r="R25" t="n">
-        <v>6967080</v>
+        <v>6967129</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3168,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133152221</v>
+        <v>133152161</v>
       </c>
       <c r="B26" t="n">
-        <v>91918</v>
+        <v>79366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,21 +3179,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3203,10 +3203,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630134</v>
+        <v>630345</v>
       </c>
       <c r="R26" t="n">
-        <v>6967158</v>
+        <v>6967095</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>04:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>04:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3275,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133152161</v>
+        <v>133152221</v>
       </c>
       <c r="B27" t="n">
-        <v>79365</v>
+        <v>91920</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630345</v>
+        <v>630134</v>
       </c>
       <c r="R27" t="n">
-        <v>6967095</v>
+        <v>6967158</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>04:42</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>04:42</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3385,7 +3385,7 @@
         <v>133152224</v>
       </c>
       <c r="B28" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3489,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133152173</v>
+        <v>133152184</v>
       </c>
       <c r="B29" t="n">
-        <v>79333</v>
+        <v>79366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,21 +3500,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630300</v>
+        <v>630304</v>
       </c>
       <c r="R29" t="n">
-        <v>6967133</v>
+        <v>6967273</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3599,7 +3599,7 @@
         <v>133152188</v>
       </c>
       <c r="B30" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133152184</v>
+        <v>133152173</v>
       </c>
       <c r="B31" t="n">
-        <v>79365</v>
+        <v>79334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630304</v>
+        <v>630300</v>
       </c>
       <c r="R31" t="n">
-        <v>6967273</v>
+        <v>6967133</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3810,10 +3810,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133152193</v>
+        <v>133152203</v>
       </c>
       <c r="B32" t="n">
-        <v>83181</v>
+        <v>91934</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3821,21 +3821,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630280</v>
+        <v>630258</v>
       </c>
       <c r="R32" t="n">
-        <v>6967356</v>
+        <v>6967247</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3917,10 +3917,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133152203</v>
+        <v>133152193</v>
       </c>
       <c r="B33" t="n">
-        <v>91932</v>
+        <v>83182</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3928,21 +3928,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630258</v>
+        <v>630280</v>
       </c>
       <c r="R33" t="n">
-        <v>6967247</v>
+        <v>6967356</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4024,10 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133152206</v>
+        <v>133152234</v>
       </c>
       <c r="B34" t="n">
-        <v>79333</v>
+        <v>79366</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630256</v>
+        <v>630161</v>
       </c>
       <c r="R34" t="n">
-        <v>6967220</v>
+        <v>6967098</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4131,10 +4131,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133152234</v>
+        <v>133152164</v>
       </c>
       <c r="B35" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630161</v>
+        <v>630325</v>
       </c>
       <c r="R35" t="n">
-        <v>6967098</v>
+        <v>6967107</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4238,10 +4238,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133152164</v>
+        <v>133152167</v>
       </c>
       <c r="B36" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630325</v>
+        <v>630318</v>
       </c>
       <c r="R36" t="n">
-        <v>6967107</v>
+        <v>6967112</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4345,10 +4345,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133152167</v>
+        <v>133152206</v>
       </c>
       <c r="B37" t="n">
-        <v>79365</v>
+        <v>79334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4356,21 +4356,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630318</v>
+        <v>630256</v>
       </c>
       <c r="R37" t="n">
-        <v>6967112</v>
+        <v>6967220</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>04:51</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>04:51</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4452,10 +4452,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133152196</v>
+        <v>133152242</v>
       </c>
       <c r="B38" t="n">
-        <v>83181</v>
+        <v>79334</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4463,21 +4463,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630299</v>
+        <v>630247</v>
       </c>
       <c r="R38" t="n">
-        <v>6967344</v>
+        <v>6967129</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4562,7 +4562,7 @@
         <v>133152243</v>
       </c>
       <c r="B39" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4666,10 +4666,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133152242</v>
+        <v>133152196</v>
       </c>
       <c r="B40" t="n">
-        <v>79333</v>
+        <v>83182</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630247</v>
+        <v>630299</v>
       </c>
       <c r="R40" t="n">
-        <v>6967129</v>
+        <v>6967344</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4776,7 +4776,7 @@
         <v>133152210</v>
       </c>
       <c r="B41" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>133152178</v>
       </c>
       <c r="B42" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4987,32 +4987,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133152195</v>
+        <v>133152201</v>
       </c>
       <c r="B43" t="n">
-        <v>75433</v>
+        <v>91920</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630297</v>
+        <v>630261</v>
       </c>
       <c r="R43" t="n">
-        <v>6967347</v>
+        <v>6967251</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5094,32 +5094,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133152216</v>
+        <v>133152195</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>75433</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630149</v>
+        <v>630297</v>
       </c>
       <c r="R44" t="n">
-        <v>6967241</v>
+        <v>6967347</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5201,10 +5201,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133152201</v>
+        <v>133152216</v>
       </c>
       <c r="B45" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5212,21 +5212,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630261</v>
+        <v>630149</v>
       </c>
       <c r="R45" t="n">
-        <v>6967251</v>
+        <v>6967241</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5415,10 +5415,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133152241</v>
+        <v>133152159</v>
       </c>
       <c r="B47" t="n">
-        <v>83181</v>
+        <v>79366</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,21 +5426,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5450,13 +5450,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>630259</v>
+        <v>630350</v>
       </c>
       <c r="R47" t="n">
-        <v>6967135</v>
+        <v>6967090</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5522,10 +5522,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133152159</v>
+        <v>133152198</v>
       </c>
       <c r="B48" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5557,13 +5557,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>630350</v>
+        <v>630231</v>
       </c>
       <c r="R48" t="n">
-        <v>6967090</v>
+        <v>6967393</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5629,10 +5629,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133152198</v>
+        <v>133152232</v>
       </c>
       <c r="B49" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>630231</v>
+        <v>630147</v>
       </c>
       <c r="R49" t="n">
-        <v>6967393</v>
+        <v>6967088</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5736,10 +5736,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133152232</v>
+        <v>133152241</v>
       </c>
       <c r="B50" t="n">
-        <v>79365</v>
+        <v>83182</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5747,21 +5747,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>630147</v>
+        <v>630259</v>
       </c>
       <c r="R50" t="n">
-        <v>6967088</v>
+        <v>6967135</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5846,7 +5846,7 @@
         <v>133152189</v>
       </c>
       <c r="B51" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5950,10 +5950,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133152209</v>
+        <v>133152235</v>
       </c>
       <c r="B52" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5961,21 +5961,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>630184</v>
+        <v>630162</v>
       </c>
       <c r="R52" t="n">
-        <v>6967242</v>
+        <v>6967096</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6057,10 +6057,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133152235</v>
+        <v>133152209</v>
       </c>
       <c r="B53" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6068,21 +6068,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>630162</v>
+        <v>630184</v>
       </c>
       <c r="R53" t="n">
-        <v>6967096</v>
+        <v>6967242</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6167,7 +6167,7 @@
         <v>133152194</v>
       </c>
       <c r="B54" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6271,32 +6271,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133152183</v>
+        <v>133152208</v>
       </c>
       <c r="B55" t="n">
-        <v>75433</v>
+        <v>79334</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6306,13 +6306,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630308</v>
+        <v>630207</v>
       </c>
       <c r="R55" t="n">
-        <v>6967259</v>
+        <v>6967295</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6378,10 +6378,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133152208</v>
+        <v>133152238</v>
       </c>
       <c r="B56" t="n">
-        <v>79333</v>
+        <v>83182</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6389,21 +6389,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6413,13 +6413,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630207</v>
+        <v>630180</v>
       </c>
       <c r="R56" t="n">
-        <v>6967295</v>
+        <v>6967130</v>
       </c>
       <c r="S56" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6485,32 +6485,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133152238</v>
+        <v>133152183</v>
       </c>
       <c r="B57" t="n">
-        <v>83181</v>
+        <v>75433</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>6426</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6520,13 +6520,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>630180</v>
+        <v>630308</v>
       </c>
       <c r="R57" t="n">
-        <v>6967130</v>
+        <v>6967259</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6595,7 +6595,7 @@
         <v>133152168</v>
       </c>
       <c r="B58" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6699,10 +6699,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133152227</v>
+        <v>133152215</v>
       </c>
       <c r="B59" t="n">
-        <v>83181</v>
+        <v>91920</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6710,21 +6710,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630148</v>
+        <v>630159</v>
       </c>
       <c r="R59" t="n">
-        <v>6967117</v>
+        <v>6967229</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6806,10 +6806,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133152191</v>
+        <v>133152175</v>
       </c>
       <c r="B60" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6841,13 +6841,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>630272</v>
+        <v>630308</v>
       </c>
       <c r="R60" t="n">
-        <v>6967349</v>
+        <v>6967163</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6913,10 +6913,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133152240</v>
+        <v>133152239</v>
       </c>
       <c r="B61" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6924,21 +6924,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>630263</v>
+        <v>630255</v>
       </c>
       <c r="R61" t="n">
-        <v>6967142</v>
+        <v>6967168</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7020,10 +7020,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133152215</v>
+        <v>133152191</v>
       </c>
       <c r="B62" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7031,21 +7031,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7055,10 +7055,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630159</v>
+        <v>630272</v>
       </c>
       <c r="R62" t="n">
-        <v>6967229</v>
+        <v>6967349</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7130,7 +7130,7 @@
         <v>133152180</v>
       </c>
       <c r="B63" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7234,10 +7234,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133152239</v>
+        <v>133152227</v>
       </c>
       <c r="B64" t="n">
-        <v>91918</v>
+        <v>83182</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7245,21 +7245,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>630255</v>
+        <v>630148</v>
       </c>
       <c r="R64" t="n">
-        <v>6967168</v>
+        <v>6967117</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7341,10 +7341,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133152175</v>
+        <v>133152240</v>
       </c>
       <c r="B65" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7376,13 +7376,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>630308</v>
+        <v>630263</v>
       </c>
       <c r="R65" t="n">
-        <v>6967163</v>
+        <v>6967142</v>
       </c>
       <c r="S65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7448,10 +7448,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133152177</v>
+        <v>133152199</v>
       </c>
       <c r="B66" t="n">
-        <v>58119</v>
+        <v>79366</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7459,46 +7459,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>630306</v>
+        <v>630251</v>
       </c>
       <c r="R66" t="n">
-        <v>6967160</v>
+        <v>6967351</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7530,7 +7518,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>05:13</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7540,7 +7528,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>05:13</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7567,10 +7555,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133152190</v>
+        <v>133152219</v>
       </c>
       <c r="B67" t="n">
-        <v>83181</v>
+        <v>91920</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7578,21 +7566,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7602,10 +7590,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>630270</v>
+        <v>630121</v>
       </c>
       <c r="R67" t="n">
-        <v>6967330</v>
+        <v>6967203</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7637,7 +7625,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7647,7 +7635,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7674,10 +7662,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133152199</v>
+        <v>133152190</v>
       </c>
       <c r="B68" t="n">
-        <v>79365</v>
+        <v>83182</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7685,21 +7673,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7709,10 +7697,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>630251</v>
+        <v>630270</v>
       </c>
       <c r="R68" t="n">
-        <v>6967351</v>
+        <v>6967330</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7744,7 +7732,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7754,7 +7742,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7781,10 +7769,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133152219</v>
+        <v>133152177</v>
       </c>
       <c r="B69" t="n">
-        <v>91918</v>
+        <v>58119</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7792,34 +7780,46 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630121</v>
+        <v>630306</v>
       </c>
       <c r="R69" t="n">
-        <v>6967203</v>
+        <v>6967160</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>05:13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>05:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7891,7 +7891,7 @@
         <v>133152230</v>
       </c>
       <c r="B70" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>133152214</v>
       </c>
       <c r="B71" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>133152187</v>
       </c>
       <c r="B72" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>133152200</v>
       </c>
       <c r="B73" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>133152223</v>
       </c>
       <c r="B74" t="n">
-        <v>89300</v>
+        <v>89302</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8423,10 +8423,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133152212</v>
+        <v>133152171</v>
       </c>
       <c r="B75" t="n">
-        <v>83181</v>
+        <v>79366</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8434,21 +8434,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8458,13 +8458,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>630176</v>
+        <v>630307</v>
       </c>
       <c r="R75" t="n">
-        <v>6967173</v>
+        <v>6967118</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8530,10 +8530,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133152182</v>
+        <v>133152212</v>
       </c>
       <c r="B76" t="n">
-        <v>79333</v>
+        <v>83182</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8541,21 +8541,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8565,13 +8565,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>630324</v>
+        <v>630176</v>
       </c>
       <c r="R76" t="n">
-        <v>6967248</v>
+        <v>6967173</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8640,7 +8640,7 @@
         <v>133152181</v>
       </c>
       <c r="B77" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8744,10 +8744,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133152171</v>
+        <v>133152182</v>
       </c>
       <c r="B78" t="n">
-        <v>79365</v>
+        <v>79334</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8755,21 +8755,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>630307</v>
+        <v>630324</v>
       </c>
       <c r="R78" t="n">
-        <v>6967118</v>
+        <v>6967248</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8851,10 +8851,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133152228</v>
+        <v>133152169</v>
       </c>
       <c r="B79" t="n">
-        <v>79365</v>
+        <v>79334</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8862,21 +8862,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8886,10 +8886,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>630092</v>
+        <v>630316</v>
       </c>
       <c r="R79" t="n">
-        <v>6967142</v>
+        <v>6967112</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8958,10 +8958,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133152207</v>
+        <v>133152170</v>
       </c>
       <c r="B80" t="n">
-        <v>58119</v>
+        <v>79334</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8969,46 +8969,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>630231</v>
+        <v>630313</v>
       </c>
       <c r="R80" t="n">
-        <v>6967249</v>
+        <v>6967117</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9040,7 +9028,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9050,7 +9038,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9077,10 +9065,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133152170</v>
+        <v>133152207</v>
       </c>
       <c r="B81" t="n">
-        <v>79333</v>
+        <v>58119</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9088,34 +9076,46 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>630313</v>
+        <v>630231</v>
       </c>
       <c r="R81" t="n">
-        <v>6967117</v>
+        <v>6967249</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9184,10 +9184,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133152169</v>
+        <v>133152228</v>
       </c>
       <c r="B82" t="n">
-        <v>79333</v>
+        <v>79366</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9195,21 +9195,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9219,10 +9219,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>630316</v>
+        <v>630092</v>
       </c>
       <c r="R82" t="n">
-        <v>6967112</v>
+        <v>6967142</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9294,7 +9294,7 @@
         <v>133152213</v>
       </c>
       <c r="B83" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>133152229</v>
       </c>
       <c r="B84" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>133152172</v>
       </c>
       <c r="B85" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>133152162</v>
       </c>
       <c r="B86" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>133202128</v>
       </c>
       <c r="B87" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>133202135</v>
       </c>
       <c r="B88" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9933,10 +9933,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133202134</v>
+        <v>133202147</v>
       </c>
       <c r="B89" t="n">
-        <v>83181</v>
+        <v>91934</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9944,21 +9944,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>630178</v>
+        <v>630094</v>
       </c>
       <c r="R89" t="n">
-        <v>6967146</v>
+        <v>6967070</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10003,7 +10003,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10040,10 +10040,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133202147</v>
+        <v>133202134</v>
       </c>
       <c r="B90" t="n">
-        <v>91932</v>
+        <v>83182</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10051,21 +10051,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>630094</v>
+        <v>630178</v>
       </c>
       <c r="R90" t="n">
-        <v>6967070</v>
+        <v>6967146</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10150,7 +10150,7 @@
         <v>133202165</v>
       </c>
       <c r="B91" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10254,10 +10254,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133202148</v>
+        <v>133202145</v>
       </c>
       <c r="B92" t="n">
-        <v>79333</v>
+        <v>91934</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10265,21 +10265,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>630099</v>
+        <v>630093</v>
       </c>
       <c r="R92" t="n">
-        <v>6967120</v>
+        <v>6967070</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10361,32 +10361,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133202173</v>
+        <v>133202155</v>
       </c>
       <c r="B93" t="n">
-        <v>92641</v>
+        <v>91920</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>630299</v>
+        <v>630210</v>
       </c>
       <c r="R93" t="n">
-        <v>6967218</v>
+        <v>6967196</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10468,10 +10468,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133202145</v>
+        <v>133202148</v>
       </c>
       <c r="B94" t="n">
-        <v>91932</v>
+        <v>79334</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10479,21 +10479,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>630093</v>
+        <v>630099</v>
       </c>
       <c r="R94" t="n">
-        <v>6967070</v>
+        <v>6967120</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10578,7 +10578,7 @@
         <v>133202168</v>
       </c>
       <c r="B95" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10682,32 +10682,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133202155</v>
+        <v>133202173</v>
       </c>
       <c r="B96" t="n">
-        <v>91918</v>
+        <v>92643</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10717,10 +10717,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>630210</v>
+        <v>630299</v>
       </c>
       <c r="R96" t="n">
-        <v>6967196</v>
+        <v>6967218</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10792,7 +10792,7 @@
         <v>133202162</v>
       </c>
       <c r="B97" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>133202142</v>
       </c>
       <c r="B98" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11003,32 +11003,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133202163</v>
+        <v>133202150</v>
       </c>
       <c r="B99" t="n">
-        <v>79333</v>
+        <v>79590</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11038,10 +11038,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>630344</v>
+        <v>630122</v>
       </c>
       <c r="R99" t="n">
-        <v>6967158</v>
+        <v>6967138</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11110,32 +11110,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133202150</v>
+        <v>133202163</v>
       </c>
       <c r="B100" t="n">
-        <v>79589</v>
+        <v>79334</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11145,10 +11145,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>630122</v>
+        <v>630344</v>
       </c>
       <c r="R100" t="n">
-        <v>6967138</v>
+        <v>6967158</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11342,7 +11342,7 @@
         <v>133202169</v>
       </c>
       <c r="B102" t="n">
-        <v>91932</v>
+        <v>91934</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>133202151</v>
       </c>
       <c r="B103" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133202171</v>
+        <v>133202152</v>
       </c>
       <c r="B104" t="n">
-        <v>79333</v>
+        <v>79366</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>630271</v>
+        <v>630108</v>
       </c>
       <c r="R104" t="n">
-        <v>6967309</v>
+        <v>6967186</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11660,10 +11660,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133202159</v>
+        <v>133202125</v>
       </c>
       <c r="B105" t="n">
-        <v>91932</v>
+        <v>79366</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11671,21 +11671,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>630290</v>
+        <v>630331</v>
       </c>
       <c r="R105" t="n">
-        <v>6967123</v>
+        <v>6967087</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11767,10 +11767,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133202152</v>
+        <v>133202159</v>
       </c>
       <c r="B106" t="n">
-        <v>79365</v>
+        <v>91934</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11778,21 +11778,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>630108</v>
+        <v>630290</v>
       </c>
       <c r="R106" t="n">
-        <v>6967186</v>
+        <v>6967123</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11874,10 +11874,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133202125</v>
+        <v>133202171</v>
       </c>
       <c r="B107" t="n">
-        <v>79365</v>
+        <v>79334</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>630331</v>
+        <v>630271</v>
       </c>
       <c r="R107" t="n">
-        <v>6967087</v>
+        <v>6967309</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11981,10 +11981,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133202161</v>
+        <v>133202172</v>
       </c>
       <c r="B108" t="n">
-        <v>91918</v>
+        <v>79366</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11992,21 +11992,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12016,10 +12016,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>630352</v>
+        <v>630285</v>
       </c>
       <c r="R108" t="n">
-        <v>6967119</v>
+        <v>6967276</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133202139</v>
+        <v>133202161</v>
       </c>
       <c r="B109" t="n">
-        <v>91932</v>
+        <v>91920</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12099,21 +12099,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12123,10 +12123,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>630104</v>
+        <v>630352</v>
       </c>
       <c r="R109" t="n">
-        <v>6967096</v>
+        <v>6967119</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12195,32 +12195,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133202156</v>
+        <v>133202139</v>
       </c>
       <c r="B110" t="n">
-        <v>92378</v>
+        <v>91934</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12230,13 +12230,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>630219</v>
+        <v>630104</v>
       </c>
       <c r="R110" t="n">
-        <v>6967208</v>
+        <v>6967096</v>
       </c>
       <c r="S110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12302,32 +12302,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133202172</v>
+        <v>133202156</v>
       </c>
       <c r="B111" t="n">
-        <v>79365</v>
+        <v>92380</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12337,13 +12337,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>630285</v>
+        <v>630219</v>
       </c>
       <c r="R111" t="n">
-        <v>6967276</v>
+        <v>6967208</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12409,10 +12409,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>133202160</v>
+        <v>133202158</v>
       </c>
       <c r="B112" t="n">
-        <v>91918</v>
+        <v>83182</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12420,21 +12420,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>630361</v>
+        <v>630269</v>
       </c>
       <c r="R112" t="n">
-        <v>6967100</v>
+        <v>6967158</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12516,10 +12516,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133202158</v>
+        <v>133202160</v>
       </c>
       <c r="B113" t="n">
-        <v>83181</v>
+        <v>91920</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12527,21 +12527,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12551,10 +12551,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>630269</v>
+        <v>630361</v>
       </c>
       <c r="R113" t="n">
-        <v>6967158</v>
+        <v>6967100</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12626,7 +12626,7 @@
         <v>133202132</v>
       </c>
       <c r="B114" t="n">
-        <v>91932</v>
+        <v>91934</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>133202167</v>
       </c>
       <c r="B115" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>133202144</v>
       </c>
       <c r="B116" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>133202153</v>
       </c>
       <c r="B117" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13051,53 +13051,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133202138</v>
+        <v>133202170</v>
       </c>
       <c r="B118" t="n">
-        <v>57136</v>
+        <v>79358</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>102612</v>
+        <v>6434</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>630143</v>
+        <v>630274</v>
       </c>
       <c r="R118" t="n">
-        <v>6967085</v>
+        <v>6967318</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13129,7 +13121,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13139,12 +13131,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Sannolikt tagen av en rovfågel.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13171,45 +13158,53 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133202170</v>
+        <v>133202138</v>
       </c>
       <c r="B119" t="n">
-        <v>79357</v>
+        <v>57136</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6434</v>
+        <v>102612</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>630274</v>
+        <v>630143</v>
       </c>
       <c r="R119" t="n">
-        <v>6967318</v>
+        <v>6967085</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13241,7 +13236,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13251,7 +13246,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Sannolikt tagen av en rovfågel.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13278,10 +13278,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133202164</v>
+        <v>133202141</v>
       </c>
       <c r="B120" t="n">
-        <v>79333</v>
+        <v>89302</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13289,21 +13289,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13313,10 +13313,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>630329</v>
+        <v>630101</v>
       </c>
       <c r="R120" t="n">
-        <v>6967216</v>
+        <v>6967092</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13348,7 +13348,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13385,10 +13385,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133202141</v>
+        <v>133202164</v>
       </c>
       <c r="B121" t="n">
-        <v>89300</v>
+        <v>79334</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13396,21 +13396,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13420,10 +13420,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>630101</v>
+        <v>630329</v>
       </c>
       <c r="R121" t="n">
-        <v>6967092</v>
+        <v>6967216</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13455,7 +13455,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13492,10 +13492,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133202130</v>
+        <v>133202149</v>
       </c>
       <c r="B122" t="n">
-        <v>83181</v>
+        <v>79366</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13503,21 +13503,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13527,10 +13527,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>630275</v>
+        <v>630102</v>
       </c>
       <c r="R122" t="n">
-        <v>6967143</v>
+        <v>6967124</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13599,10 +13599,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133202149</v>
+        <v>133202137</v>
       </c>
       <c r="B123" t="n">
-        <v>79365</v>
+        <v>92219</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13610,21 +13610,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13634,10 +13634,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>630102</v>
+        <v>630158</v>
       </c>
       <c r="R123" t="n">
-        <v>6967124</v>
+        <v>6967093</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13709,7 +13709,7 @@
         <v>133202157</v>
       </c>
       <c r="B124" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13813,10 +13813,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133202137</v>
+        <v>133202136</v>
       </c>
       <c r="B125" t="n">
-        <v>92217</v>
+        <v>79334</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13824,21 +13824,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>630158</v>
+        <v>630184</v>
       </c>
       <c r="R125" t="n">
-        <v>6967093</v>
+        <v>6967090</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13920,10 +13920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133202136</v>
+        <v>133202130</v>
       </c>
       <c r="B126" t="n">
-        <v>79333</v>
+        <v>83182</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13931,21 +13931,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>630184</v>
+        <v>630275</v>
       </c>
       <c r="R126" t="n">
-        <v>6967090</v>
+        <v>6967143</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14030,7 +14030,7 @@
         <v>133202131</v>
       </c>
       <c r="B127" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>133202133</v>
       </c>
       <c r="B128" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>133240046</v>
       </c>
       <c r="B129" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>133240023</v>
       </c>
       <c r="B130" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14455,10 +14455,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133240027</v>
+        <v>133240011</v>
       </c>
       <c r="B131" t="n">
-        <v>79333</v>
+        <v>79366</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14466,21 +14466,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>630159</v>
+        <v>630186</v>
       </c>
       <c r="R131" t="n">
-        <v>6967184</v>
+        <v>6967049</v>
       </c>
       <c r="S131" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14562,10 +14562,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133240011</v>
+        <v>133240026</v>
       </c>
       <c r="B132" t="n">
-        <v>79365</v>
+        <v>91870</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14573,21 +14573,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14597,10 +14597,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>630186</v>
+        <v>630151</v>
       </c>
       <c r="R132" t="n">
-        <v>6967049</v>
+        <v>6967182</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14669,10 +14669,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133240026</v>
+        <v>133240027</v>
       </c>
       <c r="B133" t="n">
-        <v>91868</v>
+        <v>79334</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14680,21 +14680,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14704,13 +14704,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>630151</v>
+        <v>630159</v>
       </c>
       <c r="R133" t="n">
-        <v>6967182</v>
+        <v>6967184</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14779,7 +14779,7 @@
         <v>133240044</v>
       </c>
       <c r="B134" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>133240019</v>
       </c>
       <c r="B135" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>133240006</v>
       </c>
       <c r="B136" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>133240003</v>
       </c>
       <c r="B137" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>133240009</v>
       </c>
       <c r="B138" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>133240034</v>
       </c>
       <c r="B139" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15418,10 +15418,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133240037</v>
+        <v>133240004</v>
       </c>
       <c r="B140" t="n">
-        <v>79333</v>
+        <v>79366</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15429,21 +15429,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15453,10 +15453,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>630379</v>
+        <v>630287</v>
       </c>
       <c r="R140" t="n">
-        <v>6967127</v>
+        <v>6967110</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15525,10 +15525,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133240030</v>
+        <v>133240037</v>
       </c>
       <c r="B141" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15560,13 +15560,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>630210</v>
+        <v>630379</v>
       </c>
       <c r="R141" t="n">
-        <v>6967208</v>
+        <v>6967127</v>
       </c>
       <c r="S141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15632,10 +15632,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133240004</v>
+        <v>133240030</v>
       </c>
       <c r="B142" t="n">
-        <v>79365</v>
+        <v>79334</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15643,21 +15643,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15667,13 +15667,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>630287</v>
+        <v>630210</v>
       </c>
       <c r="R142" t="n">
-        <v>6967110</v>
+        <v>6967208</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15742,7 +15742,7 @@
         <v>133240010</v>
       </c>
       <c r="B143" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>133240005</v>
       </c>
       <c r="B144" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>133240032</v>
       </c>
       <c r="B145" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>133240008</v>
       </c>
       <c r="B146" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>133240020</v>
       </c>
       <c r="B147" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>133240042</v>
       </c>
       <c r="B149" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16509,10 +16509,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133240038</v>
+        <v>133240024</v>
       </c>
       <c r="B150" t="n">
-        <v>79333</v>
+        <v>79366</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16520,21 +16520,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16544,13 +16544,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>630337</v>
+        <v>630079</v>
       </c>
       <c r="R150" t="n">
-        <v>6967201</v>
+        <v>6967088</v>
       </c>
       <c r="S150" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16616,10 +16616,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133240024</v>
+        <v>133240038</v>
       </c>
       <c r="B151" t="n">
-        <v>79365</v>
+        <v>79334</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16627,21 +16627,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16651,13 +16651,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>630079</v>
+        <v>630337</v>
       </c>
       <c r="R151" t="n">
-        <v>6967088</v>
+        <v>6967201</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16723,10 +16723,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133240022</v>
+        <v>133240002</v>
       </c>
       <c r="B152" t="n">
-        <v>79333</v>
+        <v>79366</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16734,21 +16734,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16758,10 +16758,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>630082</v>
+        <v>630334</v>
       </c>
       <c r="R152" t="n">
-        <v>6967056</v>
+        <v>6967084</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16830,10 +16830,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133240033</v>
+        <v>133240022</v>
       </c>
       <c r="B153" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16865,10 +16865,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>630273</v>
+        <v>630082</v>
       </c>
       <c r="R153" t="n">
-        <v>6967142</v>
+        <v>6967056</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -16900,7 +16900,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16937,10 +16937,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133240002</v>
+        <v>133240033</v>
       </c>
       <c r="B154" t="n">
-        <v>79365</v>
+        <v>79334</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16948,21 +16948,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16972,10 +16972,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>630334</v>
+        <v>630273</v>
       </c>
       <c r="R154" t="n">
-        <v>6967084</v>
+        <v>6967142</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -17007,7 +17007,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17017,7 +17017,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17047,7 +17047,7 @@
         <v>133240040</v>
       </c>
       <c r="B155" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>133240043</v>
       </c>
       <c r="B156" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>133240013</v>
       </c>
       <c r="B157" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17365,10 +17365,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133240036</v>
+        <v>133240039</v>
       </c>
       <c r="B158" t="n">
-        <v>79333</v>
+        <v>89302</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17376,21 +17376,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17400,10 +17400,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>630368</v>
+        <v>630317</v>
       </c>
       <c r="R158" t="n">
-        <v>6967120</v>
+        <v>6967329</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -17435,7 +17435,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17472,10 +17472,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>133240028</v>
+        <v>133240007</v>
       </c>
       <c r="B159" t="n">
-        <v>79333</v>
+        <v>79366</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17483,21 +17483,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17507,13 +17507,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>630174</v>
+        <v>630244</v>
       </c>
       <c r="R159" t="n">
-        <v>6967208</v>
+        <v>6967085</v>
       </c>
       <c r="S159" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17579,10 +17579,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133240025</v>
+        <v>133240036</v>
       </c>
       <c r="B160" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17614,10 +17614,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>630103</v>
+        <v>630368</v>
       </c>
       <c r="R160" t="n">
-        <v>6967179</v>
+        <v>6967120</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17686,10 +17686,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133240039</v>
+        <v>133240028</v>
       </c>
       <c r="B161" t="n">
-        <v>89300</v>
+        <v>79334</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17697,21 +17697,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17721,10 +17721,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>630317</v>
+        <v>630174</v>
       </c>
       <c r="R161" t="n">
-        <v>6967329</v>
+        <v>6967208</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17793,10 +17793,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133240007</v>
+        <v>133240025</v>
       </c>
       <c r="B162" t="n">
-        <v>79365</v>
+        <v>79334</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17804,21 +17804,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17828,13 +17828,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>630244</v>
+        <v>630103</v>
       </c>
       <c r="R162" t="n">
-        <v>6967085</v>
+        <v>6967179</v>
       </c>
       <c r="S162" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17903,7 +17903,7 @@
         <v>133240021</v>
       </c>
       <c r="B163" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>133240031</v>
       </c>
       <c r="B164" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18114,10 +18114,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133240041</v>
+        <v>133240029</v>
       </c>
       <c r="B165" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18125,21 +18125,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18149,10 +18149,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>630250</v>
+        <v>630179</v>
       </c>
       <c r="R165" t="n">
-        <v>6967366</v>
+        <v>6967208</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18221,10 +18221,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133240018</v>
+        <v>133240041</v>
       </c>
       <c r="B166" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18256,10 +18256,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>630148</v>
+        <v>630250</v>
       </c>
       <c r="R166" t="n">
-        <v>6967065</v>
+        <v>6967366</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18328,10 +18328,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>133240029</v>
+        <v>133240018</v>
       </c>
       <c r="B167" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18339,21 +18339,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18363,10 +18363,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>630179</v>
+        <v>630148</v>
       </c>
       <c r="R167" t="n">
-        <v>6967208</v>
+        <v>6967065</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -6271,10 +6271,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133152208</v>
+        <v>133152168</v>
       </c>
       <c r="B55" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6282,21 +6282,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6306,13 +6306,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630207</v>
+        <v>630316</v>
       </c>
       <c r="R55" t="n">
-        <v>6967295</v>
+        <v>6967112</v>
       </c>
       <c r="S55" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6378,10 +6378,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133152238</v>
+        <v>133152208</v>
       </c>
       <c r="B56" t="n">
-        <v>83182</v>
+        <v>79334</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6389,21 +6389,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6413,13 +6413,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630180</v>
+        <v>630207</v>
       </c>
       <c r="R56" t="n">
-        <v>6967130</v>
+        <v>6967295</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6485,32 +6485,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133152183</v>
+        <v>133152238</v>
       </c>
       <c r="B57" t="n">
-        <v>75433</v>
+        <v>83182</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6426</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6520,13 +6520,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>630308</v>
+        <v>630180</v>
       </c>
       <c r="R57" t="n">
-        <v>6967259</v>
+        <v>6967130</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6592,32 +6592,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133152168</v>
+        <v>133152183</v>
       </c>
       <c r="B58" t="n">
-        <v>79366</v>
+        <v>75433</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6627,13 +6627,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>630316</v>
+        <v>630308</v>
       </c>
       <c r="R58" t="n">
-        <v>6967112</v>
+        <v>6967259</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8851,10 +8851,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133152169</v>
+        <v>133152228</v>
       </c>
       <c r="B79" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8862,21 +8862,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8886,10 +8886,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>630316</v>
+        <v>630092</v>
       </c>
       <c r="R79" t="n">
-        <v>6967112</v>
+        <v>6967142</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8958,7 +8958,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133152170</v>
+        <v>133152169</v>
       </c>
       <c r="B80" t="n">
         <v>79334</v>
@@ -8993,10 +8993,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>630313</v>
+        <v>630316</v>
       </c>
       <c r="R80" t="n">
-        <v>6967117</v>
+        <v>6967112</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9065,10 +9065,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133152207</v>
+        <v>133152170</v>
       </c>
       <c r="B81" t="n">
-        <v>58119</v>
+        <v>79334</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9076,46 +9076,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>630231</v>
+        <v>630313</v>
       </c>
       <c r="R81" t="n">
-        <v>6967249</v>
+        <v>6967117</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9147,7 +9135,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9157,7 +9145,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9184,10 +9172,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133152228</v>
+        <v>133152207</v>
       </c>
       <c r="B82" t="n">
-        <v>79366</v>
+        <v>58119</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9195,34 +9183,46 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>630092</v>
+        <v>630231</v>
       </c>
       <c r="R82" t="n">
-        <v>6967142</v>
+        <v>6967249</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10468,32 +10468,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133202148</v>
+        <v>133202173</v>
       </c>
       <c r="B94" t="n">
-        <v>79334</v>
+        <v>92643</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>630099</v>
+        <v>630299</v>
       </c>
       <c r="R94" t="n">
-        <v>6967120</v>
+        <v>6967218</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10575,10 +10575,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133202168</v>
+        <v>133202148</v>
       </c>
       <c r="B95" t="n">
-        <v>83182</v>
+        <v>79334</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10586,21 +10586,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>630290</v>
+        <v>630099</v>
       </c>
       <c r="R95" t="n">
-        <v>6967317</v>
+        <v>6967120</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10682,32 +10682,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133202173</v>
+        <v>133202168</v>
       </c>
       <c r="B96" t="n">
-        <v>92643</v>
+        <v>83182</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10717,10 +10717,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>630299</v>
+        <v>630290</v>
       </c>
       <c r="R96" t="n">
-        <v>6967218</v>
+        <v>6967317</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11981,32 +11981,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133202172</v>
+        <v>133202156</v>
       </c>
       <c r="B108" t="n">
-        <v>79366</v>
+        <v>92380</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12016,13 +12016,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>630285</v>
+        <v>630219</v>
       </c>
       <c r="R108" t="n">
-        <v>6967276</v>
+        <v>6967208</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133202161</v>
+        <v>133202172</v>
       </c>
       <c r="B109" t="n">
-        <v>91920</v>
+        <v>79366</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12099,21 +12099,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12123,10 +12123,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>630352</v>
+        <v>630285</v>
       </c>
       <c r="R109" t="n">
-        <v>6967119</v>
+        <v>6967276</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12195,10 +12195,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133202139</v>
+        <v>133202161</v>
       </c>
       <c r="B110" t="n">
-        <v>91934</v>
+        <v>91920</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12206,21 +12206,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12230,10 +12230,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>630104</v>
+        <v>630352</v>
       </c>
       <c r="R110" t="n">
-        <v>6967096</v>
+        <v>6967119</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12302,32 +12302,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133202156</v>
+        <v>133202139</v>
       </c>
       <c r="B111" t="n">
-        <v>92380</v>
+        <v>91934</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12337,13 +12337,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>630219</v>
+        <v>630104</v>
       </c>
       <c r="R111" t="n">
-        <v>6967208</v>
+        <v>6967096</v>
       </c>
       <c r="S111" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13706,10 +13706,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133202157</v>
+        <v>133202136</v>
       </c>
       <c r="B124" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13717,21 +13717,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>630257</v>
+        <v>630184</v>
       </c>
       <c r="R124" t="n">
-        <v>6967180</v>
+        <v>6967090</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13813,10 +13813,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133202136</v>
+        <v>133202130</v>
       </c>
       <c r="B125" t="n">
-        <v>79334</v>
+        <v>83182</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13824,21 +13824,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>630184</v>
+        <v>630275</v>
       </c>
       <c r="R125" t="n">
-        <v>6967090</v>
+        <v>6967143</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13920,10 +13920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133202130</v>
+        <v>133202157</v>
       </c>
       <c r="B126" t="n">
-        <v>83182</v>
+        <v>91920</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13931,21 +13931,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>630275</v>
+        <v>630257</v>
       </c>
       <c r="R126" t="n">
-        <v>6967143</v>
+        <v>6967180</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -16509,10 +16509,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133240024</v>
+        <v>133240038</v>
       </c>
       <c r="B150" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16520,21 +16520,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16544,13 +16544,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>630079</v>
+        <v>630337</v>
       </c>
       <c r="R150" t="n">
-        <v>6967088</v>
+        <v>6967201</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16616,10 +16616,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133240038</v>
+        <v>133240024</v>
       </c>
       <c r="B151" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16627,21 +16627,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16651,13 +16651,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>630337</v>
+        <v>630079</v>
       </c>
       <c r="R151" t="n">
-        <v>6967201</v>
+        <v>6967088</v>
       </c>
       <c r="S151" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD151" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -6271,10 +6271,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133152168</v>
+        <v>133152208</v>
       </c>
       <c r="B55" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6282,21 +6282,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6306,13 +6306,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630316</v>
+        <v>630207</v>
       </c>
       <c r="R55" t="n">
-        <v>6967112</v>
+        <v>6967295</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6378,10 +6378,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133152208</v>
+        <v>133152238</v>
       </c>
       <c r="B56" t="n">
-        <v>79334</v>
+        <v>83182</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6389,21 +6389,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6413,13 +6413,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630207</v>
+        <v>630180</v>
       </c>
       <c r="R56" t="n">
-        <v>6967295</v>
+        <v>6967130</v>
       </c>
       <c r="S56" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6485,32 +6485,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133152238</v>
+        <v>133152183</v>
       </c>
       <c r="B57" t="n">
-        <v>83182</v>
+        <v>75433</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>6426</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6520,13 +6520,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>630180</v>
+        <v>630308</v>
       </c>
       <c r="R57" t="n">
-        <v>6967130</v>
+        <v>6967259</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6592,32 +6592,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133152183</v>
+        <v>133152168</v>
       </c>
       <c r="B58" t="n">
-        <v>75433</v>
+        <v>79366</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6627,13 +6627,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>630308</v>
+        <v>630316</v>
       </c>
       <c r="R58" t="n">
-        <v>6967259</v>
+        <v>6967112</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8851,10 +8851,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133152228</v>
+        <v>133152169</v>
       </c>
       <c r="B79" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8862,21 +8862,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8886,10 +8886,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>630092</v>
+        <v>630316</v>
       </c>
       <c r="R79" t="n">
-        <v>6967142</v>
+        <v>6967112</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8958,7 +8958,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133152169</v>
+        <v>133152170</v>
       </c>
       <c r="B80" t="n">
         <v>79334</v>
@@ -8993,10 +8993,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>630316</v>
+        <v>630313</v>
       </c>
       <c r="R80" t="n">
-        <v>6967112</v>
+        <v>6967117</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9065,10 +9065,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133152170</v>
+        <v>133152207</v>
       </c>
       <c r="B81" t="n">
-        <v>79334</v>
+        <v>58119</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9076,34 +9076,46 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>630313</v>
+        <v>630231</v>
       </c>
       <c r="R81" t="n">
-        <v>6967117</v>
+        <v>6967249</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9135,7 +9147,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9145,7 +9157,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9172,10 +9184,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133152207</v>
+        <v>133152228</v>
       </c>
       <c r="B82" t="n">
-        <v>58119</v>
+        <v>79366</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9183,46 +9195,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>630231</v>
+        <v>630092</v>
       </c>
       <c r="R82" t="n">
-        <v>6967249</v>
+        <v>6967142</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11217,54 +11217,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133202127</v>
+        <v>133202169</v>
       </c>
       <c r="B101" t="n">
-        <v>5199</v>
+        <v>91934</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>105930</v>
+        <v>1204</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>630318</v>
+        <v>630259</v>
       </c>
       <c r="R101" t="n">
-        <v>6967099</v>
+        <v>6967344</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11296,7 +11287,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11306,12 +11297,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11320,7 +11306,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11339,10 +11324,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133202169</v>
+        <v>133202151</v>
       </c>
       <c r="B102" t="n">
-        <v>91934</v>
+        <v>83182</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11350,21 +11335,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11374,10 +11359,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>630259</v>
+        <v>630118</v>
       </c>
       <c r="R102" t="n">
-        <v>6967344</v>
+        <v>6967158</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11409,7 +11394,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11419,7 +11404,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11446,45 +11431,54 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133202151</v>
+        <v>133202127</v>
       </c>
       <c r="B103" t="n">
-        <v>83182</v>
+        <v>5199</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1312</v>
+        <v>105930</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>630118</v>
+        <v>630318</v>
       </c>
       <c r="R103" t="n">
-        <v>6967158</v>
+        <v>6967099</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11516,7 +11510,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11526,7 +11520,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11535,6 +11534,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133202152</v>
+        <v>133202159</v>
       </c>
       <c r="B104" t="n">
-        <v>79366</v>
+        <v>91934</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>630108</v>
+        <v>630290</v>
       </c>
       <c r="R104" t="n">
-        <v>6967186</v>
+        <v>6967123</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11660,10 +11660,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133202125</v>
+        <v>133202171</v>
       </c>
       <c r="B105" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11671,21 +11671,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>630331</v>
+        <v>630271</v>
       </c>
       <c r="R105" t="n">
-        <v>6967087</v>
+        <v>6967309</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11767,10 +11767,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133202159</v>
+        <v>133202152</v>
       </c>
       <c r="B106" t="n">
-        <v>91934</v>
+        <v>79366</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11778,21 +11778,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>630290</v>
+        <v>630108</v>
       </c>
       <c r="R106" t="n">
-        <v>6967123</v>
+        <v>6967186</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11874,10 +11874,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133202171</v>
+        <v>133202125</v>
       </c>
       <c r="B107" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>630271</v>
+        <v>630331</v>
       </c>
       <c r="R107" t="n">
-        <v>6967309</v>
+        <v>6967087</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13051,45 +13051,53 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133202170</v>
+        <v>133202138</v>
       </c>
       <c r="B118" t="n">
-        <v>79358</v>
+        <v>57136</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6434</v>
+        <v>102612</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>630274</v>
+        <v>630143</v>
       </c>
       <c r="R118" t="n">
-        <v>6967318</v>
+        <v>6967085</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13121,7 +13129,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13131,7 +13139,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Sannolikt tagen av en rovfågel.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13158,53 +13171,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133202138</v>
+        <v>133202170</v>
       </c>
       <c r="B119" t="n">
-        <v>57136</v>
+        <v>79358</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>102612</v>
+        <v>6434</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>630143</v>
+        <v>630274</v>
       </c>
       <c r="R119" t="n">
-        <v>6967085</v>
+        <v>6967318</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13236,7 +13241,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13246,12 +13251,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Sannolikt tagen av en rovfågel.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14027,10 +14027,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133202131</v>
+        <v>133202133</v>
       </c>
       <c r="B127" t="n">
-        <v>83182</v>
+        <v>83316</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14038,21 +14038,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14062,10 +14062,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>630252</v>
+        <v>630226</v>
       </c>
       <c r="R127" t="n">
-        <v>6967151</v>
+        <v>6967128</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14097,7 +14097,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14134,10 +14134,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133202133</v>
+        <v>133202131</v>
       </c>
       <c r="B128" t="n">
-        <v>83316</v>
+        <v>83182</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14145,21 +14145,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14169,10 +14169,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>630226</v>
+        <v>630252</v>
       </c>
       <c r="R128" t="n">
-        <v>6967128</v>
+        <v>6967151</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15525,10 +15525,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133240037</v>
+        <v>133240010</v>
       </c>
       <c r="B141" t="n">
-        <v>79334</v>
+        <v>91920</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15536,21 +15536,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15560,10 +15560,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>630379</v>
+        <v>630202</v>
       </c>
       <c r="R141" t="n">
-        <v>6967127</v>
+        <v>6967062</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15632,7 +15632,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133240030</v>
+        <v>133240037</v>
       </c>
       <c r="B142" t="n">
         <v>79334</v>
@@ -15667,13 +15667,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>630210</v>
+        <v>630379</v>
       </c>
       <c r="R142" t="n">
-        <v>6967208</v>
+        <v>6967127</v>
       </c>
       <c r="S142" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15739,10 +15739,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133240010</v>
+        <v>133240030</v>
       </c>
       <c r="B143" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15750,21 +15750,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15774,13 +15774,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>630202</v>
+        <v>630210</v>
       </c>
       <c r="R143" t="n">
-        <v>6967062</v>
+        <v>6967208</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD143" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133152204</v>
+        <v>133152237</v>
       </c>
       <c r="B11" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630265</v>
+        <v>630189</v>
       </c>
       <c r="R11" t="n">
-        <v>6967240</v>
+        <v>6967121</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1638,7 +1638,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133152222</v>
+        <v>133152204</v>
       </c>
       <c r="B12" t="n">
-        <v>83182</v>
+        <v>91928</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630156</v>
+        <v>630265</v>
       </c>
       <c r="R12" t="n">
-        <v>6967155</v>
+        <v>6967240</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1735,7 +1740,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1745,7 +1750,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1772,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133152237</v>
+        <v>133152222</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>83183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,21 +1788,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1807,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630189</v>
+        <v>630156</v>
       </c>
       <c r="R13" t="n">
-        <v>6967121</v>
+        <v>6967155</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1842,7 +1847,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1852,12 +1857,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,7 +1887,7 @@
         <v>133152220</v>
       </c>
       <c r="B14" t="n">
-        <v>91934</v>
+        <v>91942</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>133152217</v>
       </c>
       <c r="B15" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,10 +2098,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133152225</v>
+        <v>133152165</v>
       </c>
       <c r="B16" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2109,21 +2109,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630153</v>
+        <v>630325</v>
       </c>
       <c r="R16" t="n">
-        <v>6967136</v>
+        <v>6967107</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,32 +2205,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133152246</v>
+        <v>133152185</v>
       </c>
       <c r="B17" t="n">
-        <v>79366</v>
+        <v>91891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630264</v>
+        <v>630303</v>
       </c>
       <c r="R17" t="n">
-        <v>6967100</v>
+        <v>6967279</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133152163</v>
+        <v>133152205</v>
       </c>
       <c r="B18" t="n">
-        <v>79366</v>
+        <v>92227</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630334</v>
+        <v>630269</v>
       </c>
       <c r="R18" t="n">
-        <v>6967097</v>
+        <v>6967234</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2419,32 +2419,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133152185</v>
+        <v>133152225</v>
       </c>
       <c r="B19" t="n">
-        <v>91883</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630303</v>
+        <v>630153</v>
       </c>
       <c r="R19" t="n">
-        <v>6967279</v>
+        <v>6967136</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133152205</v>
+        <v>133152246</v>
       </c>
       <c r="B20" t="n">
-        <v>92219</v>
+        <v>79366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630269</v>
+        <v>630264</v>
       </c>
       <c r="R20" t="n">
-        <v>6967234</v>
+        <v>6967100</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133152165</v>
+        <v>133152174</v>
       </c>
       <c r="B21" t="n">
-        <v>79334</v>
+        <v>83183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630325</v>
+        <v>630286</v>
       </c>
       <c r="R21" t="n">
-        <v>6967107</v>
+        <v>6967149</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>05:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>05:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2740,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133152174</v>
+        <v>133152163</v>
       </c>
       <c r="B22" t="n">
-        <v>83182</v>
+        <v>79366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630286</v>
+        <v>630334</v>
       </c>
       <c r="R22" t="n">
-        <v>6967149</v>
+        <v>6967097</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2850,7 +2850,7 @@
         <v>133152218</v>
       </c>
       <c r="B23" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2954,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133152231</v>
+        <v>133152226</v>
       </c>
       <c r="B24" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630146</v>
+        <v>630154</v>
       </c>
       <c r="R24" t="n">
-        <v>6967080</v>
+        <v>6967129</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133152226</v>
+        <v>133152231</v>
       </c>
       <c r="B25" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630154</v>
+        <v>630146</v>
       </c>
       <c r="R25" t="n">
-        <v>6967129</v>
+        <v>6967080</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3168,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133152161</v>
+        <v>133152221</v>
       </c>
       <c r="B26" t="n">
-        <v>79366</v>
+        <v>91928</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,21 +3179,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3203,10 +3203,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630345</v>
+        <v>630134</v>
       </c>
       <c r="R26" t="n">
-        <v>6967095</v>
+        <v>6967158</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>04:42</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>04:42</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3275,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133152221</v>
+        <v>133152161</v>
       </c>
       <c r="B27" t="n">
-        <v>91920</v>
+        <v>79366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630134</v>
+        <v>630345</v>
       </c>
       <c r="R27" t="n">
-        <v>6967158</v>
+        <v>6967095</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>04:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>04:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3385,7 +3385,7 @@
         <v>133152224</v>
       </c>
       <c r="B28" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3489,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133152184</v>
+        <v>133152173</v>
       </c>
       <c r="B29" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,21 +3500,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630304</v>
+        <v>630300</v>
       </c>
       <c r="R29" t="n">
-        <v>6967273</v>
+        <v>6967133</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3599,7 +3599,7 @@
         <v>133152188</v>
       </c>
       <c r="B30" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133152173</v>
+        <v>133152184</v>
       </c>
       <c r="B31" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630300</v>
+        <v>630304</v>
       </c>
       <c r="R31" t="n">
-        <v>6967133</v>
+        <v>6967273</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3813,7 +3813,7 @@
         <v>133152203</v>
       </c>
       <c r="B32" t="n">
-        <v>91934</v>
+        <v>91942</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>133152193</v>
       </c>
       <c r="B33" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133152234</v>
+        <v>133152206</v>
       </c>
       <c r="B34" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630161</v>
+        <v>630256</v>
       </c>
       <c r="R34" t="n">
-        <v>6967098</v>
+        <v>6967220</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4131,7 +4131,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133152164</v>
+        <v>133152234</v>
       </c>
       <c r="B35" t="n">
         <v>79366</v>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630325</v>
+        <v>630161</v>
       </c>
       <c r="R35" t="n">
-        <v>6967107</v>
+        <v>6967098</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4238,7 +4238,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133152167</v>
+        <v>133152164</v>
       </c>
       <c r="B36" t="n">
         <v>79366</v>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630318</v>
+        <v>630325</v>
       </c>
       <c r="R36" t="n">
-        <v>6967112</v>
+        <v>6967107</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>04:51</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>04:51</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4345,10 +4345,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133152206</v>
+        <v>133152167</v>
       </c>
       <c r="B37" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4356,21 +4356,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630256</v>
+        <v>630318</v>
       </c>
       <c r="R37" t="n">
-        <v>6967220</v>
+        <v>6967112</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4559,10 +4559,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133152243</v>
+        <v>133152178</v>
       </c>
       <c r="B39" t="n">
-        <v>83182</v>
+        <v>79366</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,21 +4570,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4594,13 +4594,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630223</v>
+        <v>630300</v>
       </c>
       <c r="R39" t="n">
-        <v>6967132</v>
+        <v>6967148</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>05:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>05:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4666,10 +4666,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133152196</v>
+        <v>133152243</v>
       </c>
       <c r="B40" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630299</v>
+        <v>630223</v>
       </c>
       <c r="R40" t="n">
-        <v>6967344</v>
+        <v>6967132</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4773,10 +4773,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133152210</v>
+        <v>133152196</v>
       </c>
       <c r="B41" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>630184</v>
+        <v>630299</v>
       </c>
       <c r="R41" t="n">
-        <v>6967161</v>
+        <v>6967344</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4880,10 +4880,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133152178</v>
+        <v>133152210</v>
       </c>
       <c r="B42" t="n">
-        <v>79366</v>
+        <v>83183</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4891,21 +4891,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4915,13 +4915,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630300</v>
+        <v>630184</v>
       </c>
       <c r="R42" t="n">
-        <v>6967148</v>
+        <v>6967161</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>05:16</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>05:16</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4987,32 +4987,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133152201</v>
+        <v>133152195</v>
       </c>
       <c r="B43" t="n">
-        <v>91920</v>
+        <v>75433</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630261</v>
+        <v>630297</v>
       </c>
       <c r="R43" t="n">
-        <v>6967251</v>
+        <v>6967347</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5094,32 +5094,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133152195</v>
+        <v>133152216</v>
       </c>
       <c r="B44" t="n">
-        <v>75433</v>
+        <v>79334</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630297</v>
+        <v>630149</v>
       </c>
       <c r="R44" t="n">
-        <v>6967347</v>
+        <v>6967241</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5201,32 +5201,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133152216</v>
+        <v>133152197</v>
       </c>
       <c r="B45" t="n">
-        <v>79334</v>
+        <v>75433</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630149</v>
+        <v>630298</v>
       </c>
       <c r="R45" t="n">
-        <v>6967241</v>
+        <v>6967342</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5308,32 +5308,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133152197</v>
+        <v>133152201</v>
       </c>
       <c r="B46" t="n">
-        <v>75433</v>
+        <v>91928</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5343,10 +5343,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630298</v>
+        <v>630261</v>
       </c>
       <c r="R46" t="n">
-        <v>6967342</v>
+        <v>6967251</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5415,10 +5415,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133152159</v>
+        <v>133152241</v>
       </c>
       <c r="B47" t="n">
-        <v>79366</v>
+        <v>83183</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,21 +5426,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5450,13 +5450,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>630350</v>
+        <v>630259</v>
       </c>
       <c r="R47" t="n">
-        <v>6967090</v>
+        <v>6967135</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5522,7 +5522,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133152198</v>
+        <v>133152159</v>
       </c>
       <c r="B48" t="n">
         <v>79366</v>
@@ -5557,13 +5557,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>630231</v>
+        <v>630350</v>
       </c>
       <c r="R48" t="n">
-        <v>6967393</v>
+        <v>6967090</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5629,7 +5629,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133152232</v>
+        <v>133152198</v>
       </c>
       <c r="B49" t="n">
         <v>79366</v>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>630147</v>
+        <v>630231</v>
       </c>
       <c r="R49" t="n">
-        <v>6967088</v>
+        <v>6967393</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5736,10 +5736,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133152241</v>
+        <v>133152232</v>
       </c>
       <c r="B50" t="n">
-        <v>83182</v>
+        <v>79366</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5747,21 +5747,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>630259</v>
+        <v>630147</v>
       </c>
       <c r="R50" t="n">
-        <v>6967135</v>
+        <v>6967088</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5843,10 +5843,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133152189</v>
+        <v>133152209</v>
       </c>
       <c r="B51" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5854,21 +5854,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>630270</v>
+        <v>630184</v>
       </c>
       <c r="R51" t="n">
-        <v>6967330</v>
+        <v>6967242</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>05:56</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>05:56</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5950,10 +5950,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133152235</v>
+        <v>133152189</v>
       </c>
       <c r="B52" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>630162</v>
+        <v>630270</v>
       </c>
       <c r="R52" t="n">
-        <v>6967096</v>
+        <v>6967330</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>05:56</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>05:56</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6057,10 +6057,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133152209</v>
+        <v>133152235</v>
       </c>
       <c r="B53" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6068,21 +6068,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>630184</v>
+        <v>630162</v>
       </c>
       <c r="R53" t="n">
-        <v>6967242</v>
+        <v>6967096</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6167,7 +6167,7 @@
         <v>133152194</v>
       </c>
       <c r="B54" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6378,32 +6378,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133152238</v>
+        <v>133152183</v>
       </c>
       <c r="B56" t="n">
-        <v>83182</v>
+        <v>75433</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>6426</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6413,13 +6413,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630180</v>
+        <v>630308</v>
       </c>
       <c r="R56" t="n">
-        <v>6967130</v>
+        <v>6967259</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6485,32 +6485,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133152183</v>
+        <v>133152238</v>
       </c>
       <c r="B57" t="n">
-        <v>75433</v>
+        <v>83183</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6426</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6520,13 +6520,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>630308</v>
+        <v>630180</v>
       </c>
       <c r="R57" t="n">
-        <v>6967259</v>
+        <v>6967130</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6699,10 +6699,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133152215</v>
+        <v>133152175</v>
       </c>
       <c r="B59" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6710,21 +6710,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6734,13 +6734,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630159</v>
+        <v>630308</v>
       </c>
       <c r="R59" t="n">
-        <v>6967229</v>
+        <v>6967163</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6806,7 +6806,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133152175</v>
+        <v>133152191</v>
       </c>
       <c r="B60" t="n">
         <v>79334</v>
@@ -6841,13 +6841,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>630308</v>
+        <v>630272</v>
       </c>
       <c r="R60" t="n">
-        <v>6967163</v>
+        <v>6967349</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6913,10 +6913,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133152239</v>
+        <v>133152180</v>
       </c>
       <c r="B61" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6924,21 +6924,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6948,13 +6948,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>630255</v>
+        <v>630315</v>
       </c>
       <c r="R61" t="n">
-        <v>6967168</v>
+        <v>6967166</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7020,7 +7020,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133152191</v>
+        <v>133152240</v>
       </c>
       <c r="B62" t="n">
         <v>79334</v>
@@ -7055,10 +7055,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630272</v>
+        <v>630263</v>
       </c>
       <c r="R62" t="n">
-        <v>6967349</v>
+        <v>6967142</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7127,10 +7127,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133152180</v>
+        <v>133152215</v>
       </c>
       <c r="B63" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7138,21 +7138,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7162,13 +7162,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>630315</v>
+        <v>630159</v>
       </c>
       <c r="R63" t="n">
-        <v>6967166</v>
+        <v>6967229</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7234,10 +7234,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133152227</v>
+        <v>133152239</v>
       </c>
       <c r="B64" t="n">
-        <v>83182</v>
+        <v>91928</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7245,21 +7245,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>630148</v>
+        <v>630255</v>
       </c>
       <c r="R64" t="n">
-        <v>6967117</v>
+        <v>6967168</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7341,10 +7341,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133152240</v>
+        <v>133152227</v>
       </c>
       <c r="B65" t="n">
-        <v>79334</v>
+        <v>83183</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7352,21 +7352,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>630263</v>
+        <v>630148</v>
       </c>
       <c r="R65" t="n">
-        <v>6967142</v>
+        <v>6967117</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7558,7 +7558,7 @@
         <v>133152219</v>
       </c>
       <c r="B67" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>133152190</v>
       </c>
       <c r="B68" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>133152187</v>
       </c>
       <c r="B72" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>133152200</v>
       </c>
       <c r="B73" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>133152223</v>
       </c>
       <c r="B74" t="n">
-        <v>89302</v>
+        <v>89310</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8423,10 +8423,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133152171</v>
+        <v>133152181</v>
       </c>
       <c r="B75" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8434,21 +8434,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8458,10 +8458,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>630307</v>
+        <v>630334</v>
       </c>
       <c r="R75" t="n">
-        <v>6967118</v>
+        <v>6967171</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8530,10 +8530,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133152212</v>
+        <v>133152182</v>
       </c>
       <c r="B76" t="n">
-        <v>83182</v>
+        <v>79334</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8541,21 +8541,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8565,13 +8565,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>630176</v>
+        <v>630324</v>
       </c>
       <c r="R76" t="n">
-        <v>6967173</v>
+        <v>6967248</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8637,10 +8637,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133152181</v>
+        <v>133152171</v>
       </c>
       <c r="B77" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8648,21 +8648,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>630334</v>
+        <v>630307</v>
       </c>
       <c r="R77" t="n">
-        <v>6967171</v>
+        <v>6967118</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8744,10 +8744,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133152182</v>
+        <v>133152212</v>
       </c>
       <c r="B78" t="n">
-        <v>79334</v>
+        <v>83183</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8755,21 +8755,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8779,13 +8779,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>630324</v>
+        <v>630176</v>
       </c>
       <c r="R78" t="n">
-        <v>6967248</v>
+        <v>6967173</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9065,10 +9065,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133152207</v>
+        <v>133152228</v>
       </c>
       <c r="B81" t="n">
-        <v>58119</v>
+        <v>79366</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9076,46 +9076,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>630231</v>
+        <v>630092</v>
       </c>
       <c r="R81" t="n">
-        <v>6967249</v>
+        <v>6967142</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9147,7 +9135,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9157,7 +9145,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9184,10 +9172,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133152228</v>
+        <v>133152207</v>
       </c>
       <c r="B82" t="n">
-        <v>79366</v>
+        <v>58119</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9195,34 +9183,46 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>630092</v>
+        <v>630231</v>
       </c>
       <c r="R82" t="n">
-        <v>6967142</v>
+        <v>6967249</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9294,7 +9294,7 @@
         <v>133152213</v>
       </c>
       <c r="B83" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>133202135</v>
       </c>
       <c r="B88" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9933,10 +9933,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133202147</v>
+        <v>133202134</v>
       </c>
       <c r="B89" t="n">
-        <v>91934</v>
+        <v>83183</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9944,21 +9944,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>630094</v>
+        <v>630178</v>
       </c>
       <c r="R89" t="n">
-        <v>6967070</v>
+        <v>6967146</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10003,7 +10003,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10040,10 +10040,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133202134</v>
+        <v>133202147</v>
       </c>
       <c r="B90" t="n">
-        <v>83182</v>
+        <v>91942</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10051,21 +10051,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>630178</v>
+        <v>630094</v>
       </c>
       <c r="R90" t="n">
-        <v>6967146</v>
+        <v>6967070</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10150,7 +10150,7 @@
         <v>133202165</v>
       </c>
       <c r="B91" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>133202145</v>
       </c>
       <c r="B92" t="n">
-        <v>91934</v>
+        <v>91942</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10361,10 +10361,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133202155</v>
+        <v>133202148</v>
       </c>
       <c r="B93" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10372,21 +10372,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>630210</v>
+        <v>630099</v>
       </c>
       <c r="R93" t="n">
-        <v>6967196</v>
+        <v>6967120</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10468,32 +10468,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133202173</v>
+        <v>133202155</v>
       </c>
       <c r="B94" t="n">
-        <v>92643</v>
+        <v>91928</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>630299</v>
+        <v>630210</v>
       </c>
       <c r="R94" t="n">
-        <v>6967218</v>
+        <v>6967196</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10575,32 +10575,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133202148</v>
+        <v>133202173</v>
       </c>
       <c r="B95" t="n">
-        <v>79334</v>
+        <v>92651</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>630099</v>
+        <v>630299</v>
       </c>
       <c r="R95" t="n">
-        <v>6967120</v>
+        <v>6967218</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10685,7 +10685,7 @@
         <v>133202168</v>
       </c>
       <c r="B96" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>133202169</v>
       </c>
       <c r="B101" t="n">
-        <v>91934</v>
+        <v>91942</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>133202151</v>
       </c>
       <c r="B102" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>133202159</v>
       </c>
       <c r="B104" t="n">
-        <v>91934</v>
+        <v>91942</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11981,32 +11981,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133202156</v>
+        <v>133202161</v>
       </c>
       <c r="B108" t="n">
-        <v>92380</v>
+        <v>91928</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12016,13 +12016,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>630219</v>
+        <v>630352</v>
       </c>
       <c r="R108" t="n">
-        <v>6967208</v>
+        <v>6967119</v>
       </c>
       <c r="S108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133202172</v>
+        <v>133202139</v>
       </c>
       <c r="B109" t="n">
-        <v>79366</v>
+        <v>91942</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12099,21 +12099,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12123,10 +12123,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>630285</v>
+        <v>630104</v>
       </c>
       <c r="R109" t="n">
-        <v>6967276</v>
+        <v>6967096</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12195,32 +12195,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133202161</v>
+        <v>133202156</v>
       </c>
       <c r="B110" t="n">
-        <v>91920</v>
+        <v>92388</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12230,13 +12230,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>630352</v>
+        <v>630219</v>
       </c>
       <c r="R110" t="n">
-        <v>6967119</v>
+        <v>6967208</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12302,10 +12302,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133202139</v>
+        <v>133202172</v>
       </c>
       <c r="B111" t="n">
-        <v>91934</v>
+        <v>79366</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12313,21 +12313,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12337,10 +12337,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>630104</v>
+        <v>630285</v>
       </c>
       <c r="R111" t="n">
-        <v>6967096</v>
+        <v>6967276</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12412,7 +12412,7 @@
         <v>133202158</v>
       </c>
       <c r="B112" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>133202160</v>
       </c>
       <c r="B113" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>133202132</v>
       </c>
       <c r="B114" t="n">
-        <v>91934</v>
+        <v>91942</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12837,10 +12837,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>133202144</v>
+        <v>133202153</v>
       </c>
       <c r="B116" t="n">
-        <v>79366</v>
+        <v>92227</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12848,21 +12848,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12872,10 +12872,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>630098</v>
+        <v>630160</v>
       </c>
       <c r="R116" t="n">
-        <v>6967075</v>
+        <v>6967163</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12917,7 +12917,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12944,10 +12944,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>133202153</v>
+        <v>133202144</v>
       </c>
       <c r="B117" t="n">
-        <v>92219</v>
+        <v>79366</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12955,21 +12955,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>630160</v>
+        <v>630098</v>
       </c>
       <c r="R117" t="n">
-        <v>6967163</v>
+        <v>6967075</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13278,10 +13278,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133202141</v>
+        <v>133202164</v>
       </c>
       <c r="B120" t="n">
-        <v>89302</v>
+        <v>79334</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13289,21 +13289,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13313,10 +13313,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>630101</v>
+        <v>630329</v>
       </c>
       <c r="R120" t="n">
-        <v>6967092</v>
+        <v>6967216</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13348,7 +13348,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13385,10 +13385,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133202164</v>
+        <v>133202141</v>
       </c>
       <c r="B121" t="n">
-        <v>79334</v>
+        <v>89310</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13396,21 +13396,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13420,10 +13420,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>630329</v>
+        <v>630101</v>
       </c>
       <c r="R121" t="n">
-        <v>6967216</v>
+        <v>6967092</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13455,7 +13455,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13492,10 +13492,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133202149</v>
+        <v>133202130</v>
       </c>
       <c r="B122" t="n">
-        <v>79366</v>
+        <v>83183</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13503,21 +13503,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13527,10 +13527,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>630102</v>
+        <v>630275</v>
       </c>
       <c r="R122" t="n">
-        <v>6967124</v>
+        <v>6967143</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13599,10 +13599,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133202137</v>
+        <v>133202157</v>
       </c>
       <c r="B123" t="n">
-        <v>92219</v>
+        <v>91928</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13610,21 +13610,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13634,10 +13634,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>630158</v>
+        <v>630257</v>
       </c>
       <c r="R123" t="n">
-        <v>6967093</v>
+        <v>6967180</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13706,10 +13706,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133202136</v>
+        <v>133202137</v>
       </c>
       <c r="B124" t="n">
-        <v>79334</v>
+        <v>92227</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13717,21 +13717,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>630184</v>
+        <v>630158</v>
       </c>
       <c r="R124" t="n">
-        <v>6967090</v>
+        <v>6967093</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13813,10 +13813,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133202130</v>
+        <v>133202136</v>
       </c>
       <c r="B125" t="n">
-        <v>83182</v>
+        <v>79334</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13824,21 +13824,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>630275</v>
+        <v>630184</v>
       </c>
       <c r="R125" t="n">
-        <v>6967143</v>
+        <v>6967090</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13920,10 +13920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133202157</v>
+        <v>133202149</v>
       </c>
       <c r="B126" t="n">
-        <v>91920</v>
+        <v>79366</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13931,21 +13931,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>630257</v>
+        <v>630102</v>
       </c>
       <c r="R126" t="n">
-        <v>6967180</v>
+        <v>6967124</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14030,7 +14030,7 @@
         <v>133202133</v>
       </c>
       <c r="B127" t="n">
-        <v>83316</v>
+        <v>83319</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>133202131</v>
       </c>
       <c r="B128" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14455,10 +14455,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133240011</v>
+        <v>133240027</v>
       </c>
       <c r="B131" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14466,21 +14466,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>630186</v>
+        <v>630159</v>
       </c>
       <c r="R131" t="n">
-        <v>6967049</v>
+        <v>6967184</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14562,10 +14562,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133240026</v>
+        <v>133240011</v>
       </c>
       <c r="B132" t="n">
-        <v>91870</v>
+        <v>79366</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14573,21 +14573,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14597,10 +14597,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>630151</v>
+        <v>630186</v>
       </c>
       <c r="R132" t="n">
-        <v>6967182</v>
+        <v>6967049</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14669,10 +14669,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133240027</v>
+        <v>133240026</v>
       </c>
       <c r="B133" t="n">
-        <v>79334</v>
+        <v>91878</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14680,21 +14680,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14704,13 +14704,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>630159</v>
+        <v>630151</v>
       </c>
       <c r="R133" t="n">
-        <v>6967184</v>
+        <v>6967182</v>
       </c>
       <c r="S133" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14776,7 +14776,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133240044</v>
+        <v>133240019</v>
       </c>
       <c r="B134" t="n">
         <v>79334</v>
@@ -14811,10 +14811,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>630257</v>
+        <v>630164</v>
       </c>
       <c r="R134" t="n">
-        <v>6967346</v>
+        <v>6967058</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14846,7 +14846,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14883,7 +14883,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133240019</v>
+        <v>133240044</v>
       </c>
       <c r="B135" t="n">
         <v>79334</v>
@@ -14918,10 +14918,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>630164</v>
+        <v>630257</v>
       </c>
       <c r="R135" t="n">
-        <v>6967058</v>
+        <v>6967346</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14990,10 +14990,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133240006</v>
+        <v>133240009</v>
       </c>
       <c r="B136" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15001,21 +15001,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15025,10 +15025,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>630259</v>
+        <v>630210</v>
       </c>
       <c r="R136" t="n">
-        <v>6967095</v>
+        <v>6967061</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -15060,7 +15060,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15070,7 +15070,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15097,10 +15097,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133240003</v>
+        <v>133240034</v>
       </c>
       <c r="B137" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15108,21 +15108,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15132,10 +15132,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>630320</v>
+        <v>630375</v>
       </c>
       <c r="R137" t="n">
-        <v>6967080</v>
+        <v>6967109</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15204,10 +15204,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133240009</v>
+        <v>133240006</v>
       </c>
       <c r="B138" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15215,21 +15215,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15239,10 +15239,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>630210</v>
+        <v>630259</v>
       </c>
       <c r="R138" t="n">
-        <v>6967061</v>
+        <v>6967095</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15311,10 +15311,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133240034</v>
+        <v>133240003</v>
       </c>
       <c r="B139" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>630375</v>
+        <v>630320</v>
       </c>
       <c r="R139" t="n">
-        <v>6967109</v>
+        <v>6967080</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15418,10 +15418,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133240004</v>
+        <v>133240037</v>
       </c>
       <c r="B140" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15429,21 +15429,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15453,10 +15453,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>630287</v>
+        <v>630379</v>
       </c>
       <c r="R140" t="n">
-        <v>6967110</v>
+        <v>6967127</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15528,7 +15528,7 @@
         <v>133240010</v>
       </c>
       <c r="B141" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15632,10 +15632,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133240037</v>
+        <v>133240004</v>
       </c>
       <c r="B142" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15643,21 +15643,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15667,10 +15667,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>630379</v>
+        <v>630287</v>
       </c>
       <c r="R142" t="n">
-        <v>6967127</v>
+        <v>6967110</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15953,10 +15953,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>133240032</v>
+        <v>133240008</v>
       </c>
       <c r="B145" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15964,21 +15964,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15988,10 +15988,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>630247</v>
+        <v>630229</v>
       </c>
       <c r="R145" t="n">
-        <v>6967189</v>
+        <v>6967080</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16060,10 +16060,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133240008</v>
+        <v>133240032</v>
       </c>
       <c r="B146" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16071,21 +16071,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16095,10 +16095,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>630229</v>
+        <v>630247</v>
       </c>
       <c r="R146" t="n">
-        <v>6967080</v>
+        <v>6967189</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16167,10 +16167,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133240020</v>
+        <v>133244099</v>
       </c>
       <c r="B147" t="n">
-        <v>79366</v>
+        <v>57958</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16178,37 +16178,53 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Gillemyrtjärnen, Ång</t>
+          <t>Gillermyrtjärnen, Lomtjärnsåsen, Sela, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>630162</v>
+        <v>630169</v>
       </c>
       <c r="R147" t="n">
-        <v>6967059</v>
+        <v>6967162</v>
       </c>
       <c r="S147" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16237,7 +16253,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16247,7 +16263,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Ljudbox har använts och trummande tretåig hackspett har registrerats. Programmet Audacity har använts för att analysera trumningarna som hördes tidigt på morgonen. Trumningarna är i genomsnitt 1,2 sekunder långa med en slagfrekvens på i genomsnitt 12,7 slag/sekund vilket stämmer väl in på tretåig hackspett. Bifogat finns en del av ljudupptagningen och en bild med ett utmarkerat grönt kryss där genomsnittsvärdena har placerats ut samt ett skärmklipp från analysprogrammet audacity där trumningarna syns.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16274,10 +16295,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133244099</v>
+        <v>133240020</v>
       </c>
       <c r="B148" t="n">
-        <v>57958</v>
+        <v>79366</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16285,53 +16306,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Gillermyrtjärnen, Lomtjärnsåsen, Sela, Ång</t>
+          <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>630169</v>
+        <v>630162</v>
       </c>
       <c r="R148" t="n">
-        <v>6967162</v>
+        <v>6967059</v>
       </c>
       <c r="S148" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16360,7 +16365,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16370,12 +16375,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Ljudbox har använts och trummande tretåig hackspett har registrerats. Programmet Audacity har använts för att analysera trumningarna som hördes tidigt på morgonen. Trumningarna är i genomsnitt 1,2 sekunder långa med en slagfrekvens på i genomsnitt 12,7 slag/sekund vilket stämmer väl in på tretåig hackspett. Bifogat finns en del av ljudupptagningen och en bild med ett utmarkerat grönt kryss där genomsnittsvärdena har placerats ut samt ett skärmklipp från analysprogrammet audacity där trumningarna syns.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16509,10 +16509,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133240038</v>
+        <v>133240024</v>
       </c>
       <c r="B150" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16520,21 +16520,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16544,13 +16544,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>630337</v>
+        <v>630079</v>
       </c>
       <c r="R150" t="n">
-        <v>6967201</v>
+        <v>6967088</v>
       </c>
       <c r="S150" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16616,10 +16616,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133240024</v>
+        <v>133240038</v>
       </c>
       <c r="B151" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16627,21 +16627,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16651,13 +16651,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>630079</v>
+        <v>630337</v>
       </c>
       <c r="R151" t="n">
-        <v>6967088</v>
+        <v>6967201</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16723,10 +16723,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133240002</v>
+        <v>133240022</v>
       </c>
       <c r="B152" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16734,21 +16734,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16758,10 +16758,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>630334</v>
+        <v>630082</v>
       </c>
       <c r="R152" t="n">
-        <v>6967084</v>
+        <v>6967056</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16830,7 +16830,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133240022</v>
+        <v>133240033</v>
       </c>
       <c r="B153" t="n">
         <v>79334</v>
@@ -16865,10 +16865,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>630082</v>
+        <v>630273</v>
       </c>
       <c r="R153" t="n">
-        <v>6967056</v>
+        <v>6967142</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -16900,7 +16900,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16937,10 +16937,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133240033</v>
+        <v>133240002</v>
       </c>
       <c r="B154" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16948,21 +16948,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16972,10 +16972,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>630273</v>
+        <v>630334</v>
       </c>
       <c r="R154" t="n">
-        <v>6967142</v>
+        <v>6967084</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -17007,7 +17007,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17017,7 +17017,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17044,10 +17044,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133240040</v>
+        <v>133240043</v>
       </c>
       <c r="B155" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17055,21 +17055,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17079,10 +17079,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>630295</v>
+        <v>630242</v>
       </c>
       <c r="R155" t="n">
-        <v>6967374</v>
+        <v>6967369</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17151,7 +17151,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133240043</v>
+        <v>133240013</v>
       </c>
       <c r="B156" t="n">
         <v>79334</v>
@@ -17186,10 +17186,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>630242</v>
+        <v>630166</v>
       </c>
       <c r="R156" t="n">
-        <v>6967369</v>
+        <v>6967049</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -17221,7 +17221,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17258,10 +17258,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133240013</v>
+        <v>133240040</v>
       </c>
       <c r="B157" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17269,21 +17269,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17293,10 +17293,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>630166</v>
+        <v>630295</v>
       </c>
       <c r="R157" t="n">
-        <v>6967049</v>
+        <v>6967374</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -17328,7 +17328,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17338,7 +17338,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17365,10 +17365,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133240039</v>
+        <v>133240025</v>
       </c>
       <c r="B158" t="n">
-        <v>89302</v>
+        <v>79334</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17376,21 +17376,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17400,10 +17400,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>630317</v>
+        <v>630103</v>
       </c>
       <c r="R158" t="n">
-        <v>6967329</v>
+        <v>6967179</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -17435,7 +17435,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17472,10 +17472,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>133240007</v>
+        <v>133240039</v>
       </c>
       <c r="B159" t="n">
-        <v>79366</v>
+        <v>89310</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17483,21 +17483,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17507,13 +17507,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>630244</v>
+        <v>630317</v>
       </c>
       <c r="R159" t="n">
-        <v>6967085</v>
+        <v>6967329</v>
       </c>
       <c r="S159" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17579,10 +17579,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133240036</v>
+        <v>133240007</v>
       </c>
       <c r="B160" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17590,21 +17590,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17614,13 +17614,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>630368</v>
+        <v>630244</v>
       </c>
       <c r="R160" t="n">
-        <v>6967120</v>
+        <v>6967085</v>
       </c>
       <c r="S160" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17686,7 +17686,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133240028</v>
+        <v>133240036</v>
       </c>
       <c r="B161" t="n">
         <v>79334</v>
@@ -17721,10 +17721,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>630174</v>
+        <v>630368</v>
       </c>
       <c r="R161" t="n">
-        <v>6967208</v>
+        <v>6967120</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17793,7 +17793,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133240025</v>
+        <v>133240028</v>
       </c>
       <c r="B162" t="n">
         <v>79334</v>
@@ -17828,10 +17828,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>630103</v>
+        <v>630174</v>
       </c>
       <c r="R162" t="n">
-        <v>6967179</v>
+        <v>6967208</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18010,7 +18010,7 @@
         <v>133240031</v>
       </c>
       <c r="B164" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18114,10 +18114,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133240029</v>
+        <v>133240018</v>
       </c>
       <c r="B165" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18125,21 +18125,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18149,10 +18149,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>630179</v>
+        <v>630148</v>
       </c>
       <c r="R165" t="n">
-        <v>6967208</v>
+        <v>6967065</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18328,10 +18328,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>133240018</v>
+        <v>133240029</v>
       </c>
       <c r="B167" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18339,21 +18339,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18363,10 +18363,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>630148</v>
+        <v>630179</v>
       </c>
       <c r="R167" t="n">
-        <v>6967065</v>
+        <v>6967208</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133152237</v>
+        <v>133152204</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630189</v>
+        <v>630265</v>
       </c>
       <c r="R11" t="n">
-        <v>6967121</v>
+        <v>6967240</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1638,12 +1638,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133152204</v>
+        <v>133152222</v>
       </c>
       <c r="B12" t="n">
-        <v>91928</v>
+        <v>83183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630265</v>
+        <v>630156</v>
       </c>
       <c r="R12" t="n">
-        <v>6967240</v>
+        <v>6967155</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1740,7 +1735,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1750,7 +1745,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133152222</v>
+        <v>133152220</v>
       </c>
       <c r="B13" t="n">
-        <v>83183</v>
+        <v>91942</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630156</v>
+        <v>630135</v>
       </c>
       <c r="R13" t="n">
-        <v>6967155</v>
+        <v>6967160</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1847,7 +1842,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1857,7 +1852,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133152220</v>
+        <v>133152217</v>
       </c>
       <c r="B14" t="n">
-        <v>91942</v>
+        <v>92227</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1895,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1919,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630135</v>
+        <v>630130</v>
       </c>
       <c r="R14" t="n">
-        <v>6967160</v>
+        <v>6967217</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1954,7 +1949,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1964,7 +1959,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,10 +1986,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133152217</v>
+        <v>133152237</v>
       </c>
       <c r="B15" t="n">
-        <v>92227</v>
+        <v>79334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2002,21 +1997,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630130</v>
+        <v>630189</v>
       </c>
       <c r="R15" t="n">
-        <v>6967217</v>
+        <v>6967121</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2061,7 +2056,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2071,7 +2066,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3489,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133152173</v>
+        <v>133152188</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>92227</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,21 +3500,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630300</v>
+        <v>630274</v>
       </c>
       <c r="R29" t="n">
-        <v>6967133</v>
+        <v>6967324</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3596,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133152188</v>
+        <v>133152184</v>
       </c>
       <c r="B30" t="n">
-        <v>92227</v>
+        <v>79366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630274</v>
+        <v>630304</v>
       </c>
       <c r="R30" t="n">
-        <v>6967324</v>
+        <v>6967273</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3703,10 +3703,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133152184</v>
+        <v>133152173</v>
       </c>
       <c r="B31" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630304</v>
+        <v>630300</v>
       </c>
       <c r="R31" t="n">
-        <v>6967273</v>
+        <v>6967133</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -11553,10 +11553,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133202159</v>
+        <v>133202171</v>
       </c>
       <c r="B104" t="n">
-        <v>91942</v>
+        <v>79334</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>630290</v>
+        <v>630271</v>
       </c>
       <c r="R104" t="n">
-        <v>6967123</v>
+        <v>6967309</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11660,10 +11660,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133202171</v>
+        <v>133202159</v>
       </c>
       <c r="B105" t="n">
-        <v>79334</v>
+        <v>91942</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11671,21 +11671,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>630271</v>
+        <v>630290</v>
       </c>
       <c r="R105" t="n">
-        <v>6967309</v>
+        <v>6967123</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13051,53 +13051,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133202138</v>
+        <v>133202170</v>
       </c>
       <c r="B118" t="n">
-        <v>57136</v>
+        <v>79358</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>102612</v>
+        <v>6434</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>630143</v>
+        <v>630274</v>
       </c>
       <c r="R118" t="n">
-        <v>6967085</v>
+        <v>6967318</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13129,7 +13121,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13139,12 +13131,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Sannolikt tagen av en rovfågel.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13171,45 +13158,53 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133202170</v>
+        <v>133202138</v>
       </c>
       <c r="B119" t="n">
-        <v>79358</v>
+        <v>57136</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6434</v>
+        <v>102612</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>630274</v>
+        <v>630143</v>
       </c>
       <c r="R119" t="n">
-        <v>6967318</v>
+        <v>6967085</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13241,7 +13236,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13251,7 +13246,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Sannolikt tagen av en rovfågel.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13492,10 +13492,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133202130</v>
+        <v>133202157</v>
       </c>
       <c r="B122" t="n">
-        <v>83183</v>
+        <v>91928</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13503,21 +13503,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13527,10 +13527,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>630275</v>
+        <v>630257</v>
       </c>
       <c r="R122" t="n">
-        <v>6967143</v>
+        <v>6967180</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13599,10 +13599,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133202157</v>
+        <v>133202137</v>
       </c>
       <c r="B123" t="n">
-        <v>91928</v>
+        <v>92227</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13610,21 +13610,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13634,10 +13634,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>630257</v>
+        <v>630158</v>
       </c>
       <c r="R123" t="n">
-        <v>6967180</v>
+        <v>6967093</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13706,10 +13706,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133202137</v>
+        <v>133202136</v>
       </c>
       <c r="B124" t="n">
-        <v>92227</v>
+        <v>79334</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13717,21 +13717,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>630158</v>
+        <v>630184</v>
       </c>
       <c r="R124" t="n">
-        <v>6967093</v>
+        <v>6967090</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13813,10 +13813,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133202136</v>
+        <v>133202149</v>
       </c>
       <c r="B125" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13824,21 +13824,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>630184</v>
+        <v>630102</v>
       </c>
       <c r="R125" t="n">
-        <v>6967090</v>
+        <v>6967124</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13920,10 +13920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133202149</v>
+        <v>133202130</v>
       </c>
       <c r="B126" t="n">
-        <v>79366</v>
+        <v>83183</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13931,21 +13931,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>630102</v>
+        <v>630275</v>
       </c>
       <c r="R126" t="n">
-        <v>6967124</v>
+        <v>6967143</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14776,7 +14776,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133240019</v>
+        <v>133240044</v>
       </c>
       <c r="B134" t="n">
         <v>79334</v>
@@ -14811,10 +14811,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>630164</v>
+        <v>630257</v>
       </c>
       <c r="R134" t="n">
-        <v>6967058</v>
+        <v>6967346</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14846,7 +14846,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14883,7 +14883,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133240044</v>
+        <v>133240019</v>
       </c>
       <c r="B135" t="n">
         <v>79334</v>
@@ -14918,10 +14918,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>630257</v>
+        <v>630164</v>
       </c>
       <c r="R135" t="n">
-        <v>6967346</v>
+        <v>6967058</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD135" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -3489,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133152188</v>
+        <v>133152173</v>
       </c>
       <c r="B29" t="n">
-        <v>92227</v>
+        <v>79334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,21 +3500,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630274</v>
+        <v>630300</v>
       </c>
       <c r="R29" t="n">
-        <v>6967324</v>
+        <v>6967133</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3596,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133152184</v>
+        <v>133152188</v>
       </c>
       <c r="B30" t="n">
-        <v>79366</v>
+        <v>92227</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630304</v>
+        <v>630274</v>
       </c>
       <c r="R30" t="n">
-        <v>6967273</v>
+        <v>6967324</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3703,10 +3703,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133152173</v>
+        <v>133152184</v>
       </c>
       <c r="B31" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630300</v>
+        <v>630304</v>
       </c>
       <c r="R31" t="n">
-        <v>6967133</v>
+        <v>6967273</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5843,10 +5843,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133152209</v>
+        <v>133152189</v>
       </c>
       <c r="B51" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5854,21 +5854,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>630184</v>
+        <v>630270</v>
       </c>
       <c r="R51" t="n">
-        <v>6967242</v>
+        <v>6967330</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>05:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>05:56</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5950,7 +5950,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133152189</v>
+        <v>133152235</v>
       </c>
       <c r="B52" t="n">
         <v>91928</v>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>630270</v>
+        <v>630162</v>
       </c>
       <c r="R52" t="n">
-        <v>6967330</v>
+        <v>6967096</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>05:56</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>05:56</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6057,7 +6057,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133152235</v>
+        <v>133152194</v>
       </c>
       <c r="B53" t="n">
         <v>91928</v>
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>630162</v>
+        <v>630296</v>
       </c>
       <c r="R53" t="n">
-        <v>6967096</v>
+        <v>6967350</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6164,10 +6164,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133152194</v>
+        <v>133152209</v>
       </c>
       <c r="B54" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6175,21 +6175,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>630296</v>
+        <v>630184</v>
       </c>
       <c r="R54" t="n">
-        <v>6967350</v>
+        <v>6967242</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -10254,10 +10254,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133202145</v>
+        <v>133202168</v>
       </c>
       <c r="B92" t="n">
-        <v>91942</v>
+        <v>83183</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10265,21 +10265,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>630093</v>
+        <v>630290</v>
       </c>
       <c r="R92" t="n">
-        <v>6967070</v>
+        <v>6967317</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10468,10 +10468,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133202155</v>
+        <v>133202145</v>
       </c>
       <c r="B94" t="n">
-        <v>91928</v>
+        <v>91942</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10479,21 +10479,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>630210</v>
+        <v>630093</v>
       </c>
       <c r="R94" t="n">
-        <v>6967196</v>
+        <v>6967070</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10575,32 +10575,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133202173</v>
+        <v>133202155</v>
       </c>
       <c r="B95" t="n">
-        <v>92651</v>
+        <v>91928</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>630299</v>
+        <v>630210</v>
       </c>
       <c r="R95" t="n">
-        <v>6967218</v>
+        <v>6967196</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10682,32 +10682,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133202168</v>
+        <v>133202173</v>
       </c>
       <c r="B96" t="n">
-        <v>83183</v>
+        <v>92651</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10717,10 +10717,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>630290</v>
+        <v>630299</v>
       </c>
       <c r="R96" t="n">
-        <v>6967317</v>
+        <v>6967218</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11003,32 +11003,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133202150</v>
+        <v>133202163</v>
       </c>
       <c r="B99" t="n">
-        <v>79590</v>
+        <v>79334</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11038,10 +11038,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>630122</v>
+        <v>630344</v>
       </c>
       <c r="R99" t="n">
-        <v>6967138</v>
+        <v>6967158</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11110,32 +11110,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133202163</v>
+        <v>133202150</v>
       </c>
       <c r="B100" t="n">
-        <v>79334</v>
+        <v>79590</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11145,10 +11145,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>630344</v>
+        <v>630122</v>
       </c>
       <c r="R100" t="n">
-        <v>6967158</v>
+        <v>6967138</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12837,10 +12837,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>133202153</v>
+        <v>133202144</v>
       </c>
       <c r="B116" t="n">
-        <v>92227</v>
+        <v>79366</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12848,21 +12848,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12872,10 +12872,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>630160</v>
+        <v>630098</v>
       </c>
       <c r="R116" t="n">
-        <v>6967163</v>
+        <v>6967075</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12917,7 +12917,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12944,10 +12944,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>133202144</v>
+        <v>133202153</v>
       </c>
       <c r="B117" t="n">
-        <v>79366</v>
+        <v>92227</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12955,21 +12955,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>630098</v>
+        <v>630160</v>
       </c>
       <c r="R117" t="n">
-        <v>6967075</v>
+        <v>6967163</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13706,10 +13706,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133202136</v>
+        <v>133202130</v>
       </c>
       <c r="B124" t="n">
-        <v>79334</v>
+        <v>83183</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13717,21 +13717,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>630184</v>
+        <v>630275</v>
       </c>
       <c r="R124" t="n">
-        <v>6967090</v>
+        <v>6967143</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13813,10 +13813,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133202149</v>
+        <v>133202136</v>
       </c>
       <c r="B125" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13824,21 +13824,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>630102</v>
+        <v>630184</v>
       </c>
       <c r="R125" t="n">
-        <v>6967124</v>
+        <v>6967090</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13920,10 +13920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133202130</v>
+        <v>133202149</v>
       </c>
       <c r="B126" t="n">
-        <v>83183</v>
+        <v>79366</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13931,21 +13931,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>630275</v>
+        <v>630102</v>
       </c>
       <c r="R126" t="n">
-        <v>6967143</v>
+        <v>6967124</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15418,10 +15418,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133240037</v>
+        <v>133240010</v>
       </c>
       <c r="B140" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15429,21 +15429,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15453,10 +15453,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>630379</v>
+        <v>630202</v>
       </c>
       <c r="R140" t="n">
-        <v>6967127</v>
+        <v>6967062</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15525,10 +15525,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133240010</v>
+        <v>133240030</v>
       </c>
       <c r="B141" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15536,21 +15536,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15560,13 +15560,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>630202</v>
+        <v>630210</v>
       </c>
       <c r="R141" t="n">
-        <v>6967062</v>
+        <v>6967208</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15632,10 +15632,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133240004</v>
+        <v>133240037</v>
       </c>
       <c r="B142" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15643,21 +15643,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15667,10 +15667,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>630287</v>
+        <v>630379</v>
       </c>
       <c r="R142" t="n">
-        <v>6967110</v>
+        <v>6967127</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15739,10 +15739,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133240030</v>
+        <v>133240004</v>
       </c>
       <c r="B143" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15750,21 +15750,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15774,13 +15774,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>630210</v>
+        <v>630287</v>
       </c>
       <c r="R143" t="n">
-        <v>6967208</v>
+        <v>6967110</v>
       </c>
       <c r="S143" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16509,10 +16509,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133240024</v>
+        <v>133240038</v>
       </c>
       <c r="B150" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16520,21 +16520,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16544,13 +16544,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>630079</v>
+        <v>630337</v>
       </c>
       <c r="R150" t="n">
-        <v>6967088</v>
+        <v>6967201</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16616,10 +16616,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133240038</v>
+        <v>133240024</v>
       </c>
       <c r="B151" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16627,21 +16627,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16651,13 +16651,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>630337</v>
+        <v>630079</v>
       </c>
       <c r="R151" t="n">
-        <v>6967201</v>
+        <v>6967088</v>
       </c>
       <c r="S151" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17044,7 +17044,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133240043</v>
+        <v>133240013</v>
       </c>
       <c r="B155" t="n">
         <v>79334</v>
@@ -17079,10 +17079,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>630242</v>
+        <v>630166</v>
       </c>
       <c r="R155" t="n">
-        <v>6967369</v>
+        <v>6967049</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17151,7 +17151,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133240013</v>
+        <v>133240043</v>
       </c>
       <c r="B156" t="n">
         <v>79334</v>
@@ -17186,10 +17186,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>630166</v>
+        <v>630242</v>
       </c>
       <c r="R156" t="n">
-        <v>6967049</v>
+        <v>6967369</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -17221,7 +17221,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD156" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133152204</v>
+        <v>133152237</v>
       </c>
       <c r="B11" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630265</v>
+        <v>630189</v>
       </c>
       <c r="R11" t="n">
-        <v>6967240</v>
+        <v>6967121</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1638,7 +1638,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133152222</v>
+        <v>133152204</v>
       </c>
       <c r="B12" t="n">
-        <v>83183</v>
+        <v>91928</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630156</v>
+        <v>630265</v>
       </c>
       <c r="R12" t="n">
-        <v>6967155</v>
+        <v>6967240</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1735,7 +1740,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1745,7 +1750,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1772,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133152220</v>
+        <v>133152222</v>
       </c>
       <c r="B13" t="n">
-        <v>91942</v>
+        <v>83183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,21 +1788,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1807,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630135</v>
+        <v>630156</v>
       </c>
       <c r="R13" t="n">
-        <v>6967160</v>
+        <v>6967155</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1842,7 +1847,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1852,7 +1857,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133152217</v>
+        <v>133152220</v>
       </c>
       <c r="B14" t="n">
-        <v>92227</v>
+        <v>91942</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1895,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630130</v>
+        <v>630135</v>
       </c>
       <c r="R14" t="n">
-        <v>6967217</v>
+        <v>6967160</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1949,7 +1954,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1959,7 +1964,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1986,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133152237</v>
+        <v>133152217</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>92227</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,21 +2002,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630189</v>
+        <v>630130</v>
       </c>
       <c r="R15" t="n">
-        <v>6967121</v>
+        <v>6967217</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2056,7 +2061,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2066,12 +2071,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -5843,10 +5843,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133152189</v>
+        <v>133152209</v>
       </c>
       <c r="B51" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5854,21 +5854,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>630270</v>
+        <v>630184</v>
       </c>
       <c r="R51" t="n">
-        <v>6967330</v>
+        <v>6967242</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>05:56</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>05:56</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5950,7 +5950,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133152235</v>
+        <v>133152189</v>
       </c>
       <c r="B52" t="n">
         <v>91928</v>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>630162</v>
+        <v>630270</v>
       </c>
       <c r="R52" t="n">
-        <v>6967096</v>
+        <v>6967330</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>05:56</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>05:56</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6057,7 +6057,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133152194</v>
+        <v>133152235</v>
       </c>
       <c r="B53" t="n">
         <v>91928</v>
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>630296</v>
+        <v>630162</v>
       </c>
       <c r="R53" t="n">
-        <v>6967350</v>
+        <v>6967096</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6164,10 +6164,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133152209</v>
+        <v>133152194</v>
       </c>
       <c r="B54" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6175,21 +6175,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>630184</v>
+        <v>630296</v>
       </c>
       <c r="R54" t="n">
-        <v>6967242</v>
+        <v>6967350</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -11003,32 +11003,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133202163</v>
+        <v>133202150</v>
       </c>
       <c r="B99" t="n">
-        <v>79334</v>
+        <v>79590</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11038,10 +11038,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>630344</v>
+        <v>630122</v>
       </c>
       <c r="R99" t="n">
-        <v>6967158</v>
+        <v>6967138</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11110,32 +11110,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133202150</v>
+        <v>133202163</v>
       </c>
       <c r="B100" t="n">
-        <v>79590</v>
+        <v>79334</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11145,10 +11145,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>630122</v>
+        <v>630344</v>
       </c>
       <c r="R100" t="n">
-        <v>6967138</v>
+        <v>6967158</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11217,10 +11217,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133202169</v>
+        <v>133202151</v>
       </c>
       <c r="B101" t="n">
-        <v>91942</v>
+        <v>83183</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11228,21 +11228,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11252,10 +11252,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>630259</v>
+        <v>630118</v>
       </c>
       <c r="R101" t="n">
-        <v>6967344</v>
+        <v>6967158</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11287,7 +11287,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11324,10 +11324,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133202151</v>
+        <v>133202169</v>
       </c>
       <c r="B102" t="n">
-        <v>83183</v>
+        <v>91942</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11335,21 +11335,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11359,10 +11359,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>630118</v>
+        <v>630259</v>
       </c>
       <c r="R102" t="n">
-        <v>6967158</v>
+        <v>6967344</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11394,7 +11394,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12837,10 +12837,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>133202144</v>
+        <v>133202153</v>
       </c>
       <c r="B116" t="n">
-        <v>79366</v>
+        <v>92227</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12848,21 +12848,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12872,10 +12872,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>630098</v>
+        <v>630160</v>
       </c>
       <c r="R116" t="n">
-        <v>6967075</v>
+        <v>6967163</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12917,7 +12917,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12944,10 +12944,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>133202153</v>
+        <v>133202144</v>
       </c>
       <c r="B117" t="n">
-        <v>92227</v>
+        <v>79366</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12955,21 +12955,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>630160</v>
+        <v>630098</v>
       </c>
       <c r="R117" t="n">
-        <v>6967163</v>
+        <v>6967075</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14776,7 +14776,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133240044</v>
+        <v>133240019</v>
       </c>
       <c r="B134" t="n">
         <v>79334</v>
@@ -14811,10 +14811,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>630257</v>
+        <v>630164</v>
       </c>
       <c r="R134" t="n">
-        <v>6967346</v>
+        <v>6967058</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14846,7 +14846,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14883,7 +14883,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133240019</v>
+        <v>133240044</v>
       </c>
       <c r="B135" t="n">
         <v>79334</v>
@@ -14918,10 +14918,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>630164</v>
+        <v>630257</v>
       </c>
       <c r="R135" t="n">
-        <v>6967058</v>
+        <v>6967346</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15418,10 +15418,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133240010</v>
+        <v>133240037</v>
       </c>
       <c r="B140" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15429,21 +15429,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15453,10 +15453,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>630202</v>
+        <v>630379</v>
       </c>
       <c r="R140" t="n">
-        <v>6967062</v>
+        <v>6967127</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15525,10 +15525,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133240030</v>
+        <v>133240010</v>
       </c>
       <c r="B141" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15536,21 +15536,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15560,13 +15560,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>630210</v>
+        <v>630202</v>
       </c>
       <c r="R141" t="n">
-        <v>6967208</v>
+        <v>6967062</v>
       </c>
       <c r="S141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15632,10 +15632,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133240037</v>
+        <v>133240004</v>
       </c>
       <c r="B142" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15643,21 +15643,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15667,10 +15667,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>630379</v>
+        <v>630287</v>
       </c>
       <c r="R142" t="n">
-        <v>6967127</v>
+        <v>6967110</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15739,10 +15739,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133240004</v>
+        <v>133240030</v>
       </c>
       <c r="B143" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15750,21 +15750,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15774,13 +15774,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>630287</v>
+        <v>630210</v>
       </c>
       <c r="R143" t="n">
-        <v>6967110</v>
+        <v>6967208</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15953,10 +15953,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>133240008</v>
+        <v>133240032</v>
       </c>
       <c r="B145" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15964,21 +15964,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15988,10 +15988,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>630229</v>
+        <v>630247</v>
       </c>
       <c r="R145" t="n">
-        <v>6967080</v>
+        <v>6967189</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16060,10 +16060,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133240032</v>
+        <v>133240008</v>
       </c>
       <c r="B146" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16071,21 +16071,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16095,10 +16095,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>630247</v>
+        <v>630229</v>
       </c>
       <c r="R146" t="n">
-        <v>6967189</v>
+        <v>6967080</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16167,10 +16167,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133244099</v>
+        <v>133240020</v>
       </c>
       <c r="B147" t="n">
-        <v>57958</v>
+        <v>79366</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16178,53 +16178,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Gillermyrtjärnen, Lomtjärnsåsen, Sela, Ång</t>
+          <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>630169</v>
+        <v>630162</v>
       </c>
       <c r="R147" t="n">
-        <v>6967162</v>
+        <v>6967059</v>
       </c>
       <c r="S147" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16253,7 +16237,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16263,12 +16247,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Ljudbox har använts och trummande tretåig hackspett har registrerats. Programmet Audacity har använts för att analysera trumningarna som hördes tidigt på morgonen. Trumningarna är i genomsnitt 1,2 sekunder långa med en slagfrekvens på i genomsnitt 12,7 slag/sekund vilket stämmer väl in på tretåig hackspett. Bifogat finns en del av ljudupptagningen och en bild med ett utmarkerat grönt kryss där genomsnittsvärdena har placerats ut samt ett skärmklipp från analysprogrammet audacity där trumningarna syns.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16295,10 +16274,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133240020</v>
+        <v>133244099</v>
       </c>
       <c r="B148" t="n">
-        <v>79366</v>
+        <v>57958</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16306,37 +16285,53 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Gillemyrtjärnen, Ång</t>
+          <t>Gillermyrtjärnen, Lomtjärnsåsen, Sela, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>630162</v>
+        <v>630169</v>
       </c>
       <c r="R148" t="n">
-        <v>6967059</v>
+        <v>6967162</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16365,7 +16360,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16375,7 +16370,12 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Ljudbox har använts och trummande tretåig hackspett har registrerats. Programmet Audacity har använts för att analysera trumningarna som hördes tidigt på morgonen. Trumningarna är i genomsnitt 1,2 sekunder långa med en slagfrekvens på i genomsnitt 12,7 slag/sekund vilket stämmer väl in på tretåig hackspett. Bifogat finns en del av ljudupptagningen och en bild med ett utmarkerat grönt kryss där genomsnittsvärdena har placerats ut samt ett skärmklipp från analysprogrammet audacity där trumningarna syns.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17472,10 +17472,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>133240039</v>
+        <v>133240007</v>
       </c>
       <c r="B159" t="n">
-        <v>89310</v>
+        <v>79366</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17483,21 +17483,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17507,13 +17507,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>630317</v>
+        <v>630244</v>
       </c>
       <c r="R159" t="n">
-        <v>6967329</v>
+        <v>6967085</v>
       </c>
       <c r="S159" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17579,10 +17579,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133240007</v>
+        <v>133240036</v>
       </c>
       <c r="B160" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17590,21 +17590,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17614,13 +17614,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>630244</v>
+        <v>630368</v>
       </c>
       <c r="R160" t="n">
-        <v>6967085</v>
+        <v>6967120</v>
       </c>
       <c r="S160" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17686,7 +17686,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133240036</v>
+        <v>133240028</v>
       </c>
       <c r="B161" t="n">
         <v>79334</v>
@@ -17721,10 +17721,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>630368</v>
+        <v>630174</v>
       </c>
       <c r="R161" t="n">
-        <v>6967120</v>
+        <v>6967208</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17793,10 +17793,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133240028</v>
+        <v>133240039</v>
       </c>
       <c r="B162" t="n">
-        <v>79334</v>
+        <v>89310</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17804,21 +17804,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17828,10 +17828,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>630174</v>
+        <v>630317</v>
       </c>
       <c r="R162" t="n">
-        <v>6967208</v>
+        <v>6967329</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD162" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133152237</v>
+        <v>133152204</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630189</v>
+        <v>630265</v>
       </c>
       <c r="R11" t="n">
-        <v>6967121</v>
+        <v>6967240</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1638,12 +1638,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133152204</v>
+        <v>133152222</v>
       </c>
       <c r="B12" t="n">
-        <v>91928</v>
+        <v>83183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630265</v>
+        <v>630156</v>
       </c>
       <c r="R12" t="n">
-        <v>6967240</v>
+        <v>6967155</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1740,7 +1735,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1750,7 +1745,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133152222</v>
+        <v>133152220</v>
       </c>
       <c r="B13" t="n">
-        <v>83183</v>
+        <v>91942</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630156</v>
+        <v>630135</v>
       </c>
       <c r="R13" t="n">
-        <v>6967155</v>
+        <v>6967160</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1847,7 +1842,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1857,7 +1852,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133152220</v>
+        <v>133152217</v>
       </c>
       <c r="B14" t="n">
-        <v>91942</v>
+        <v>92227</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1895,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1919,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630135</v>
+        <v>630130</v>
       </c>
       <c r="R14" t="n">
-        <v>6967160</v>
+        <v>6967217</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1954,7 +1949,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1964,7 +1959,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,10 +1986,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133152217</v>
+        <v>133152237</v>
       </c>
       <c r="B15" t="n">
-        <v>92227</v>
+        <v>79334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2002,21 +1997,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630130</v>
+        <v>630189</v>
       </c>
       <c r="R15" t="n">
-        <v>6967217</v>
+        <v>6967121</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2061,7 +2056,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2071,7 +2066,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3489,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133152173</v>
+        <v>133152188</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>92227</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,21 +3500,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630300</v>
+        <v>630274</v>
       </c>
       <c r="R29" t="n">
-        <v>6967133</v>
+        <v>6967324</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3596,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133152188</v>
+        <v>133152184</v>
       </c>
       <c r="B30" t="n">
-        <v>92227</v>
+        <v>79366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630274</v>
+        <v>630304</v>
       </c>
       <c r="R30" t="n">
-        <v>6967324</v>
+        <v>6967273</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3703,10 +3703,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133152184</v>
+        <v>133152173</v>
       </c>
       <c r="B31" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630304</v>
+        <v>630300</v>
       </c>
       <c r="R31" t="n">
-        <v>6967273</v>
+        <v>6967133</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -10254,10 +10254,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133202168</v>
+        <v>133202145</v>
       </c>
       <c r="B92" t="n">
-        <v>83183</v>
+        <v>91942</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10265,21 +10265,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>630290</v>
+        <v>630093</v>
       </c>
       <c r="R92" t="n">
-        <v>6967317</v>
+        <v>6967070</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10468,10 +10468,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133202145</v>
+        <v>133202155</v>
       </c>
       <c r="B94" t="n">
-        <v>91942</v>
+        <v>91928</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10479,21 +10479,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>630093</v>
+        <v>630210</v>
       </c>
       <c r="R94" t="n">
-        <v>6967070</v>
+        <v>6967196</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10575,32 +10575,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133202155</v>
+        <v>133202173</v>
       </c>
       <c r="B95" t="n">
-        <v>91928</v>
+        <v>92651</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>630210</v>
+        <v>630299</v>
       </c>
       <c r="R95" t="n">
-        <v>6967196</v>
+        <v>6967218</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10682,32 +10682,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133202173</v>
+        <v>133202168</v>
       </c>
       <c r="B96" t="n">
-        <v>92651</v>
+        <v>83183</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10717,10 +10717,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>630299</v>
+        <v>630290</v>
       </c>
       <c r="R96" t="n">
-        <v>6967218</v>
+        <v>6967317</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13706,10 +13706,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133202130</v>
+        <v>133202136</v>
       </c>
       <c r="B124" t="n">
-        <v>83183</v>
+        <v>79334</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13717,21 +13717,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>630275</v>
+        <v>630184</v>
       </c>
       <c r="R124" t="n">
-        <v>6967143</v>
+        <v>6967090</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13813,10 +13813,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133202136</v>
+        <v>133202149</v>
       </c>
       <c r="B125" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13824,21 +13824,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>630184</v>
+        <v>630102</v>
       </c>
       <c r="R125" t="n">
-        <v>6967090</v>
+        <v>6967124</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13920,10 +13920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133202149</v>
+        <v>133202130</v>
       </c>
       <c r="B126" t="n">
-        <v>79366</v>
+        <v>83183</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13931,21 +13931,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>630102</v>
+        <v>630275</v>
       </c>
       <c r="R126" t="n">
-        <v>6967124</v>
+        <v>6967143</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15418,10 +15418,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133240037</v>
+        <v>133240010</v>
       </c>
       <c r="B140" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15429,21 +15429,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15453,10 +15453,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>630379</v>
+        <v>630202</v>
       </c>
       <c r="R140" t="n">
-        <v>6967127</v>
+        <v>6967062</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15525,10 +15525,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133240010</v>
+        <v>133240037</v>
       </c>
       <c r="B141" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15536,21 +15536,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15560,10 +15560,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>630202</v>
+        <v>630379</v>
       </c>
       <c r="R141" t="n">
-        <v>6967062</v>
+        <v>6967127</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15953,10 +15953,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>133240032</v>
+        <v>133240008</v>
       </c>
       <c r="B145" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15964,21 +15964,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15988,10 +15988,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>630247</v>
+        <v>630229</v>
       </c>
       <c r="R145" t="n">
-        <v>6967189</v>
+        <v>6967080</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16060,10 +16060,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133240008</v>
+        <v>133240032</v>
       </c>
       <c r="B146" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16071,21 +16071,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16095,10 +16095,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>630229</v>
+        <v>630247</v>
       </c>
       <c r="R146" t="n">
-        <v>6967080</v>
+        <v>6967189</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16167,10 +16167,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133240020</v>
+        <v>133244099</v>
       </c>
       <c r="B147" t="n">
-        <v>79366</v>
+        <v>57958</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16178,37 +16178,53 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Gillemyrtjärnen, Ång</t>
+          <t>Gillermyrtjärnen, Lomtjärnsåsen, Sela, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>630162</v>
+        <v>630169</v>
       </c>
       <c r="R147" t="n">
-        <v>6967059</v>
+        <v>6967162</v>
       </c>
       <c r="S147" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16237,7 +16253,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16247,7 +16263,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Ljudbox har använts och trummande tretåig hackspett har registrerats. Programmet Audacity har använts för att analysera trumningarna som hördes tidigt på morgonen. Trumningarna är i genomsnitt 1,2 sekunder långa med en slagfrekvens på i genomsnitt 12,7 slag/sekund vilket stämmer väl in på tretåig hackspett. Bifogat finns en del av ljudupptagningen och en bild med ett utmarkerat grönt kryss där genomsnittsvärdena har placerats ut samt ett skärmklipp från analysprogrammet audacity där trumningarna syns.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16274,10 +16295,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133244099</v>
+        <v>133240020</v>
       </c>
       <c r="B148" t="n">
-        <v>57958</v>
+        <v>79366</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16285,53 +16306,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Gillermyrtjärnen, Lomtjärnsåsen, Sela, Ång</t>
+          <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>630169</v>
+        <v>630162</v>
       </c>
       <c r="R148" t="n">
-        <v>6967162</v>
+        <v>6967059</v>
       </c>
       <c r="S148" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16360,7 +16365,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16370,12 +16375,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Ljudbox har använts och trummande tretåig hackspett har registrerats. Programmet Audacity har använts för att analysera trumningarna som hördes tidigt på morgonen. Trumningarna är i genomsnitt 1,2 sekunder långa med en slagfrekvens på i genomsnitt 12,7 slag/sekund vilket stämmer väl in på tretåig hackspett. Bifogat finns en del av ljudupptagningen och en bild med ett utmarkerat grönt kryss där genomsnittsvärdena har placerats ut samt ett skärmklipp från analysprogrammet audacity där trumningarna syns.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17044,7 +17044,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133240013</v>
+        <v>133240043</v>
       </c>
       <c r="B155" t="n">
         <v>79334</v>
@@ -17079,10 +17079,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>630166</v>
+        <v>630242</v>
       </c>
       <c r="R155" t="n">
-        <v>6967049</v>
+        <v>6967369</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17151,7 +17151,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133240043</v>
+        <v>133240013</v>
       </c>
       <c r="B156" t="n">
         <v>79334</v>
@@ -17186,10 +17186,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>630242</v>
+        <v>630166</v>
       </c>
       <c r="R156" t="n">
-        <v>6967369</v>
+        <v>6967049</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -17221,7 +17221,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD156" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -3489,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133152188</v>
+        <v>133152173</v>
       </c>
       <c r="B29" t="n">
-        <v>92227</v>
+        <v>79334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,21 +3500,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630274</v>
+        <v>630300</v>
       </c>
       <c r="R29" t="n">
-        <v>6967324</v>
+        <v>6967133</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3596,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133152184</v>
+        <v>133152188</v>
       </c>
       <c r="B30" t="n">
-        <v>79366</v>
+        <v>92227</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630304</v>
+        <v>630274</v>
       </c>
       <c r="R30" t="n">
-        <v>6967273</v>
+        <v>6967324</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3703,10 +3703,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133152173</v>
+        <v>133152184</v>
       </c>
       <c r="B31" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630300</v>
+        <v>630304</v>
       </c>
       <c r="R31" t="n">
-        <v>6967133</v>
+        <v>6967273</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -9719,10 +9719,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133202128</v>
+        <v>133202135</v>
       </c>
       <c r="B87" t="n">
-        <v>79366</v>
+        <v>83183</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9730,21 +9730,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9754,10 +9754,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>630304</v>
+        <v>630165</v>
       </c>
       <c r="R87" t="n">
-        <v>6967096</v>
+        <v>6967141</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9826,10 +9826,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133202135</v>
+        <v>133202128</v>
       </c>
       <c r="B88" t="n">
-        <v>83183</v>
+        <v>79366</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9837,21 +9837,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9861,10 +9861,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>630165</v>
+        <v>630304</v>
       </c>
       <c r="R88" t="n">
-        <v>6967141</v>
+        <v>6967096</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10254,10 +10254,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133202145</v>
+        <v>133202148</v>
       </c>
       <c r="B92" t="n">
-        <v>91942</v>
+        <v>79334</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10265,21 +10265,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>630093</v>
+        <v>630099</v>
       </c>
       <c r="R92" t="n">
-        <v>6967070</v>
+        <v>6967120</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10361,10 +10361,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133202148</v>
+        <v>133202145</v>
       </c>
       <c r="B93" t="n">
-        <v>79334</v>
+        <v>91942</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10372,21 +10372,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>630099</v>
+        <v>630093</v>
       </c>
       <c r="R93" t="n">
-        <v>6967120</v>
+        <v>6967070</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -15953,10 +15953,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>133240008</v>
+        <v>133240032</v>
       </c>
       <c r="B145" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15964,21 +15964,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15988,10 +15988,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>630229</v>
+        <v>630247</v>
       </c>
       <c r="R145" t="n">
-        <v>6967080</v>
+        <v>6967189</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16060,10 +16060,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133240032</v>
+        <v>133240008</v>
       </c>
       <c r="B146" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16071,21 +16071,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16095,10 +16095,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>630247</v>
+        <v>630229</v>
       </c>
       <c r="R146" t="n">
-        <v>6967189</v>
+        <v>6967080</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16509,10 +16509,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133240038</v>
+        <v>133240024</v>
       </c>
       <c r="B150" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16520,21 +16520,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16544,13 +16544,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>630337</v>
+        <v>630079</v>
       </c>
       <c r="R150" t="n">
-        <v>6967201</v>
+        <v>6967088</v>
       </c>
       <c r="S150" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16616,10 +16616,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133240024</v>
+        <v>133240038</v>
       </c>
       <c r="B151" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16627,21 +16627,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16651,13 +16651,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>630079</v>
+        <v>630337</v>
       </c>
       <c r="R151" t="n">
-        <v>6967088</v>
+        <v>6967201</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17044,7 +17044,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133240043</v>
+        <v>133240013</v>
       </c>
       <c r="B155" t="n">
         <v>79334</v>
@@ -17079,10 +17079,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>630242</v>
+        <v>630166</v>
       </c>
       <c r="R155" t="n">
-        <v>6967369</v>
+        <v>6967049</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17151,7 +17151,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133240013</v>
+        <v>133240043</v>
       </c>
       <c r="B156" t="n">
         <v>79334</v>
@@ -17186,10 +17186,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>630166</v>
+        <v>630242</v>
       </c>
       <c r="R156" t="n">
-        <v>6967049</v>
+        <v>6967369</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -17221,7 +17221,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD156" t="b">

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -1561,7 +1561,7 @@
         <v>133152204</v>
       </c>
       <c r="B11" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>133152222</v>
       </c>
       <c r="B12" t="n">
-        <v>83183</v>
+        <v>83197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133152220</v>
+        <v>133152237</v>
       </c>
       <c r="B13" t="n">
-        <v>91942</v>
+        <v>79348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630135</v>
+        <v>630189</v>
       </c>
       <c r="R13" t="n">
-        <v>6967160</v>
+        <v>6967121</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1852,7 +1852,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1882,7 +1887,7 @@
         <v>133152217</v>
       </c>
       <c r="B14" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133152237</v>
+        <v>133152220</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>91961</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,21 +2002,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630189</v>
+        <v>630135</v>
       </c>
       <c r="R15" t="n">
-        <v>6967121</v>
+        <v>6967160</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2056,7 +2061,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2066,12 +2071,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2098,32 +2098,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133152165</v>
+        <v>133152185</v>
       </c>
       <c r="B16" t="n">
-        <v>79334</v>
+        <v>91910</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630325</v>
+        <v>630303</v>
       </c>
       <c r="R16" t="n">
-        <v>6967107</v>
+        <v>6967279</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,32 +2205,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133152185</v>
+        <v>133152174</v>
       </c>
       <c r="B17" t="n">
-        <v>91891</v>
+        <v>83197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630303</v>
+        <v>630286</v>
       </c>
       <c r="R17" t="n">
-        <v>6967279</v>
+        <v>6967149</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>05:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>05:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133152205</v>
+        <v>133152163</v>
       </c>
       <c r="B18" t="n">
-        <v>92227</v>
+        <v>79380</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630269</v>
+        <v>630334</v>
       </c>
       <c r="R18" t="n">
-        <v>6967234</v>
+        <v>6967097</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133152225</v>
+        <v>133152218</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>92218</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630153</v>
+        <v>630124</v>
       </c>
       <c r="R19" t="n">
-        <v>6967136</v>
+        <v>6967208</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133152246</v>
+        <v>133152205</v>
       </c>
       <c r="B20" t="n">
-        <v>79366</v>
+        <v>92218</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630264</v>
+        <v>630269</v>
       </c>
       <c r="R20" t="n">
-        <v>6967100</v>
+        <v>6967234</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133152174</v>
+        <v>133152225</v>
       </c>
       <c r="B21" t="n">
-        <v>83183</v>
+        <v>79380</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630286</v>
+        <v>630153</v>
       </c>
       <c r="R21" t="n">
-        <v>6967149</v>
+        <v>6967136</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2740,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133152163</v>
+        <v>133152165</v>
       </c>
       <c r="B22" t="n">
-        <v>79366</v>
+        <v>79348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630334</v>
+        <v>630325</v>
       </c>
       <c r="R22" t="n">
-        <v>6967097</v>
+        <v>6967107</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133152218</v>
+        <v>133152246</v>
       </c>
       <c r="B23" t="n">
-        <v>92227</v>
+        <v>79380</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630124</v>
+        <v>630264</v>
       </c>
       <c r="R23" t="n">
-        <v>6967208</v>
+        <v>6967100</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2954,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133152226</v>
+        <v>133152231</v>
       </c>
       <c r="B24" t="n">
-        <v>91928</v>
+        <v>79348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630154</v>
+        <v>630146</v>
       </c>
       <c r="R24" t="n">
-        <v>6967129</v>
+        <v>6967080</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133152231</v>
+        <v>133152226</v>
       </c>
       <c r="B25" t="n">
-        <v>79334</v>
+        <v>91947</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630146</v>
+        <v>630154</v>
       </c>
       <c r="R25" t="n">
-        <v>6967080</v>
+        <v>6967129</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3168,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133152221</v>
+        <v>133152161</v>
       </c>
       <c r="B26" t="n">
-        <v>91928</v>
+        <v>79380</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,21 +3179,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3203,10 +3203,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630134</v>
+        <v>630345</v>
       </c>
       <c r="R26" t="n">
-        <v>6967158</v>
+        <v>6967095</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>04:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>04:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3275,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133152161</v>
+        <v>133152221</v>
       </c>
       <c r="B27" t="n">
-        <v>79366</v>
+        <v>91947</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630345</v>
+        <v>630134</v>
       </c>
       <c r="R27" t="n">
-        <v>6967095</v>
+        <v>6967158</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>04:42</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>04:42</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3385,7 +3385,7 @@
         <v>133152224</v>
       </c>
       <c r="B28" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3489,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133152173</v>
+        <v>133152188</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>92218</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,21 +3500,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630300</v>
+        <v>630274</v>
       </c>
       <c r="R29" t="n">
-        <v>6967133</v>
+        <v>6967324</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3596,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133152188</v>
+        <v>133152184</v>
       </c>
       <c r="B30" t="n">
-        <v>92227</v>
+        <v>79380</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630274</v>
+        <v>630304</v>
       </c>
       <c r="R30" t="n">
-        <v>6967324</v>
+        <v>6967273</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3703,10 +3703,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133152184</v>
+        <v>133152173</v>
       </c>
       <c r="B31" t="n">
-        <v>79366</v>
+        <v>79348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630304</v>
+        <v>630300</v>
       </c>
       <c r="R31" t="n">
-        <v>6967273</v>
+        <v>6967133</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3810,10 +3810,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133152203</v>
+        <v>133152193</v>
       </c>
       <c r="B32" t="n">
-        <v>91942</v>
+        <v>83197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3821,21 +3821,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630258</v>
+        <v>630280</v>
       </c>
       <c r="R32" t="n">
-        <v>6967247</v>
+        <v>6967356</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3917,10 +3917,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133152193</v>
+        <v>133152203</v>
       </c>
       <c r="B33" t="n">
-        <v>83183</v>
+        <v>91961</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3928,21 +3928,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630280</v>
+        <v>630258</v>
       </c>
       <c r="R33" t="n">
-        <v>6967356</v>
+        <v>6967247</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4024,10 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133152206</v>
+        <v>133152164</v>
       </c>
       <c r="B34" t="n">
-        <v>79334</v>
+        <v>79380</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630256</v>
+        <v>630325</v>
       </c>
       <c r="R34" t="n">
-        <v>6967220</v>
+        <v>6967107</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>04:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4131,10 +4131,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133152234</v>
+        <v>133152167</v>
       </c>
       <c r="B35" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630161</v>
+        <v>630318</v>
       </c>
       <c r="R35" t="n">
-        <v>6967098</v>
+        <v>6967112</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4238,10 +4238,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133152164</v>
+        <v>133152234</v>
       </c>
       <c r="B36" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630325</v>
+        <v>630161</v>
       </c>
       <c r="R36" t="n">
-        <v>6967107</v>
+        <v>6967098</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4345,10 +4345,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133152167</v>
+        <v>133152206</v>
       </c>
       <c r="B37" t="n">
-        <v>79366</v>
+        <v>79348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4356,21 +4356,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630318</v>
+        <v>630256</v>
       </c>
       <c r="R37" t="n">
-        <v>6967112</v>
+        <v>6967220</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>04:51</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>04:51</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4452,10 +4452,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133152242</v>
+        <v>133152178</v>
       </c>
       <c r="B38" t="n">
-        <v>79334</v>
+        <v>79380</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4463,21 +4463,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4487,13 +4487,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630247</v>
+        <v>630300</v>
       </c>
       <c r="R38" t="n">
-        <v>6967129</v>
+        <v>6967148</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>05:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>05:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4559,10 +4559,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133152178</v>
+        <v>133152210</v>
       </c>
       <c r="B39" t="n">
-        <v>79366</v>
+        <v>83197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,21 +4570,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4594,13 +4594,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630300</v>
+        <v>630184</v>
       </c>
       <c r="R39" t="n">
-        <v>6967148</v>
+        <v>6967161</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>05:16</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>05:16</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4666,10 +4666,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133152243</v>
+        <v>133152242</v>
       </c>
       <c r="B40" t="n">
-        <v>83183</v>
+        <v>79348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630223</v>
+        <v>630247</v>
       </c>
       <c r="R40" t="n">
-        <v>6967132</v>
+        <v>6967129</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4773,10 +4773,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133152196</v>
+        <v>133152243</v>
       </c>
       <c r="B41" t="n">
-        <v>83183</v>
+        <v>83197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>630299</v>
+        <v>630223</v>
       </c>
       <c r="R41" t="n">
-        <v>6967344</v>
+        <v>6967132</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4880,10 +4880,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133152210</v>
+        <v>133152196</v>
       </c>
       <c r="B42" t="n">
-        <v>83183</v>
+        <v>83197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630184</v>
+        <v>630299</v>
       </c>
       <c r="R42" t="n">
-        <v>6967161</v>
+        <v>6967344</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4987,32 +4987,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133152195</v>
+        <v>133152201</v>
       </c>
       <c r="B43" t="n">
-        <v>75433</v>
+        <v>91947</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630297</v>
+        <v>630261</v>
       </c>
       <c r="R43" t="n">
-        <v>6967347</v>
+        <v>6967251</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5094,32 +5094,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133152216</v>
+        <v>133152195</v>
       </c>
       <c r="B44" t="n">
-        <v>79334</v>
+        <v>75444</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630149</v>
+        <v>630297</v>
       </c>
       <c r="R44" t="n">
-        <v>6967241</v>
+        <v>6967347</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5201,32 +5201,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133152197</v>
+        <v>133152216</v>
       </c>
       <c r="B45" t="n">
-        <v>75433</v>
+        <v>79348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630298</v>
+        <v>630149</v>
       </c>
       <c r="R45" t="n">
-        <v>6967342</v>
+        <v>6967241</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5308,32 +5308,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133152201</v>
+        <v>133152197</v>
       </c>
       <c r="B46" t="n">
-        <v>91928</v>
+        <v>75444</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5343,10 +5343,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630261</v>
+        <v>630298</v>
       </c>
       <c r="R46" t="n">
-        <v>6967251</v>
+        <v>6967342</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5418,7 +5418,7 @@
         <v>133152241</v>
       </c>
       <c r="B47" t="n">
-        <v>83183</v>
+        <v>83197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>133152159</v>
       </c>
       <c r="B48" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5629,10 +5629,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133152198</v>
+        <v>133152232</v>
       </c>
       <c r="B49" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>630231</v>
+        <v>630147</v>
       </c>
       <c r="R49" t="n">
-        <v>6967393</v>
+        <v>6967088</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5736,10 +5736,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133152232</v>
+        <v>133152198</v>
       </c>
       <c r="B50" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>630147</v>
+        <v>630231</v>
       </c>
       <c r="R50" t="n">
-        <v>6967088</v>
+        <v>6967393</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5846,7 +5846,7 @@
         <v>133152209</v>
       </c>
       <c r="B51" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>133152189</v>
       </c>
       <c r="B52" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>133152235</v>
       </c>
       <c r="B53" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>133152194</v>
       </c>
       <c r="B54" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6271,32 +6271,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133152208</v>
+        <v>133152183</v>
       </c>
       <c r="B55" t="n">
-        <v>79334</v>
+        <v>75444</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6306,13 +6306,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630207</v>
+        <v>630308</v>
       </c>
       <c r="R55" t="n">
-        <v>6967295</v>
+        <v>6967259</v>
       </c>
       <c r="S55" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6378,32 +6378,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133152183</v>
+        <v>133152208</v>
       </c>
       <c r="B56" t="n">
-        <v>75433</v>
+        <v>79348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6413,13 +6413,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630308</v>
+        <v>630207</v>
       </c>
       <c r="R56" t="n">
-        <v>6967259</v>
+        <v>6967295</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6488,7 +6488,7 @@
         <v>133152238</v>
       </c>
       <c r="B57" t="n">
-        <v>83183</v>
+        <v>83197</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>133152168</v>
       </c>
       <c r="B58" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6699,10 +6699,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133152175</v>
+        <v>133152191</v>
       </c>
       <c r="B59" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6734,13 +6734,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630308</v>
+        <v>630272</v>
       </c>
       <c r="R59" t="n">
-        <v>6967163</v>
+        <v>6967349</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6806,10 +6806,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133152191</v>
+        <v>133152215</v>
       </c>
       <c r="B60" t="n">
-        <v>79334</v>
+        <v>91947</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6817,21 +6817,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>630272</v>
+        <v>630159</v>
       </c>
       <c r="R60" t="n">
-        <v>6967349</v>
+        <v>6967229</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6913,10 +6913,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133152180</v>
+        <v>133152175</v>
       </c>
       <c r="B61" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>630315</v>
+        <v>630308</v>
       </c>
       <c r="R61" t="n">
-        <v>6967166</v>
+        <v>6967163</v>
       </c>
       <c r="S61" t="n">
         <v>6</v>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7020,10 +7020,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133152240</v>
+        <v>133152227</v>
       </c>
       <c r="B62" t="n">
-        <v>79334</v>
+        <v>83197</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7031,21 +7031,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7055,10 +7055,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630263</v>
+        <v>630148</v>
       </c>
       <c r="R62" t="n">
-        <v>6967142</v>
+        <v>6967117</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7127,10 +7127,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133152215</v>
+        <v>133152239</v>
       </c>
       <c r="B63" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>630159</v>
+        <v>630255</v>
       </c>
       <c r="R63" t="n">
-        <v>6967229</v>
+        <v>6967168</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7234,10 +7234,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133152239</v>
+        <v>133152180</v>
       </c>
       <c r="B64" t="n">
-        <v>91928</v>
+        <v>79348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7245,21 +7245,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7269,13 +7269,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>630255</v>
+        <v>630315</v>
       </c>
       <c r="R64" t="n">
-        <v>6967168</v>
+        <v>6967166</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7341,10 +7341,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133152227</v>
+        <v>133152240</v>
       </c>
       <c r="B65" t="n">
-        <v>83183</v>
+        <v>79348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7352,21 +7352,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>630148</v>
+        <v>630263</v>
       </c>
       <c r="R65" t="n">
-        <v>6967117</v>
+        <v>6967142</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7448,10 +7448,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133152199</v>
+        <v>133152219</v>
       </c>
       <c r="B66" t="n">
-        <v>79366</v>
+        <v>91947</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7459,21 +7459,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>630251</v>
+        <v>630121</v>
       </c>
       <c r="R66" t="n">
-        <v>6967351</v>
+        <v>6967203</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7555,10 +7555,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133152219</v>
+        <v>133152190</v>
       </c>
       <c r="B67" t="n">
-        <v>91928</v>
+        <v>83197</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7566,21 +7566,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>630121</v>
+        <v>630270</v>
       </c>
       <c r="R67" t="n">
-        <v>6967203</v>
+        <v>6967330</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7662,10 +7662,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133152190</v>
+        <v>133152177</v>
       </c>
       <c r="B68" t="n">
-        <v>83183</v>
+        <v>58126</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7673,34 +7673,46 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>630270</v>
+        <v>630306</v>
       </c>
       <c r="R68" t="n">
-        <v>6967330</v>
+        <v>6967160</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7732,7 +7744,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>05:13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7742,7 +7754,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>05:13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7769,10 +7781,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133152177</v>
+        <v>133152199</v>
       </c>
       <c r="B69" t="n">
-        <v>58119</v>
+        <v>79380</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7780,46 +7792,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630306</v>
+        <v>630251</v>
       </c>
       <c r="R69" t="n">
-        <v>6967160</v>
+        <v>6967351</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>05:13</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>05:13</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7888,10 +7888,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133152230</v>
+        <v>133152214</v>
       </c>
       <c r="B70" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7923,10 +7923,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>630109</v>
+        <v>630143</v>
       </c>
       <c r="R70" t="n">
-        <v>6967064</v>
+        <v>6967201</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7995,10 +7995,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133152214</v>
+        <v>133152230</v>
       </c>
       <c r="B71" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8030,10 +8030,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>630143</v>
+        <v>630109</v>
       </c>
       <c r="R71" t="n">
-        <v>6967201</v>
+        <v>6967064</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8102,32 +8102,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133152187</v>
+        <v>133152200</v>
       </c>
       <c r="B72" t="n">
-        <v>91891</v>
+        <v>83197</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>630305</v>
+        <v>630250</v>
       </c>
       <c r="R72" t="n">
-        <v>6967310</v>
+        <v>6967263</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8209,32 +8209,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133152200</v>
+        <v>133152187</v>
       </c>
       <c r="B73" t="n">
-        <v>83183</v>
+        <v>91910</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>630250</v>
+        <v>630305</v>
       </c>
       <c r="R73" t="n">
-        <v>6967263</v>
+        <v>6967310</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8319,7 +8319,7 @@
         <v>133152223</v>
       </c>
       <c r="B74" t="n">
-        <v>89310</v>
+        <v>89328</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8423,10 +8423,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133152181</v>
+        <v>133152212</v>
       </c>
       <c r="B75" t="n">
-        <v>79334</v>
+        <v>83197</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8434,21 +8434,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8458,13 +8458,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>630334</v>
+        <v>630176</v>
       </c>
       <c r="R75" t="n">
-        <v>6967171</v>
+        <v>6967173</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8530,10 +8530,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133152182</v>
+        <v>133152181</v>
       </c>
       <c r="B76" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>630324</v>
+        <v>630334</v>
       </c>
       <c r="R76" t="n">
-        <v>6967248</v>
+        <v>6967171</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8640,7 +8640,7 @@
         <v>133152171</v>
       </c>
       <c r="B77" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8744,10 +8744,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133152212</v>
+        <v>133152182</v>
       </c>
       <c r="B78" t="n">
-        <v>83183</v>
+        <v>79348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8755,21 +8755,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8779,13 +8779,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>630176</v>
+        <v>630324</v>
       </c>
       <c r="R78" t="n">
-        <v>6967173</v>
+        <v>6967248</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8851,10 +8851,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133152169</v>
+        <v>133152207</v>
       </c>
       <c r="B79" t="n">
-        <v>79334</v>
+        <v>58126</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8862,34 +8862,46 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>630316</v>
+        <v>630231</v>
       </c>
       <c r="R79" t="n">
-        <v>6967112</v>
+        <v>6967249</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8921,7 +8933,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8931,7 +8943,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>04:52</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8958,10 +8970,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133152170</v>
+        <v>133152169</v>
       </c>
       <c r="B80" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8993,10 +9005,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>630313</v>
+        <v>630316</v>
       </c>
       <c r="R80" t="n">
-        <v>6967117</v>
+        <v>6967112</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9028,7 +9040,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9038,7 +9050,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>04:52</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9068,7 +9080,7 @@
         <v>133152228</v>
       </c>
       <c r="B81" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9172,10 +9184,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133152207</v>
+        <v>133152170</v>
       </c>
       <c r="B82" t="n">
-        <v>58119</v>
+        <v>79348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9183,46 +9195,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>630231</v>
+        <v>630313</v>
       </c>
       <c r="R82" t="n">
-        <v>6967249</v>
+        <v>6967117</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>04:54</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9294,7 +9294,7 @@
         <v>133152213</v>
       </c>
       <c r="B83" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9398,10 +9398,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133152229</v>
+        <v>133152172</v>
       </c>
       <c r="B84" t="n">
-        <v>79334</v>
+        <v>79380</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9409,21 +9409,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9433,10 +9433,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>630095</v>
+        <v>630311</v>
       </c>
       <c r="R84" t="n">
-        <v>6967106</v>
+        <v>6967128</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>04:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>04:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9505,10 +9505,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133152172</v>
+        <v>133152229</v>
       </c>
       <c r="B85" t="n">
-        <v>79366</v>
+        <v>79348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9516,21 +9516,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>630311</v>
+        <v>630095</v>
       </c>
       <c r="R85" t="n">
-        <v>6967128</v>
+        <v>6967106</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>04:56</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>04:56</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9615,7 +9615,7 @@
         <v>133152162</v>
       </c>
       <c r="B86" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>133202135</v>
       </c>
       <c r="B87" t="n">
-        <v>83183</v>
+        <v>83197</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>133202128</v>
       </c>
       <c r="B88" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>133202134</v>
       </c>
       <c r="B89" t="n">
-        <v>83183</v>
+        <v>83197</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>133202147</v>
       </c>
       <c r="B90" t="n">
-        <v>91942</v>
+        <v>91961</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>133202165</v>
       </c>
       <c r="B91" t="n">
-        <v>83183</v>
+        <v>83197</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10254,10 +10254,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133202148</v>
+        <v>133202145</v>
       </c>
       <c r="B92" t="n">
-        <v>79334</v>
+        <v>91961</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10265,21 +10265,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>630099</v>
+        <v>630093</v>
       </c>
       <c r="R92" t="n">
-        <v>6967120</v>
+        <v>6967070</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10361,10 +10361,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133202145</v>
+        <v>133202148</v>
       </c>
       <c r="B93" t="n">
-        <v>91942</v>
+        <v>79348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10372,21 +10372,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>630093</v>
+        <v>630099</v>
       </c>
       <c r="R93" t="n">
-        <v>6967070</v>
+        <v>6967120</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10468,10 +10468,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133202155</v>
+        <v>133202168</v>
       </c>
       <c r="B94" t="n">
-        <v>91928</v>
+        <v>83197</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10479,21 +10479,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>630210</v>
+        <v>630290</v>
       </c>
       <c r="R94" t="n">
-        <v>6967196</v>
+        <v>6967317</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10578,7 +10578,7 @@
         <v>133202173</v>
       </c>
       <c r="B95" t="n">
-        <v>92651</v>
+        <v>92172</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10682,10 +10682,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133202168</v>
+        <v>133202155</v>
       </c>
       <c r="B96" t="n">
-        <v>83183</v>
+        <v>91947</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10693,21 +10693,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10717,10 +10717,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>630290</v>
+        <v>630210</v>
       </c>
       <c r="R96" t="n">
-        <v>6967317</v>
+        <v>6967196</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10792,7 +10792,7 @@
         <v>133202162</v>
       </c>
       <c r="B97" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>133202142</v>
       </c>
       <c r="B98" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>133202150</v>
       </c>
       <c r="B99" t="n">
-        <v>79590</v>
+        <v>79604</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>133202163</v>
       </c>
       <c r="B100" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11217,10 +11217,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133202151</v>
+        <v>133202169</v>
       </c>
       <c r="B101" t="n">
-        <v>83183</v>
+        <v>91961</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11228,21 +11228,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11252,10 +11252,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>630118</v>
+        <v>630259</v>
       </c>
       <c r="R101" t="n">
-        <v>6967158</v>
+        <v>6967344</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11287,7 +11287,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11324,10 +11324,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133202169</v>
+        <v>133202151</v>
       </c>
       <c r="B102" t="n">
-        <v>91942</v>
+        <v>83197</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11335,21 +11335,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11359,10 +11359,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>630259</v>
+        <v>630118</v>
       </c>
       <c r="R102" t="n">
-        <v>6967344</v>
+        <v>6967158</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11394,7 +11394,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11434,7 +11434,7 @@
         <v>133202127</v>
       </c>
       <c r="B103" t="n">
-        <v>5199</v>
+        <v>5201</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>133202171</v>
       </c>
       <c r="B104" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11660,10 +11660,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133202159</v>
+        <v>133202152</v>
       </c>
       <c r="B105" t="n">
-        <v>91942</v>
+        <v>79380</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11671,21 +11671,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>630290</v>
+        <v>630108</v>
       </c>
       <c r="R105" t="n">
-        <v>6967123</v>
+        <v>6967186</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11767,10 +11767,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133202152</v>
+        <v>133202159</v>
       </c>
       <c r="B106" t="n">
-        <v>79366</v>
+        <v>91961</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11778,21 +11778,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>630108</v>
+        <v>630290</v>
       </c>
       <c r="R106" t="n">
-        <v>6967186</v>
+        <v>6967123</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11877,7 +11877,7 @@
         <v>133202125</v>
       </c>
       <c r="B107" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11981,10 +11981,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133202161</v>
+        <v>133202172</v>
       </c>
       <c r="B108" t="n">
-        <v>91928</v>
+        <v>79380</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11992,21 +11992,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12016,10 +12016,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>630352</v>
+        <v>630285</v>
       </c>
       <c r="R108" t="n">
-        <v>6967119</v>
+        <v>6967276</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133202139</v>
+        <v>133202161</v>
       </c>
       <c r="B109" t="n">
-        <v>91942</v>
+        <v>91947</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12099,21 +12099,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12123,10 +12123,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>630104</v>
+        <v>630352</v>
       </c>
       <c r="R109" t="n">
-        <v>6967096</v>
+        <v>6967119</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12195,32 +12195,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133202156</v>
+        <v>133202139</v>
       </c>
       <c r="B110" t="n">
-        <v>92388</v>
+        <v>91961</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12230,13 +12230,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>630219</v>
+        <v>630104</v>
       </c>
       <c r="R110" t="n">
-        <v>6967208</v>
+        <v>6967096</v>
       </c>
       <c r="S110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12302,32 +12302,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133202172</v>
+        <v>133202156</v>
       </c>
       <c r="B111" t="n">
-        <v>79366</v>
+        <v>92379</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12337,13 +12337,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>630285</v>
+        <v>630219</v>
       </c>
       <c r="R111" t="n">
-        <v>6967276</v>
+        <v>6967208</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12409,10 +12409,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>133202158</v>
+        <v>133202160</v>
       </c>
       <c r="B112" t="n">
-        <v>83183</v>
+        <v>91947</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12420,21 +12420,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>630269</v>
+        <v>630361</v>
       </c>
       <c r="R112" t="n">
-        <v>6967158</v>
+        <v>6967100</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12516,10 +12516,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133202160</v>
+        <v>133202158</v>
       </c>
       <c r="B113" t="n">
-        <v>91928</v>
+        <v>83197</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12527,21 +12527,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12551,10 +12551,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>630361</v>
+        <v>630269</v>
       </c>
       <c r="R113" t="n">
-        <v>6967100</v>
+        <v>6967158</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12626,7 +12626,7 @@
         <v>133202132</v>
       </c>
       <c r="B114" t="n">
-        <v>91942</v>
+        <v>91961</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>133202167</v>
       </c>
       <c r="B115" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12837,10 +12837,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>133202153</v>
+        <v>133202144</v>
       </c>
       <c r="B116" t="n">
-        <v>92227</v>
+        <v>79380</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12848,21 +12848,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12872,10 +12872,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>630160</v>
+        <v>630098</v>
       </c>
       <c r="R116" t="n">
-        <v>6967163</v>
+        <v>6967075</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12917,7 +12917,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12944,10 +12944,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>133202144</v>
+        <v>133202153</v>
       </c>
       <c r="B117" t="n">
-        <v>79366</v>
+        <v>92218</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12955,21 +12955,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>630098</v>
+        <v>630160</v>
       </c>
       <c r="R117" t="n">
-        <v>6967075</v>
+        <v>6967163</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13051,45 +13051,53 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133202170</v>
+        <v>133202138</v>
       </c>
       <c r="B118" t="n">
-        <v>79358</v>
+        <v>57143</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6434</v>
+        <v>102612</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>630274</v>
+        <v>630143</v>
       </c>
       <c r="R118" t="n">
-        <v>6967318</v>
+        <v>6967085</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13121,7 +13129,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13131,7 +13139,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Sannolikt tagen av en rovfågel.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13158,53 +13171,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133202138</v>
+        <v>133202170</v>
       </c>
       <c r="B119" t="n">
-        <v>57136</v>
+        <v>79372</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>102612</v>
+        <v>6434</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gillemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>630143</v>
+        <v>630274</v>
       </c>
       <c r="R119" t="n">
-        <v>6967085</v>
+        <v>6967318</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13236,7 +13241,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13246,12 +13251,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Sannolikt tagen av en rovfågel.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13278,10 +13278,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133202164</v>
+        <v>133202141</v>
       </c>
       <c r="B120" t="n">
-        <v>79334</v>
+        <v>89328</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13289,21 +13289,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13313,10 +13313,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>630329</v>
+        <v>630101</v>
       </c>
       <c r="R120" t="n">
-        <v>6967216</v>
+        <v>6967092</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13348,7 +13348,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13385,10 +13385,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133202141</v>
+        <v>133202164</v>
       </c>
       <c r="B121" t="n">
-        <v>89310</v>
+        <v>79348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13396,21 +13396,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13420,10 +13420,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>630101</v>
+        <v>630329</v>
       </c>
       <c r="R121" t="n">
-        <v>6967092</v>
+        <v>6967216</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13455,7 +13455,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13492,10 +13492,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133202157</v>
+        <v>133202149</v>
       </c>
       <c r="B122" t="n">
-        <v>91928</v>
+        <v>79380</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13503,21 +13503,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13527,10 +13527,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>630257</v>
+        <v>630102</v>
       </c>
       <c r="R122" t="n">
-        <v>6967180</v>
+        <v>6967124</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13599,10 +13599,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133202137</v>
+        <v>133202130</v>
       </c>
       <c r="B123" t="n">
-        <v>92227</v>
+        <v>83197</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13610,21 +13610,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13634,10 +13634,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>630158</v>
+        <v>630275</v>
       </c>
       <c r="R123" t="n">
-        <v>6967093</v>
+        <v>6967143</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13706,10 +13706,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133202136</v>
+        <v>133202157</v>
       </c>
       <c r="B124" t="n">
-        <v>79334</v>
+        <v>91947</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13717,21 +13717,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>630184</v>
+        <v>630257</v>
       </c>
       <c r="R124" t="n">
-        <v>6967090</v>
+        <v>6967180</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13813,10 +13813,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133202149</v>
+        <v>133202137</v>
       </c>
       <c r="B125" t="n">
-        <v>79366</v>
+        <v>92218</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13824,21 +13824,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>630102</v>
+        <v>630158</v>
       </c>
       <c r="R125" t="n">
-        <v>6967124</v>
+        <v>6967093</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13920,10 +13920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133202130</v>
+        <v>133202136</v>
       </c>
       <c r="B126" t="n">
-        <v>83183</v>
+        <v>79348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13931,21 +13931,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>630275</v>
+        <v>630184</v>
       </c>
       <c r="R126" t="n">
-        <v>6967143</v>
+        <v>6967090</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14027,10 +14027,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133202133</v>
+        <v>133202131</v>
       </c>
       <c r="B127" t="n">
-        <v>83319</v>
+        <v>83197</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14038,21 +14038,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14062,10 +14062,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>630226</v>
+        <v>630252</v>
       </c>
       <c r="R127" t="n">
-        <v>6967128</v>
+        <v>6967151</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14097,7 +14097,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14134,10 +14134,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133202131</v>
+        <v>133202133</v>
       </c>
       <c r="B128" t="n">
-        <v>83183</v>
+        <v>83333</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14145,21 +14145,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14169,10 +14169,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>630252</v>
+        <v>630226</v>
       </c>
       <c r="R128" t="n">
-        <v>6967151</v>
+        <v>6967128</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14244,7 +14244,7 @@
         <v>133240046</v>
       </c>
       <c r="B129" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>133240023</v>
       </c>
       <c r="B130" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14455,10 +14455,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133240027</v>
+        <v>133240011</v>
       </c>
       <c r="B131" t="n">
-        <v>79334</v>
+        <v>79380</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14466,21 +14466,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>630159</v>
+        <v>630186</v>
       </c>
       <c r="R131" t="n">
-        <v>6967184</v>
+        <v>6967049</v>
       </c>
       <c r="S131" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14562,10 +14562,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133240011</v>
+        <v>133240026</v>
       </c>
       <c r="B132" t="n">
-        <v>79366</v>
+        <v>91897</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14573,21 +14573,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14597,10 +14597,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>630186</v>
+        <v>630151</v>
       </c>
       <c r="R132" t="n">
-        <v>6967049</v>
+        <v>6967182</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14669,10 +14669,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133240026</v>
+        <v>133240027</v>
       </c>
       <c r="B133" t="n">
-        <v>91878</v>
+        <v>79348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14680,21 +14680,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14704,13 +14704,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>630151</v>
+        <v>630159</v>
       </c>
       <c r="R133" t="n">
-        <v>6967182</v>
+        <v>6967184</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14776,10 +14776,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133240019</v>
+        <v>133240044</v>
       </c>
       <c r="B134" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14811,10 +14811,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>630164</v>
+        <v>630257</v>
       </c>
       <c r="R134" t="n">
-        <v>6967058</v>
+        <v>6967346</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14846,7 +14846,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14883,10 +14883,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133240044</v>
+        <v>133240019</v>
       </c>
       <c r="B135" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14918,10 +14918,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>630257</v>
+        <v>630164</v>
       </c>
       <c r="R135" t="n">
-        <v>6967346</v>
+        <v>6967058</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14993,7 +14993,7 @@
         <v>133240009</v>
       </c>
       <c r="B136" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15097,10 +15097,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133240034</v>
+        <v>133240006</v>
       </c>
       <c r="B137" t="n">
-        <v>79334</v>
+        <v>79380</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15108,21 +15108,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15132,10 +15132,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>630375</v>
+        <v>630259</v>
       </c>
       <c r="R137" t="n">
-        <v>6967109</v>
+        <v>6967095</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15204,10 +15204,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133240006</v>
+        <v>133240003</v>
       </c>
       <c r="B138" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15239,10 +15239,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>630259</v>
+        <v>630320</v>
       </c>
       <c r="R138" t="n">
-        <v>6967095</v>
+        <v>6967080</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15311,10 +15311,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133240003</v>
+        <v>133240034</v>
       </c>
       <c r="B139" t="n">
-        <v>79366</v>
+        <v>79348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>630320</v>
+        <v>630375</v>
       </c>
       <c r="R139" t="n">
-        <v>6967080</v>
+        <v>6967109</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15418,10 +15418,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133240010</v>
+        <v>133240004</v>
       </c>
       <c r="B140" t="n">
-        <v>91928</v>
+        <v>79380</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15429,21 +15429,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15453,10 +15453,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>630202</v>
+        <v>630287</v>
       </c>
       <c r="R140" t="n">
-        <v>6967062</v>
+        <v>6967110</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15528,7 +15528,7 @@
         <v>133240037</v>
       </c>
       <c r="B141" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15632,10 +15632,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133240004</v>
+        <v>133240030</v>
       </c>
       <c r="B142" t="n">
-        <v>79366</v>
+        <v>79348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15643,21 +15643,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15667,13 +15667,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>630287</v>
+        <v>630210</v>
       </c>
       <c r="R142" t="n">
-        <v>6967110</v>
+        <v>6967208</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15739,10 +15739,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133240030</v>
+        <v>133240010</v>
       </c>
       <c r="B143" t="n">
-        <v>79334</v>
+        <v>91947</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15750,21 +15750,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15774,13 +15774,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>630210</v>
+        <v>630202</v>
       </c>
       <c r="R143" t="n">
-        <v>6967208</v>
+        <v>6967062</v>
       </c>
       <c r="S143" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15849,7 +15849,7 @@
         <v>133240005</v>
       </c>
       <c r="B144" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>133240032</v>
       </c>
       <c r="B145" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>133240008</v>
       </c>
       <c r="B146" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>133244099</v>
       </c>
       <c r="B147" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>133240020</v>
       </c>
       <c r="B148" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>133240042</v>
       </c>
       <c r="B149" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16509,10 +16509,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133240024</v>
+        <v>133240038</v>
       </c>
       <c r="B150" t="n">
-        <v>79366</v>
+        <v>79348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16520,21 +16520,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16544,13 +16544,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>630079</v>
+        <v>630337</v>
       </c>
       <c r="R150" t="n">
-        <v>6967088</v>
+        <v>6967201</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16616,10 +16616,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133240038</v>
+        <v>133240024</v>
       </c>
       <c r="B151" t="n">
-        <v>79334</v>
+        <v>79380</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16627,21 +16627,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16651,13 +16651,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>630337</v>
+        <v>630079</v>
       </c>
       <c r="R151" t="n">
-        <v>6967201</v>
+        <v>6967088</v>
       </c>
       <c r="S151" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16726,7 +16726,7 @@
         <v>133240022</v>
       </c>
       <c r="B152" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16830,10 +16830,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133240033</v>
+        <v>133240002</v>
       </c>
       <c r="B153" t="n">
-        <v>79334</v>
+        <v>79380</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16841,21 +16841,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16865,10 +16865,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>630273</v>
+        <v>630334</v>
       </c>
       <c r="R153" t="n">
-        <v>6967142</v>
+        <v>6967084</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -16900,7 +16900,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16937,10 +16937,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133240002</v>
+        <v>133240033</v>
       </c>
       <c r="B154" t="n">
-        <v>79366</v>
+        <v>79348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16948,21 +16948,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16972,10 +16972,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>630334</v>
+        <v>630273</v>
       </c>
       <c r="R154" t="n">
-        <v>6967084</v>
+        <v>6967142</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -17007,7 +17007,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17017,7 +17017,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17044,10 +17044,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133240013</v>
+        <v>133240043</v>
       </c>
       <c r="B155" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17079,10 +17079,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>630166</v>
+        <v>630242</v>
       </c>
       <c r="R155" t="n">
-        <v>6967049</v>
+        <v>6967369</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17151,10 +17151,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133240043</v>
+        <v>133240040</v>
       </c>
       <c r="B156" t="n">
-        <v>79334</v>
+        <v>79380</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17162,21 +17162,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17186,10 +17186,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>630242</v>
+        <v>630295</v>
       </c>
       <c r="R156" t="n">
-        <v>6967369</v>
+        <v>6967374</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -17221,7 +17221,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17258,10 +17258,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133240040</v>
+        <v>133240013</v>
       </c>
       <c r="B157" t="n">
-        <v>79366</v>
+        <v>79348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17269,21 +17269,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17293,10 +17293,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>630295</v>
+        <v>630166</v>
       </c>
       <c r="R157" t="n">
-        <v>6967374</v>
+        <v>6967049</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -17328,7 +17328,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17338,7 +17338,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17365,10 +17365,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133240025</v>
+        <v>133240039</v>
       </c>
       <c r="B158" t="n">
-        <v>79334</v>
+        <v>89328</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17376,21 +17376,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17400,10 +17400,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>630103</v>
+        <v>630317</v>
       </c>
       <c r="R158" t="n">
-        <v>6967179</v>
+        <v>6967329</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -17435,7 +17435,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17472,10 +17472,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>133240007</v>
+        <v>133240036</v>
       </c>
       <c r="B159" t="n">
-        <v>79366</v>
+        <v>79348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17483,21 +17483,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17507,13 +17507,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>630244</v>
+        <v>630368</v>
       </c>
       <c r="R159" t="n">
-        <v>6967085</v>
+        <v>6967120</v>
       </c>
       <c r="S159" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17579,10 +17579,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133240036</v>
+        <v>133240007</v>
       </c>
       <c r="B160" t="n">
-        <v>79334</v>
+        <v>79380</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17590,21 +17590,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17614,13 +17614,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>630368</v>
+        <v>630244</v>
       </c>
       <c r="R160" t="n">
-        <v>6967120</v>
+        <v>6967085</v>
       </c>
       <c r="S160" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17689,7 +17689,7 @@
         <v>133240028</v>
       </c>
       <c r="B161" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17793,10 +17793,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133240039</v>
+        <v>133240025</v>
       </c>
       <c r="B162" t="n">
-        <v>89310</v>
+        <v>79348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17804,21 +17804,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17828,10 +17828,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>630317</v>
+        <v>630103</v>
       </c>
       <c r="R162" t="n">
-        <v>6967329</v>
+        <v>6967179</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17903,7 +17903,7 @@
         <v>133240021</v>
       </c>
       <c r="B163" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>133240031</v>
       </c>
       <c r="B164" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18114,10 +18114,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133240018</v>
+        <v>133240041</v>
       </c>
       <c r="B165" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18149,10 +18149,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>630148</v>
+        <v>630250</v>
       </c>
       <c r="R165" t="n">
-        <v>6967065</v>
+        <v>6967366</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18221,10 +18221,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133240041</v>
+        <v>133240018</v>
       </c>
       <c r="B166" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18256,10 +18256,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>630250</v>
+        <v>630148</v>
       </c>
       <c r="R166" t="n">
-        <v>6967366</v>
+        <v>6967065</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18331,7 +18331,7 @@
         <v>133240029</v>
       </c>
       <c r="B167" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -14244,7 +14244,7 @@
         <v>133240046</v>
       </c>
       <c r="B129" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>133240023</v>
       </c>
       <c r="B130" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>133240011</v>
       </c>
       <c r="B131" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>133240026</v>
       </c>
       <c r="B132" t="n">
-        <v>91897</v>
+        <v>91907</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>133240027</v>
       </c>
       <c r="B133" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>133240044</v>
       </c>
       <c r="B134" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>133240019</v>
       </c>
       <c r="B135" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>133240009</v>
       </c>
       <c r="B136" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>133240006</v>
       </c>
       <c r="B137" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>133240003</v>
       </c>
       <c r="B138" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>133240034</v>
       </c>
       <c r="B139" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>133240004</v>
       </c>
       <c r="B140" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>133240037</v>
       </c>
       <c r="B141" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>133240030</v>
       </c>
       <c r="B142" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>133240010</v>
       </c>
       <c r="B143" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>133240005</v>
       </c>
       <c r="B144" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>133240032</v>
       </c>
       <c r="B145" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>133240008</v>
       </c>
       <c r="B146" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>133244099</v>
       </c>
       <c r="B147" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>133240020</v>
       </c>
       <c r="B148" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>133240042</v>
       </c>
       <c r="B149" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>133240038</v>
       </c>
       <c r="B150" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>133240024</v>
       </c>
       <c r="B151" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>133240022</v>
       </c>
       <c r="B152" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>133240002</v>
       </c>
       <c r="B153" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>133240033</v>
       </c>
       <c r="B154" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>133240043</v>
       </c>
       <c r="B155" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>133240040</v>
       </c>
       <c r="B156" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>133240013</v>
       </c>
       <c r="B157" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>133240039</v>
       </c>
       <c r="B158" t="n">
-        <v>89328</v>
+        <v>89338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>133240036</v>
       </c>
       <c r="B159" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>133240007</v>
       </c>
       <c r="B160" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>133240028</v>
       </c>
       <c r="B161" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>133240025</v>
       </c>
       <c r="B162" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>133240021</v>
       </c>
       <c r="B163" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>133240031</v>
       </c>
       <c r="B164" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>133240041</v>
       </c>
       <c r="B165" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>133240018</v>
       </c>
       <c r="B166" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>133240029</v>
       </c>
       <c r="B167" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 56749-2025 artfynd.xlsx
+++ b/artfynd/A 56749-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY167"/>
+  <dimension ref="A1:AZ167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129945640</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152159</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152161</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152162</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152163</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152164</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152167</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152168</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152171</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1839,6 +1894,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152172</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152178</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2053,6 +2118,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152184</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2160,6 +2230,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152198</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2267,6 +2342,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152199</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2374,6 +2454,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152214</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2481,6 +2566,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152225</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2588,6 +2678,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152228</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2695,6 +2790,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152230</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2802,6 +2902,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152232</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2909,6 +3014,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152234</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3016,6 +3126,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152246</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3123,6 +3238,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202125</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3230,6 +3350,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202128</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3337,6 +3462,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202144</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3444,6 +3574,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202149</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3551,6 +3686,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202152</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3658,6 +3798,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202172</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3765,6 +3910,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240002</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3872,6 +4022,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240003</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3979,6 +4134,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240004</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4086,6 +4246,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240005</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4193,6 +4358,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240006</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4300,6 +4470,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240007</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4407,6 +4582,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240011</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4514,6 +4694,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240020</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4621,6 +4806,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240024</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4728,6 +4918,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240040</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4835,6 +5030,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240042</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4942,6 +5142,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240046</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5049,6 +5254,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152223</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5156,6 +5366,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202141</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5263,6 +5478,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240039</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5360,6 +5580,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129945639</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5467,6 +5692,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152188</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5574,6 +5804,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152205</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5681,6 +5916,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152217</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5788,6 +6028,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152218</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5895,6 +6140,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152224</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6002,6 +6252,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202137</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6109,6 +6364,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202153</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6206,6 +6466,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126021884</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6313,6 +6578,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152189</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6420,6 +6690,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152194</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6527,6 +6802,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152201</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6634,6 +6914,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152204</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6741,6 +7026,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152213</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6848,6 +7138,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152215</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6955,6 +7250,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152219</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7062,6 +7362,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152221</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7169,6 +7474,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152226</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7276,6 +7586,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152235</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7383,6 +7698,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152239</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7490,6 +7810,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202155</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7597,6 +7922,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202157</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7704,6 +8034,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202160</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7811,6 +8146,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202161</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7918,6 +8258,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240010</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8025,6 +8370,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240029</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8132,6 +8482,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240031</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8239,6 +8594,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240032</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8346,6 +8706,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152203</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8453,6 +8818,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152220</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8560,6 +8930,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202132</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8667,6 +9042,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202139</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8774,6 +9154,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202145</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8881,6 +9266,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202147</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8988,6 +9378,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202159</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9095,6 +9490,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202169</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9202,6 +9602,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202156</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9309,6 +9714,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152174</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9416,6 +9826,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152190</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9523,6 +9938,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152193</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9630,6 +10050,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152196</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9737,6 +10162,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152200</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9844,6 +10274,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152210</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9951,6 +10386,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152212</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10058,6 +10498,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152222</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10165,6 +10610,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152227</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10272,6 +10722,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152238</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10379,6 +10834,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152241</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10486,6 +10946,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152243</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10593,6 +11058,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202130</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10700,6 +11170,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202131</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10807,6 +11282,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202134</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10914,6 +11394,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202135</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11021,6 +11506,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202151</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11128,6 +11618,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202158</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11235,6 +11730,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202165</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11342,6 +11842,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202168</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11439,6 +11944,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126021882</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11546,6 +12056,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202173</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11653,6 +12168,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152185</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11760,6 +12280,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152187</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11857,6 +12382,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126021886</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11954,6 +12484,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126021887</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12051,6 +12586,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129945641</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12158,6 +12698,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152165</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12265,6 +12810,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152169</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12372,6 +12922,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152170</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12479,6 +13034,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152173</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12586,6 +13146,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152175</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12693,6 +13258,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152180</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12800,6 +13370,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152181</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12907,6 +13482,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152182</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13014,6 +13594,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152191</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13121,6 +13706,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152206</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13228,6 +13818,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152208</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13335,6 +13930,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152209</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13442,6 +14042,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152216</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13549,6 +14154,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152229</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13656,6 +14266,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152231</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13768,6 +14383,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152237</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13875,6 +14495,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152240</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13982,6 +14607,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152242</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14089,6 +14719,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202136</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14196,6 +14831,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202142</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14303,6 +14943,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202148</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14410,6 +15055,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202162</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14517,6 +15167,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202163</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14624,6 +15279,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202164</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14731,6 +15391,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202167</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14838,6 +15503,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202171</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14945,6 +15615,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240008</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15052,6 +15727,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240009</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15159,6 +15839,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240013</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15266,6 +15951,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240018</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15373,6 +16063,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240019</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15480,6 +16175,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240021</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15587,6 +16287,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240022</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15694,6 +16399,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240023</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15801,6 +16511,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240025</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15908,6 +16623,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240027</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16015,6 +16735,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240028</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16122,6 +16847,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240030</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16229,6 +16959,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240033</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16336,6 +17071,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240034</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16443,6 +17183,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240036</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16550,6 +17295,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240037</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16657,6 +17407,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240038</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16764,6 +17519,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240041</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16871,6 +17631,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240043</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16978,6 +17743,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133240044</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17085,6 +17855,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152183</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17192,6 +17967,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152195</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17299,6 +18079,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152197</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17406,6 +18191,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202170</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17513,6 +18303,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202133</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17620,6 +18415,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202150</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17722,6 +18522,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129945635</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17850,6 +18655,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133244099</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17970,6 +18780,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202138</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18072,6 +18887,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129945638</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18191,6 +19011,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152177</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18310,6 +19135,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133152207</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18432,8 +19262,181 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133202127</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>